--- a/Support/links_documents_EXCEL.xlsx
+++ b/Support/links_documents_EXCEL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://msss365-my.sharepoint.com/personal/vincent_desrochers_med_ssss_gouv_qc_ca/Documents/Programmation/Git-Hub/emtools/Support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{9B365C08-431E-40CE-980D-9CE06A7F3745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD46404-7054-4988-8E9F-565E80D2250C}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="8_{9B365C08-431E-40CE-980D-9CE06A7F3745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4248E4-709E-42EA-9A5F-767D025135C2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5A9E7570-B546-46BC-9B1E-C8C8D4DF09A1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="DonnéesExternes_1" localSheetId="1" hidden="1">'links (2)'!$A$1:$E$92</definedName>
-    <definedName name="DonnéesExternes_1" localSheetId="2" hidden="1">links_documents_csv!$A$1:$J$197</definedName>
+    <definedName name="DonnéesExternes_1" localSheetId="2" hidden="1">links_documents_csv!$A$1:$J$198</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="838">
   <si>
     <t>link_text,url,source_page,link_type,collected_at</t>
   </si>
@@ -2197,9 +2197,6 @@
     <t>Rx, médicaments, pharmaco, prescription</t>
   </si>
   <si>
-    <t>https://bibliotheques.cissslaval.ca/GEIDEFile/62-200-010_Ord_Insuline_IV_2021-08-18.pdf?Archive=113145793132&amp;File=62%5F200%5F010%5Ford%5Finsuline%5FiV%5F2021%5F08%5F18%5Fpdf</t>
-  </si>
-  <si>
     <t>https://bibliotheques.cissslaval.ca/GEIDEFile/OIP_68-000-421_Traitement_des_infection_urinaire_CHSLD.pdf?Archive=113025793120&amp;File=oiP%5F68%5F000%5F421%5FTraitement%5Fdes%5Finfection%5Furinaire%5FcHSLD%5Fpdf</t>
   </si>
   <si>
@@ -2209,9 +2206,6 @@
     <t>https://bibliotheques.cissslaval.ca/GEIDEFile/OIP_62-200-262_Ordonnance_externe_Administration_fer_IV_ambulatoire.pdf?Archive=112784693096&amp;File=oiP%5F62%5F200%5F262%5Fordonnance%5Fexterne%5Fadministration%5Ffer%5FiV%5Fambulatoire%5Fpdf</t>
   </si>
   <si>
-    <t>https://bibliotheques.cissslaval.ca/GEIDEFile/OIP_62-200-267_Ord_Insuline_SC_2026-02-12.pdf?Archive=115037993321&amp;File=oiP%5F62%5F200%5F267%5Ford%5Finsuline%5FSc%5F2026%5F02%5F12%5Fpdf</t>
-  </si>
-  <si>
     <t>https://bibliotheques.cissslaval.ca/GEIDEFile/68-000-301_Ordonnances_pediatrique_Bronchilite.pdf?Archive=112776893095&amp;File=68%5F000%5F301%5Fordonnances%5Fpediatrique%5FBronchilite%5Fpdf</t>
   </si>
   <si>
@@ -2350,9 +2344,6 @@
     <t>Antibiotiques, ambulatoire</t>
   </si>
   <si>
-    <t>Traitement, asthme, mpoc</t>
-  </si>
-  <si>
     <t>https://bibliotheques.cissslaval.ca/GEIDEFile/62-200-148_Ordonnances_cessation_tabagique_en_utilisant_des_therapies_de_remplacement_de_nicotine2018-05-30.pdf?Archive=115424693360&amp;File=62%5F200%5F148%5Fordonnances%5Fcessation%5Ftabagique%5Fen%5Futilisant%5Fdes%5Ftherapies%5Fde%5Fremplacement%5Fde%5Fnicotine2018%5F05%5F30%5Fpdf</t>
   </si>
   <si>
@@ -2543,6 +2534,24 @@
   </si>
   <si>
     <t>https://choisiravecsoinquebec.ca/wp-content/uploads/2024/03/Insomnia_EN_FINAL.pdf</t>
+  </si>
+  <si>
+    <t>Occlusion intestinale</t>
+  </si>
+  <si>
+    <t>https://bibliotheques.cissslaval.ca/GEIDEFile/OIP_62-200-834_Occlusion_intestinale_2026-08-12.pdf?Archive=115323593350&amp;File=oiP%5F62%5F200%5F834%5Focclusion%5Fintestinale%5F2026%5F08%5F12%5Fpdf</t>
+  </si>
+  <si>
+    <t>Occlusion intestinale, grafin, gastro</t>
+  </si>
+  <si>
+    <t>Traitement, asthme, mpoc, inhalotherapie</t>
+  </si>
+  <si>
+    <t>https://bibliotheques.cissslaval.ca/GEIDEFile/OIP_62-200-267_Ord_Insuline_SC_2026-02-12.pdf?Archive=115558093373&amp;File=oiP%5F62%5F200%5F267%5Ford%5Finsuline%5FSc%5F2026%5F02%5F12%5Fpdf</t>
+  </si>
+  <si>
+    <t>https://bibliotheques.cissslaval.ca/GEIDEFile/62-200-010_Ord_Insuline_IV_2021-08-18.pdf?Archive=115350293353&amp;File=62%5F200%5F010%5Ford%5Finsuline%5FiV%5F2021%5F08%5F18%5Fpdf</t>
   </si>
 </sst>
 </file>
@@ -3035,13 +3044,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3089,27 +3098,6 @@
   </cellStyles>
   <dxfs count="14">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="27" formatCode="yyyy/mm/dd\ hh:mm"/>
     </dxf>
     <dxf>
@@ -3126,6 +3114,27 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3775,37 +3784,37 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DE1A692-D182-48B1-AF24-B08C3BADDDB7}" name="links" displayName="links" ref="A1:E92" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E92" xr:uid="{6DE1A692-D182-48B1-AF24-B08C3BADDDB7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8BEA4C21-4044-4079-9E1A-527E856DC298}" uniqueName="1" name="link_text" queryTableFieldId="1" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{7C65E6FF-1686-4FDD-96F3-2AD9E0FDF1F8}" uniqueName="2" name="url" queryTableFieldId="2" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{18BB0FCF-509C-47E0-A822-E32F6857A439}" uniqueName="3" name="source_page" queryTableFieldId="3" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{4A776295-DFD0-4A4F-A121-D0FF62704E6D}" uniqueName="4" name="link_type" queryTableFieldId="4" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{1C6E3148-D1F4-4F60-8957-153FC9DBB625}" uniqueName="5" name="collected_at" queryTableFieldId="5" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{8BEA4C21-4044-4079-9E1A-527E856DC298}" uniqueName="1" name="link_text" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{7C65E6FF-1686-4FDD-96F3-2AD9E0FDF1F8}" uniqueName="2" name="url" queryTableFieldId="2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{18BB0FCF-509C-47E0-A822-E32F6857A439}" uniqueName="3" name="source_page" queryTableFieldId="3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{4A776295-DFD0-4A4F-A121-D0FF62704E6D}" uniqueName="4" name="link_type" queryTableFieldId="4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{1C6E3148-D1F4-4F60-8957-153FC9DBB625}" uniqueName="5" name="collected_at" queryTableFieldId="5" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}" name="links_documents" displayName="links_documents" ref="A1:J197" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:J197" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J197">
-    <sortCondition ref="F2:F197"/>
-    <sortCondition ref="E2:E197"/>
-    <sortCondition ref="C2:C197"/>
-    <sortCondition ref="G2:G197"/>
-    <sortCondition ref="A2:A197"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}" name="links_documents" displayName="links_documents" ref="A1:J198" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:J198" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J198">
+    <sortCondition ref="F2:F198"/>
+    <sortCondition ref="E2:E198"/>
+    <sortCondition ref="C2:C198"/>
+    <sortCondition ref="G2:G198"/>
+    <sortCondition ref="A2:A198"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{487E3CF9-4E9F-41C4-A553-12FE09D4D914}" uniqueName="1" name="title" queryTableFieldId="1" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{8F61F6E0-4133-42A5-924D-8BD507F4F59B}" uniqueName="2" name="href" queryTableFieldId="2" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{0BDB0DFA-9C44-44B4-9B3D-A67A9A379DFB}" uniqueName="3" name="section" queryTableFieldId="3" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{FAE5E803-4030-4058-89B4-85BD5D0DC6D9}" uniqueName="4" name="sectionTitle" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{30F11EB6-BDD8-4CE0-8231-A45CF3C5D1BF}" uniqueName="5" name="sectionDescription" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{8AB440D0-3289-4225-8E8C-4A5AAAE34C2E}" uniqueName="6" name="sectionOrder" queryTableFieldId="6" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{C58EA5C6-C560-40F5-89D2-88E731450954}" uniqueName="7" name="category" queryTableFieldId="7" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{5329A6F8-5583-41CC-A1B7-F1DE77D80783}" uniqueName="8" name="tags" queryTableFieldId="8" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{8F61F6E0-4133-42A5-924D-8BD507F4F59B}" uniqueName="2" name="href" queryTableFieldId="2" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{0BDB0DFA-9C44-44B4-9B3D-A67A9A379DFB}" uniqueName="3" name="section" queryTableFieldId="3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{FAE5E803-4030-4058-89B4-85BD5D0DC6D9}" uniqueName="4" name="sectionTitle" queryTableFieldId="4" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{30F11EB6-BDD8-4CE0-8231-A45CF3C5D1BF}" uniqueName="5" name="sectionDescription" queryTableFieldId="5" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{8AB440D0-3289-4225-8E8C-4A5AAAE34C2E}" uniqueName="6" name="sectionOrder" queryTableFieldId="6" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{C58EA5C6-C560-40F5-89D2-88E731450954}" uniqueName="7" name="category" queryTableFieldId="7" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{5329A6F8-5583-41CC-A1B7-F1DE77D80783}" uniqueName="8" name="tags" queryTableFieldId="8" dataDxfId="6"/>
     <tableColumn id="9" xr3:uid="{0E27ED48-B958-4B99-88D7-05C34895B6F5}" uniqueName="9" name="targetBlank" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{69081A57-C339-43AB-A50E-1E99EDDAE734}" uniqueName="10" name="description" queryTableFieldId="10" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{69081A57-C339-43AB-A50E-1E99EDDAE734}" uniqueName="10" name="description" queryTableFieldId="10" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7132,14 +7141,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FCBDD6-984D-408F-975A-1DE93A8BC72E}">
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J198"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
     <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="3" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="62.140625" bestFit="1" customWidth="1"/>
@@ -7154,13 +7163,13 @@
       <c r="B1" t="s">
         <v>474</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>475</v>
       </c>
       <c r="D1" t="s">
         <v>476</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>477</v>
       </c>
       <c r="F1" t="s">
@@ -7181,26 +7190,26 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B2" t="s">
-        <v>755</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>712</v>
       </c>
       <c r="H2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="I2" t="s">
         <v>694</v>
@@ -7208,26 +7217,26 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B3" t="s">
-        <v>756</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>9</v>
       </c>
       <c r="G3" t="s">
         <v>712</v>
       </c>
       <c r="H3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="I3" t="s">
         <v>694</v>
@@ -7235,19 +7244,19 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B4" t="s">
-        <v>725</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>9</v>
       </c>
       <c r="G4" t="s">
@@ -7259,26 +7268,26 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B5" t="s">
-        <v>732</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>9</v>
       </c>
       <c r="G5" t="s">
         <v>712</v>
       </c>
       <c r="H5" t="s">
-        <v>770</v>
+        <v>835</v>
       </c>
       <c r="I5" t="s">
         <v>694</v>
@@ -7286,26 +7295,26 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B6" t="s">
-        <v>775</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>9</v>
       </c>
       <c r="G6" t="s">
         <v>712</v>
       </c>
       <c r="H6" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="I6" t="s">
         <v>694</v>
@@ -7313,26 +7322,26 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B7" t="s">
-        <v>727</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>9</v>
       </c>
       <c r="G7" t="s">
         <v>712</v>
       </c>
       <c r="H7" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="I7" t="s">
         <v>694</v>
@@ -7340,26 +7349,26 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B8" t="s">
-        <v>724</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>9</v>
       </c>
       <c r="G8" t="s">
         <v>712</v>
       </c>
       <c r="H8" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="I8" t="s">
         <v>694</v>
@@ -7367,26 +7376,26 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B9" t="s">
-        <v>731</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>9</v>
       </c>
       <c r="G9" t="s">
         <v>712</v>
       </c>
       <c r="H9" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="I9" t="s">
         <v>694</v>
@@ -7394,26 +7403,26 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B10" t="s">
-        <v>726</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>9</v>
       </c>
       <c r="G10" t="s">
         <v>712</v>
       </c>
       <c r="H10" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="I10" t="s">
         <v>694</v>
@@ -7421,26 +7430,26 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B11" t="s">
-        <v>720</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>9</v>
       </c>
       <c r="G11" t="s">
         <v>712</v>
       </c>
       <c r="H11" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="I11" t="s">
         <v>694</v>
@@ -7448,26 +7457,26 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B12" t="s">
-        <v>722</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>9</v>
       </c>
       <c r="G12" t="s">
         <v>712</v>
       </c>
       <c r="H12" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="I12" t="s">
         <v>694</v>
@@ -7475,26 +7484,26 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B13" t="s">
-        <v>728</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>9</v>
       </c>
       <c r="G13" t="s">
         <v>712</v>
       </c>
       <c r="H13" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="I13" t="s">
         <v>694</v>
@@ -7502,19 +7511,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B14" t="s">
         <v>714</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4" t="s">
+      <c r="C14" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>9</v>
       </c>
       <c r="G14" t="s">
@@ -7529,26 +7538,26 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B15" t="s">
-        <v>733</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>9</v>
       </c>
       <c r="G15" t="s">
         <v>712</v>
       </c>
       <c r="H15" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="I15" t="s">
         <v>694</v>
@@ -7556,459 +7565,458 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B16" t="s">
-        <v>773</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>9</v>
       </c>
       <c r="G16" t="s">
         <v>712</v>
       </c>
       <c r="H16" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I16" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B17" t="s">
-        <v>730</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>9</v>
       </c>
       <c r="G17" t="s">
         <v>712</v>
       </c>
       <c r="H17" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="I17" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>798</v>
-      </c>
-      <c r="B18" t="s">
-        <v>719</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>9</v>
       </c>
       <c r="G18" t="s">
         <v>712</v>
       </c>
       <c r="H18" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="I18" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>799</v>
-      </c>
-      <c r="B19" t="s">
-        <v>723</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>9</v>
       </c>
       <c r="G19" t="s">
         <v>712</v>
       </c>
       <c r="H19" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="I19" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B20" t="s">
-        <v>818</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>9</v>
       </c>
       <c r="G20" t="s">
         <v>712</v>
       </c>
       <c r="H20" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="I20" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B21" t="s">
-        <v>815</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>9</v>
       </c>
       <c r="G21" t="s">
         <v>712</v>
       </c>
       <c r="H21" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I21" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="B22" t="s">
-        <v>711</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>9</v>
       </c>
       <c r="G22" t="s">
         <v>712</v>
       </c>
       <c r="H22" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="I22" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B23" t="s">
-        <v>812</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>9</v>
       </c>
       <c r="G23" t="s">
         <v>712</v>
       </c>
       <c r="H23" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="I23" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="B24" t="s">
-        <v>780</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>9</v>
       </c>
       <c r="G24" t="s">
         <v>712</v>
       </c>
       <c r="H24" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="I24" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B25" t="s">
         <v>777</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="4" t="s">
+      <c r="C25" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>9</v>
       </c>
       <c r="G25" t="s">
         <v>712</v>
       </c>
       <c r="H25" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="I25" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B26" t="s">
-        <v>729</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>9</v>
       </c>
       <c r="G26" t="s">
         <v>712</v>
       </c>
       <c r="H26" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="I26" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B27" t="s">
-        <v>738</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>9</v>
       </c>
       <c r="G27" t="s">
         <v>712</v>
       </c>
       <c r="H27" t="s">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="I27" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B28" t="s">
-        <v>752</v>
-      </c>
-      <c r="C28" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="4" t="s">
+      <c r="C28" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>9</v>
       </c>
       <c r="G28" t="s">
         <v>712</v>
       </c>
       <c r="H28" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="I28" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="B29" t="s">
-        <v>822</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>9</v>
       </c>
       <c r="G29" t="s">
         <v>712</v>
       </c>
       <c r="H29" t="s">
-        <v>823</v>
+        <v>751</v>
       </c>
       <c r="I29" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="4" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>802</v>
+      </c>
+      <c r="B30" t="s">
+        <v>768</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>9</v>
       </c>
       <c r="G30" t="s">
         <v>712</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>772</v>
+      <c r="H30" t="s">
+        <v>769</v>
       </c>
       <c r="I30" t="s">
         <v>694</v>
       </c>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B31" t="s">
-        <v>721</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>9</v>
       </c>
       <c r="G31" t="s">
         <v>712</v>
       </c>
       <c r="H31" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="I31" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B32" t="s">
-        <v>754</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>9</v>
       </c>
       <c r="G32" t="s">
         <v>712</v>
       </c>
       <c r="H32" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="I32" t="s">
         <v>694</v>
@@ -8016,26 +8024,26 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="B33" t="s">
-        <v>778</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>9</v>
       </c>
       <c r="G33" t="s">
         <v>712</v>
       </c>
       <c r="H33" t="s">
-        <v>779</v>
+        <v>820</v>
       </c>
       <c r="I33" t="s">
         <v>694</v>
@@ -8043,20 +8051,26 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>740</v>
+        <v>805</v>
       </c>
       <c r="B34" t="s">
-        <v>741</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="F34" s="3">
+        <v>775</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="F34" s="2">
         <v>9</v>
       </c>
+      <c r="G34" t="s">
+        <v>712</v>
+      </c>
       <c r="H34" t="s">
-        <v>742</v>
+        <v>776</v>
       </c>
       <c r="I34" t="s">
         <v>694</v>
@@ -8069,11 +8083,11 @@
       <c r="B35" t="s">
         <v>717</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="F35" s="3">
+      <c r="C35" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="F35" s="2">
         <v>9</v>
       </c>
       <c r="H35" t="s">
@@ -8085,60 +8099,46 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>489</v>
+        <v>738</v>
       </c>
       <c r="B36" t="s">
-        <v>490</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F36" s="3">
-        <v>10</v>
-      </c>
-      <c r="G36" t="s">
-        <v>289</v>
+        <v>739</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="F36" s="2">
+        <v>9</v>
       </c>
       <c r="H36" t="s">
-        <v>491</v>
+        <v>740</v>
       </c>
       <c r="I36" t="s">
         <v>694</v>
-      </c>
-      <c r="J36" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="B37" t="s">
-        <v>499</v>
-      </c>
-      <c r="C37" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>10</v>
       </c>
       <c r="G37" t="s">
         <v>289</v>
       </c>
       <c r="H37" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="I37" t="s">
         <v>694</v>
@@ -8149,92 +8149,92 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B38" t="s">
-        <v>502</v>
-      </c>
-      <c r="C38" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>10</v>
       </c>
       <c r="G38" t="s">
         <v>289</v>
       </c>
       <c r="H38" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I38" t="s">
         <v>694</v>
       </c>
       <c r="J38" t="s">
-        <v>504</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B39" t="s">
-        <v>484</v>
-      </c>
-      <c r="C39" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="2">
         <v>10</v>
       </c>
       <c r="G39" t="s">
         <v>289</v>
       </c>
       <c r="H39" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="I39" t="s">
         <v>694</v>
       </c>
       <c r="J39" t="s">
-        <v>289</v>
+        <v>504</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B40" t="s">
-        <v>493</v>
-      </c>
-      <c r="C40" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="2">
         <v>10</v>
       </c>
       <c r="G40" t="s">
         <v>289</v>
       </c>
       <c r="H40" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="I40" t="s">
         <v>694</v>
@@ -8245,28 +8245,28 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B41" t="s">
-        <v>496</v>
-      </c>
-      <c r="C41" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>10</v>
       </c>
       <c r="G41" t="s">
         <v>289</v>
       </c>
       <c r="H41" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="I41" t="s">
         <v>694</v>
@@ -8277,28 +8277,28 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="B42" t="s">
-        <v>512</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="F42" s="3">
-        <v>20</v>
+        <v>496</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
       </c>
       <c r="G42" t="s">
         <v>289</v>
       </c>
       <c r="H42" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="I42" t="s">
         <v>694</v>
@@ -8309,28 +8309,28 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B43" t="s">
-        <v>506</v>
-      </c>
-      <c r="C43" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="2">
         <v>20</v>
       </c>
       <c r="G43" t="s">
         <v>289</v>
       </c>
       <c r="H43" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I43" t="s">
         <v>694</v>
@@ -8341,28 +8341,28 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="B44" t="s">
-        <v>522</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="F44" s="3">
-        <v>30</v>
+        <v>506</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="F44" s="2">
+        <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>523</v>
+        <v>289</v>
       </c>
       <c r="H44" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="I44" t="s">
         <v>694</v>
@@ -8373,28 +8373,28 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B45" t="s">
-        <v>526</v>
-      </c>
-      <c r="C45" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="2">
         <v>30</v>
       </c>
       <c r="G45" t="s">
         <v>523</v>
       </c>
       <c r="H45" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I45" t="s">
         <v>694</v>
@@ -8405,28 +8405,28 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B46" t="s">
-        <v>529</v>
-      </c>
-      <c r="C46" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="2">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="H46" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="I46" t="s">
         <v>694</v>
@@ -8437,28 +8437,28 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="B47" t="s">
-        <v>515</v>
-      </c>
-      <c r="C47" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="2">
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="H47" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="I47" t="s">
         <v>694</v>
@@ -8469,174 +8469,176 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>697</v>
+        <v>514</v>
       </c>
       <c r="B48" t="s">
-        <v>696</v>
-      </c>
-      <c r="C48" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>30</v>
       </c>
+      <c r="G48" t="s">
+        <v>519</v>
+      </c>
       <c r="H48" t="s">
-        <v>701</v>
+        <v>520</v>
       </c>
       <c r="I48" t="s">
         <v>694</v>
       </c>
       <c r="J48" t="s">
-        <v>703</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B49" t="s">
-        <v>699</v>
-      </c>
-      <c r="C49" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="2">
         <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I49" t="s">
         <v>694</v>
       </c>
       <c r="J49" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>830</v>
+        <v>698</v>
       </c>
       <c r="B50" t="s">
-        <v>831</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="F50" s="3">
-        <v>40</v>
-      </c>
-      <c r="G50" t="s">
-        <v>826</v>
+        <v>699</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="F50" s="2">
+        <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>832</v>
+        <v>700</v>
       </c>
       <c r="I50" t="s">
         <v>694</v>
+      </c>
+      <c r="J50" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="B51" t="s">
-        <v>834</v>
-      </c>
-      <c r="C51" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>40</v>
       </c>
       <c r="G51" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="H51" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="I51" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="A52" t="s">
+        <v>830</v>
+      </c>
+      <c r="B52" t="s">
+        <v>831</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F52" s="2">
+        <v>40</v>
+      </c>
+      <c r="G52" t="s">
+        <v>823</v>
+      </c>
+      <c r="H52" t="s">
         <v>829</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="F52" s="3">
-        <v>40</v>
-      </c>
-      <c r="G52" t="s">
-        <v>826</v>
-      </c>
-      <c r="H52" t="s">
-        <v>827</v>
-      </c>
       <c r="I52" t="s">
         <v>694</v>
       </c>
-      <c r="J52" s="2"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B53" t="s">
-        <v>825</v>
-      </c>
-      <c r="C53" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="2">
         <v>40</v>
       </c>
       <c r="G53" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="H53" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I53" t="s">
         <v>694</v>
@@ -8644,127 +8646,124 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>743</v>
+        <v>821</v>
       </c>
       <c r="B54" t="s">
-        <v>744</v>
-      </c>
-      <c r="C54" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="2">
         <v>40</v>
       </c>
       <c r="G54" t="s">
-        <v>745</v>
+        <v>823</v>
       </c>
       <c r="H54" t="s">
-        <v>746</v>
+        <v>824</v>
       </c>
       <c r="I54" t="s">
         <v>694</v>
-      </c>
-      <c r="J54" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B55" t="s">
-        <v>749</v>
-      </c>
-      <c r="C55" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="2">
         <v>40</v>
       </c>
       <c r="G55" t="s">
+        <v>743</v>
+      </c>
+      <c r="H55" t="s">
+        <v>744</v>
+      </c>
+      <c r="I55" t="s">
+        <v>694</v>
+      </c>
+      <c r="J55" t="s">
         <v>745</v>
-      </c>
-      <c r="H55" t="s">
-        <v>750</v>
-      </c>
-      <c r="I55" t="s">
-        <v>694</v>
-      </c>
-      <c r="J55" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>554</v>
+        <v>746</v>
       </c>
       <c r="B56" t="s">
-        <v>555</v>
-      </c>
-      <c r="C56" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="2">
         <v>40</v>
       </c>
       <c r="G56" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="H56" t="s">
-        <v>556</v>
+        <v>748</v>
       </c>
       <c r="I56" t="s">
         <v>694</v>
       </c>
       <c r="J56" t="s">
-        <v>289</v>
+        <v>749</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="B57" t="s">
-        <v>546</v>
-      </c>
-      <c r="C57" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="2">
         <v>40</v>
       </c>
       <c r="G57" t="s">
-        <v>537</v>
+        <v>743</v>
       </c>
       <c r="H57" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="I57" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="J57" t="s">
         <v>289</v>
@@ -8772,31 +8771,31 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="B58" t="s">
-        <v>533</v>
-      </c>
-      <c r="C58" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="2">
         <v>40</v>
       </c>
       <c r="G58" t="s">
         <v>537</v>
       </c>
       <c r="H58" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="I58" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J58" t="s">
         <v>289</v>
@@ -8804,28 +8803,28 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B59" t="s">
-        <v>540</v>
-      </c>
-      <c r="C59" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="2">
         <v>40</v>
       </c>
       <c r="G59" t="s">
         <v>537</v>
       </c>
       <c r="H59" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I59" t="s">
         <v>694</v>
@@ -8836,28 +8835,28 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B60" t="s">
-        <v>552</v>
-      </c>
-      <c r="C60" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="2">
         <v>40</v>
       </c>
       <c r="G60" t="s">
         <v>537</v>
       </c>
       <c r="H60" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="I60" t="s">
         <v>694</v>
@@ -8868,28 +8867,28 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s">
-        <v>543</v>
-      </c>
-      <c r="C61" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="2">
         <v>40</v>
       </c>
       <c r="G61" t="s">
         <v>537</v>
       </c>
       <c r="H61" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="I61" t="s">
         <v>694</v>
@@ -8900,28 +8899,28 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B62" t="s">
-        <v>549</v>
-      </c>
-      <c r="C62" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="2">
         <v>40</v>
       </c>
       <c r="G62" t="s">
         <v>537</v>
       </c>
       <c r="H62" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="I62" t="s">
         <v>694</v>
@@ -8932,28 +8931,28 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>613</v>
+        <v>548</v>
       </c>
       <c r="B63" t="s">
-        <v>614</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="F63" s="3">
-        <v>50</v>
+        <v>549</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F63" s="2">
+        <v>40</v>
       </c>
       <c r="G63" t="s">
-        <v>615</v>
+        <v>537</v>
       </c>
       <c r="H63" t="s">
-        <v>616</v>
+        <v>550</v>
       </c>
       <c r="I63" t="s">
         <v>694</v>
@@ -8964,28 +8963,28 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>673</v>
+        <v>613</v>
       </c>
       <c r="B64" t="s">
-        <v>674</v>
-      </c>
-      <c r="C64" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="2">
         <v>50</v>
       </c>
       <c r="G64" t="s">
-        <v>675</v>
+        <v>615</v>
       </c>
       <c r="H64" t="s">
-        <v>676</v>
+        <v>616</v>
       </c>
       <c r="I64" t="s">
         <v>694</v>
@@ -8996,28 +8995,28 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="B65" t="s">
-        <v>682</v>
-      </c>
-      <c r="C65" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="2">
         <v>50</v>
       </c>
       <c r="G65" t="s">
         <v>675</v>
       </c>
       <c r="H65" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="I65" t="s">
         <v>694</v>
@@ -9028,28 +9027,28 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>590</v>
+        <v>681</v>
       </c>
       <c r="B66" t="s">
-        <v>591</v>
-      </c>
-      <c r="C66" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="2">
         <v>50</v>
       </c>
       <c r="G66" t="s">
-        <v>584</v>
+        <v>675</v>
       </c>
       <c r="H66" t="s">
-        <v>592</v>
+        <v>683</v>
       </c>
       <c r="I66" t="s">
         <v>694</v>
@@ -9060,28 +9059,28 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B67" t="s">
-        <v>587</v>
-      </c>
-      <c r="C67" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="2">
         <v>50</v>
       </c>
       <c r="G67" t="s">
         <v>584</v>
       </c>
       <c r="H67" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="I67" t="s">
         <v>694</v>
@@ -9092,21 +9091,21 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B68" t="s">
-        <v>583</v>
-      </c>
-      <c r="C68" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="2">
         <v>50</v>
       </c>
       <c r="G68" t="s">
@@ -9124,21 +9123,21 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="B69" t="s">
-        <v>589</v>
-      </c>
-      <c r="C69" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69" s="2">
         <v>50</v>
       </c>
       <c r="G69" t="s">
@@ -9156,28 +9155,28 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B70" t="s">
-        <v>594</v>
-      </c>
-      <c r="C70" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="2">
         <v>50</v>
       </c>
       <c r="G70" t="s">
         <v>584</v>
       </c>
       <c r="H70" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="I70" t="s">
         <v>694</v>
@@ -9188,28 +9187,28 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>629</v>
+        <v>593</v>
       </c>
       <c r="B71" t="s">
-        <v>630</v>
-      </c>
-      <c r="C71" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="2">
         <v>50</v>
       </c>
       <c r="G71" t="s">
-        <v>619</v>
+        <v>584</v>
       </c>
       <c r="H71" t="s">
-        <v>631</v>
+        <v>592</v>
       </c>
       <c r="I71" t="s">
         <v>694</v>
@@ -9220,28 +9219,28 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B72" t="s">
-        <v>627</v>
-      </c>
-      <c r="C72" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="2">
         <v>50</v>
       </c>
       <c r="G72" t="s">
         <v>619</v>
       </c>
       <c r="H72" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I72" t="s">
         <v>694</v>
@@ -9252,28 +9251,28 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="B73" t="s">
-        <v>618</v>
-      </c>
-      <c r="C73" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73" s="2">
         <v>50</v>
       </c>
       <c r="G73" t="s">
         <v>619</v>
       </c>
       <c r="H73" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="I73" t="s">
         <v>694</v>
@@ -9284,28 +9283,28 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B74" t="s">
-        <v>625</v>
-      </c>
-      <c r="C74" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74" s="2">
         <v>50</v>
       </c>
       <c r="G74" t="s">
         <v>619</v>
       </c>
       <c r="H74" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="I74" t="s">
         <v>694</v>
@@ -9316,21 +9315,21 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B75" t="s">
-        <v>622</v>
-      </c>
-      <c r="C75" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75" s="2">
         <v>50</v>
       </c>
       <c r="G75" t="s">
@@ -9348,28 +9347,28 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>565</v>
+        <v>621</v>
       </c>
       <c r="B76" t="s">
-        <v>566</v>
-      </c>
-      <c r="C76" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76" s="2">
         <v>50</v>
       </c>
       <c r="G76" t="s">
-        <v>570</v>
+        <v>619</v>
       </c>
       <c r="H76" t="s">
-        <v>737</v>
+        <v>623</v>
       </c>
       <c r="I76" t="s">
         <v>694</v>
@@ -9380,28 +9379,28 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="B77" t="s">
-        <v>578</v>
-      </c>
-      <c r="C77" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="2">
         <v>50</v>
       </c>
       <c r="G77" t="s">
         <v>570</v>
       </c>
       <c r="H77" t="s">
-        <v>576</v>
+        <v>735</v>
       </c>
       <c r="I77" t="s">
         <v>694</v>
@@ -9412,21 +9411,21 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B78" t="s">
-        <v>575</v>
-      </c>
-      <c r="C78" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78" s="2">
         <v>50</v>
       </c>
       <c r="G78" t="s">
@@ -9444,28 +9443,28 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s">
-        <v>580</v>
-      </c>
-      <c r="C79" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E79" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79" s="2">
         <v>50</v>
       </c>
       <c r="G79" t="s">
         <v>570</v>
       </c>
       <c r="H79" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="I79" t="s">
         <v>694</v>
@@ -9476,28 +9475,28 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B80" t="s">
-        <v>572</v>
-      </c>
-      <c r="C80" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80" s="2">
         <v>50</v>
       </c>
       <c r="G80" t="s">
         <v>570</v>
       </c>
       <c r="H80" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="I80" t="s">
         <v>694</v>
@@ -9508,28 +9507,28 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>642</v>
+        <v>571</v>
       </c>
       <c r="B81" t="s">
-        <v>643</v>
-      </c>
-      <c r="C81" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="2">
         <v>50</v>
       </c>
       <c r="G81" t="s">
-        <v>644</v>
+        <v>570</v>
       </c>
       <c r="H81" t="s">
-        <v>645</v>
+        <v>573</v>
       </c>
       <c r="I81" t="s">
         <v>694</v>
@@ -9540,28 +9539,28 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B82" t="s">
-        <v>637</v>
-      </c>
-      <c r="C82" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E82" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82" s="2">
         <v>50</v>
       </c>
       <c r="G82" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="H82" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="I82" t="s">
         <v>694</v>
@@ -9572,21 +9571,21 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B83" t="s">
-        <v>633</v>
-      </c>
-      <c r="C83" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="2">
         <v>50</v>
       </c>
       <c r="G83" t="s">
@@ -9604,28 +9603,28 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="B84" t="s">
-        <v>611</v>
-      </c>
-      <c r="C84" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E84" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84" s="2">
         <v>50</v>
       </c>
       <c r="G84" t="s">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="H84" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="I84" t="s">
         <v>694</v>
@@ -9636,28 +9635,28 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s">
-        <v>607</v>
-      </c>
-      <c r="C85" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="2">
         <v>50</v>
       </c>
       <c r="G85" t="s">
         <v>608</v>
       </c>
       <c r="H85" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="I85" t="s">
         <v>694</v>
@@ -9668,28 +9667,28 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B86" t="s">
-        <v>603</v>
-      </c>
-      <c r="C86" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="E86" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86" s="2">
         <v>50</v>
       </c>
       <c r="G86" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="H86" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="I86" t="s">
         <v>694</v>
@@ -9700,28 +9699,28 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>638</v>
+        <v>602</v>
       </c>
       <c r="B87" t="s">
-        <v>639</v>
-      </c>
-      <c r="C87" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E87" s="4" t="s">
+      <c r="E87" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87" s="2">
         <v>50</v>
       </c>
       <c r="G87" t="s">
-        <v>640</v>
+        <v>604</v>
       </c>
       <c r="H87" t="s">
-        <v>641</v>
+        <v>605</v>
       </c>
       <c r="I87" t="s">
         <v>694</v>
@@ -9732,28 +9731,28 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s">
-        <v>655</v>
-      </c>
-      <c r="C88" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E88" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88" s="2">
         <v>50</v>
       </c>
       <c r="G88" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="H88" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="I88" t="s">
         <v>694</v>
@@ -9764,21 +9763,21 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B89" t="s">
-        <v>659</v>
-      </c>
-      <c r="C89" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="2">
         <v>50</v>
       </c>
       <c r="G89" t="s">
@@ -9796,28 +9795,28 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>600</v>
+        <v>658</v>
       </c>
       <c r="B90" t="s">
-        <v>601</v>
-      </c>
-      <c r="C90" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E90" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="2">
         <v>50</v>
       </c>
       <c r="G90" t="s">
-        <v>597</v>
+        <v>656</v>
       </c>
       <c r="H90" t="s">
-        <v>597</v>
+        <v>657</v>
       </c>
       <c r="I90" t="s">
         <v>694</v>
@@ -9828,21 +9827,21 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B91" t="s">
-        <v>596</v>
-      </c>
-      <c r="C91" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="2">
         <v>50</v>
       </c>
       <c r="G91" t="s">
@@ -9860,21 +9859,21 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B92" t="s">
-        <v>599</v>
-      </c>
-      <c r="C92" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="E92" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92" s="2">
         <v>50</v>
       </c>
       <c r="G92" t="s">
@@ -9892,28 +9891,28 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>663</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s">
-        <v>664</v>
-      </c>
-      <c r="C93" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E93" s="4" t="s">
+      <c r="E93" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93" s="2">
         <v>50</v>
       </c>
       <c r="G93" t="s">
-        <v>665</v>
+        <v>597</v>
       </c>
       <c r="H93" t="s">
-        <v>666</v>
+        <v>597</v>
       </c>
       <c r="I93" t="s">
         <v>694</v>
@@ -9924,28 +9923,28 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="B94" t="s">
-        <v>688</v>
-      </c>
-      <c r="C94" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E94" s="4" t="s">
+      <c r="E94" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="2">
         <v>50</v>
       </c>
       <c r="G94" t="s">
         <v>665</v>
       </c>
       <c r="H94" t="s">
-        <v>689</v>
+        <v>666</v>
       </c>
       <c r="I94" t="s">
         <v>694</v>
@@ -9956,28 +9955,28 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="B95" t="s">
-        <v>678</v>
-      </c>
-      <c r="C95" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="E95" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="2">
         <v>50</v>
       </c>
       <c r="G95" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="H95" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="I95" t="s">
         <v>694</v>
@@ -9988,28 +9987,28 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="B96" t="s">
-        <v>685</v>
-      </c>
-      <c r="C96" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E96" s="4" t="s">
+      <c r="E96" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="2">
         <v>50</v>
       </c>
       <c r="G96" t="s">
         <v>679</v>
       </c>
       <c r="H96" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="I96" t="s">
         <v>694</v>
@@ -10020,28 +10019,28 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="B97" t="s">
-        <v>668</v>
-      </c>
-      <c r="C97" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E97" s="4" t="s">
+      <c r="E97" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97" s="2">
         <v>50</v>
       </c>
       <c r="G97" t="s">
-        <v>537</v>
+        <v>679</v>
       </c>
       <c r="H97" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="I97" t="s">
         <v>694</v>
@@ -10052,28 +10051,28 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B98" t="s">
-        <v>671</v>
-      </c>
-      <c r="C98" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="E98" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98" s="2">
         <v>50</v>
       </c>
       <c r="G98" t="s">
         <v>537</v>
       </c>
       <c r="H98" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="I98" t="s">
         <v>694</v>
@@ -10084,28 +10083,28 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="B99" t="s">
-        <v>661</v>
-      </c>
-      <c r="C99" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E99" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="2">
         <v>50</v>
       </c>
       <c r="G99" t="s">
         <v>537</v>
       </c>
       <c r="H99" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="I99" t="s">
         <v>694</v>
@@ -10116,50 +10115,53 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>706</v>
+        <v>660</v>
       </c>
       <c r="B100" t="s">
-        <v>708</v>
-      </c>
-      <c r="C100" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E100" s="4" t="s">
+      <c r="E100" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="2">
         <v>50</v>
       </c>
       <c r="G100" t="s">
-        <v>648</v>
+        <v>537</v>
       </c>
       <c r="H100" t="s">
-        <v>710</v>
+        <v>662</v>
       </c>
       <c r="I100" t="s">
         <v>694</v>
+      </c>
+      <c r="J100" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B101" t="s">
-        <v>709</v>
-      </c>
-      <c r="C101" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E101" s="4" t="s">
+      <c r="E101" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="2">
         <v>50</v>
       </c>
       <c r="G101" t="s">
@@ -10174,21 +10176,21 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B102" t="s">
-        <v>704</v>
-      </c>
-      <c r="C102" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E102" s="4" t="s">
+      <c r="E102" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="2">
         <v>50</v>
       </c>
       <c r="G102" t="s">
@@ -10203,60 +10205,57 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>646</v>
+        <v>705</v>
       </c>
       <c r="B103" t="s">
-        <v>647</v>
-      </c>
-      <c r="C103" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E103" s="4" t="s">
+      <c r="E103" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103" s="2">
         <v>50</v>
       </c>
       <c r="G103" t="s">
         <v>648</v>
       </c>
       <c r="H103" t="s">
-        <v>649</v>
+        <v>710</v>
       </c>
       <c r="I103" t="s">
         <v>694</v>
-      </c>
-      <c r="J103" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B104" t="s">
-        <v>651</v>
-      </c>
-      <c r="C104" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E104" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104" s="2">
         <v>50</v>
       </c>
       <c r="G104" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="H104" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="I104" t="s">
         <v>694</v>
@@ -10267,114 +10266,117 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>561</v>
+        <v>650</v>
       </c>
       <c r="B105" t="s">
-        <v>562</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="F105" s="3">
+        <v>651</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F105" s="2">
         <v>50</v>
       </c>
       <c r="G105" t="s">
+        <v>652</v>
+      </c>
+      <c r="H105" t="s">
+        <v>653</v>
+      </c>
+      <c r="I105" t="s">
+        <v>694</v>
+      </c>
+      <c r="J105" t="s">
         <v>289</v>
-      </c>
-      <c r="H105" t="s">
-        <v>563</v>
-      </c>
-      <c r="I105" t="s">
-        <v>694</v>
-      </c>
-      <c r="J105" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s">
-        <v>558</v>
-      </c>
-      <c r="C106" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E106" s="4" t="s">
+      <c r="E106" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106" s="2">
         <v>50</v>
       </c>
       <c r="G106" t="s">
         <v>289</v>
       </c>
       <c r="H106" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="I106" t="s">
         <v>694</v>
       </c>
       <c r="J106" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>290</v>
+        <v>557</v>
       </c>
       <c r="B107" t="s">
-        <v>291</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="F107" s="3">
-        <v>60</v>
+        <v>558</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F107" s="2">
+        <v>50</v>
       </c>
       <c r="G107" t="s">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="H107" t="s">
-        <v>693</v>
+        <v>559</v>
       </c>
       <c r="I107" t="s">
         <v>694</v>
+      </c>
+      <c r="J107" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B108" t="s">
-        <v>293</v>
-      </c>
-      <c r="C108" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E108" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108" s="2">
         <v>60</v>
       </c>
       <c r="G108" t="s">
@@ -10389,21 +10391,21 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B109" t="s">
-        <v>295</v>
-      </c>
-      <c r="C109" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E109" s="4" t="s">
+      <c r="E109" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="2">
         <v>60</v>
       </c>
       <c r="G109" t="s">
@@ -10418,21 +10420,21 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B110" t="s">
-        <v>297</v>
-      </c>
-      <c r="C110" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="2">
         <v>60</v>
       </c>
       <c r="G110" t="s">
@@ -10447,21 +10449,21 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B111" t="s">
-        <v>299</v>
-      </c>
-      <c r="C111" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E111" s="4" t="s">
+      <c r="E111" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111" s="2">
         <v>60</v>
       </c>
       <c r="G111" t="s">
@@ -10476,21 +10478,21 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B112" t="s">
-        <v>301</v>
-      </c>
-      <c r="C112" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E112" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112" s="2">
         <v>60</v>
       </c>
       <c r="G112" t="s">
@@ -10505,21 +10507,21 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B113" t="s">
-        <v>303</v>
-      </c>
-      <c r="C113" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="E113" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113" s="2">
         <v>60</v>
       </c>
       <c r="G113" t="s">
@@ -10534,21 +10536,21 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B114" t="s">
-        <v>305</v>
-      </c>
-      <c r="C114" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E114" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="2">
         <v>60</v>
       </c>
       <c r="G114" t="s">
@@ -10563,21 +10565,21 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B115" t="s">
-        <v>307</v>
-      </c>
-      <c r="C115" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="E115" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="2">
         <v>60</v>
       </c>
       <c r="G115" t="s">
@@ -10592,21 +10594,21 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B116" t="s">
-        <v>309</v>
-      </c>
-      <c r="C116" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="E116" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="2">
         <v>60</v>
       </c>
       <c r="G116" t="s">
@@ -10621,21 +10623,21 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B117" t="s">
-        <v>311</v>
-      </c>
-      <c r="C117" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E117" s="4" t="s">
+      <c r="E117" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117" s="2">
         <v>60</v>
       </c>
       <c r="G117" t="s">
@@ -10650,21 +10652,21 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B118" t="s">
-        <v>313</v>
-      </c>
-      <c r="C118" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E118" s="4" t="s">
+      <c r="E118" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="2">
         <v>60</v>
       </c>
       <c r="G118" t="s">
@@ -10679,21 +10681,21 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B119" t="s">
-        <v>315</v>
-      </c>
-      <c r="C119" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E119" s="4" t="s">
+      <c r="E119" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="2">
         <v>60</v>
       </c>
       <c r="G119" t="s">
@@ -10708,21 +10710,21 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B120" t="s">
-        <v>317</v>
-      </c>
-      <c r="C120" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E120" s="4" t="s">
+      <c r="E120" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120" s="2">
         <v>60</v>
       </c>
       <c r="G120" t="s">
@@ -10737,21 +10739,21 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B121" t="s">
-        <v>319</v>
-      </c>
-      <c r="C121" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E121" s="4" t="s">
+      <c r="E121" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121" s="2">
         <v>60</v>
       </c>
       <c r="G121" t="s">
@@ -10766,21 +10768,21 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B122" t="s">
-        <v>321</v>
-      </c>
-      <c r="C122" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D122" s="3" t="s">
+      <c r="D122" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E122" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122" s="2">
         <v>60</v>
       </c>
       <c r="G122" t="s">
@@ -10795,21 +10797,21 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B123" t="s">
-        <v>323</v>
-      </c>
-      <c r="C123" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E123" s="4" t="s">
+      <c r="E123" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="2">
         <v>60</v>
       </c>
       <c r="G123" t="s">
@@ -10824,21 +10826,21 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B124" t="s">
-        <v>325</v>
-      </c>
-      <c r="C124" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D124" s="3" t="s">
+      <c r="D124" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="E124" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="2">
         <v>60</v>
       </c>
       <c r="G124" t="s">
@@ -10853,21 +10855,21 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B125" t="s">
-        <v>327</v>
-      </c>
-      <c r="C125" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E125" s="4" t="s">
+      <c r="E125" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125" s="2">
         <v>60</v>
       </c>
       <c r="G125" t="s">
@@ -10882,21 +10884,21 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B126" t="s">
-        <v>329</v>
-      </c>
-      <c r="C126" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E126" s="4" t="s">
+      <c r="E126" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126" s="2">
         <v>60</v>
       </c>
       <c r="G126" t="s">
@@ -10911,21 +10913,21 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B127" t="s">
-        <v>331</v>
-      </c>
-      <c r="C127" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E127" s="4" t="s">
+      <c r="E127" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="2">
         <v>60</v>
       </c>
       <c r="G127" t="s">
@@ -10940,21 +10942,21 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B128" t="s">
-        <v>333</v>
-      </c>
-      <c r="C128" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D128" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E128" s="4" t="s">
+      <c r="E128" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="2">
         <v>60</v>
       </c>
       <c r="G128" t="s">
@@ -10969,21 +10971,21 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B129" t="s">
-        <v>335</v>
-      </c>
-      <c r="C129" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D129" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E129" s="4" t="s">
+      <c r="E129" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="2">
         <v>60</v>
       </c>
       <c r="G129" t="s">
@@ -10998,21 +11000,21 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B130" t="s">
-        <v>337</v>
-      </c>
-      <c r="C130" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="D130" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="E130" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130" s="2">
         <v>60</v>
       </c>
       <c r="G130" t="s">
@@ -11027,21 +11029,21 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B131" t="s">
-        <v>339</v>
-      </c>
-      <c r="C131" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E131" s="4" t="s">
+      <c r="E131" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131" s="2">
         <v>60</v>
       </c>
       <c r="G131" t="s">
@@ -11056,21 +11058,21 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B132" t="s">
-        <v>341</v>
-      </c>
-      <c r="C132" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D132" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="E132" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="2">
         <v>60</v>
       </c>
       <c r="G132" t="s">
@@ -11085,21 +11087,21 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B133" t="s">
-        <v>343</v>
-      </c>
-      <c r="C133" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="D133" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E133" s="4" t="s">
+      <c r="E133" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="2">
         <v>60</v>
       </c>
       <c r="G133" t="s">
@@ -11114,21 +11116,21 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B134" t="s">
-        <v>345</v>
-      </c>
-      <c r="C134" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D134" s="3" t="s">
+      <c r="D134" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E134" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134" s="2">
         <v>60</v>
       </c>
       <c r="G134" t="s">
@@ -11143,21 +11145,21 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B135" t="s">
-        <v>347</v>
-      </c>
-      <c r="C135" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="D135" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="E135" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135" s="2">
         <v>60</v>
       </c>
       <c r="G135" t="s">
@@ -11172,21 +11174,21 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B136" t="s">
-        <v>349</v>
-      </c>
-      <c r="C136" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="D136" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E136" s="4" t="s">
+      <c r="E136" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="2">
         <v>60</v>
       </c>
       <c r="G136" t="s">
@@ -11201,21 +11203,21 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B137" t="s">
-        <v>351</v>
-      </c>
-      <c r="C137" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D137" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E137" s="4" t="s">
+      <c r="E137" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137" s="2">
         <v>60</v>
       </c>
       <c r="G137" t="s">
@@ -11230,21 +11232,21 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B138" t="s">
-        <v>353</v>
-      </c>
-      <c r="C138" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D138" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E138" s="4" t="s">
+      <c r="E138" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138" s="2">
         <v>60</v>
       </c>
       <c r="G138" t="s">
@@ -11259,21 +11261,21 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B139" t="s">
-        <v>355</v>
-      </c>
-      <c r="C139" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E139" s="4" t="s">
+      <c r="E139" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139" s="2">
         <v>60</v>
       </c>
       <c r="G139" t="s">
@@ -11288,21 +11290,21 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B140" t="s">
-        <v>357</v>
-      </c>
-      <c r="C140" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D140" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E140" s="4" t="s">
+      <c r="E140" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140" s="2">
         <v>60</v>
       </c>
       <c r="G140" t="s">
@@ -11317,21 +11319,21 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B141" t="s">
-        <v>359</v>
-      </c>
-      <c r="C141" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D141" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E141" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141" s="2">
         <v>60</v>
       </c>
       <c r="G141" t="s">
@@ -11346,21 +11348,21 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B142" t="s">
-        <v>361</v>
-      </c>
-      <c r="C142" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="D142" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E142" s="4" t="s">
+      <c r="E142" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142" s="2">
         <v>60</v>
       </c>
       <c r="G142" t="s">
@@ -11375,21 +11377,21 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B143" t="s">
-        <v>363</v>
-      </c>
-      <c r="C143" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E143" s="4" t="s">
+      <c r="E143" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143" s="2">
         <v>60</v>
       </c>
       <c r="G143" t="s">
@@ -11404,21 +11406,21 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B144" t="s">
-        <v>365</v>
-      </c>
-      <c r="C144" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D144" s="3" t="s">
+      <c r="D144" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E144" s="4" t="s">
+      <c r="E144" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144" s="2">
         <v>60</v>
       </c>
       <c r="G144" t="s">
@@ -11433,21 +11435,21 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B145" t="s">
-        <v>367</v>
-      </c>
-      <c r="C145" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="D145" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E145" s="4" t="s">
+      <c r="E145" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F145" s="3">
+      <c r="F145" s="2">
         <v>60</v>
       </c>
       <c r="G145" t="s">
@@ -11462,21 +11464,21 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B146" t="s">
-        <v>369</v>
-      </c>
-      <c r="C146" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="D146" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E146" s="4" t="s">
+      <c r="E146" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="2">
         <v>60</v>
       </c>
       <c r="G146" t="s">
@@ -11491,21 +11493,21 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B147" t="s">
-        <v>371</v>
-      </c>
-      <c r="C147" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="D147" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E147" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="2">
         <v>60</v>
       </c>
       <c r="G147" t="s">
@@ -11520,21 +11522,21 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B148" t="s">
-        <v>373</v>
-      </c>
-      <c r="C148" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D148" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E148" s="4" t="s">
+      <c r="E148" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148" s="2">
         <v>60</v>
       </c>
       <c r="G148" t="s">
@@ -11549,21 +11551,21 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B149" t="s">
-        <v>375</v>
-      </c>
-      <c r="C149" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E149" s="4" t="s">
+      <c r="E149" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149" s="2">
         <v>60</v>
       </c>
       <c r="G149" t="s">
@@ -11578,21 +11580,21 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B150" t="s">
-        <v>377</v>
-      </c>
-      <c r="C150" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D150" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E150" s="4" t="s">
+      <c r="E150" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F150" s="2">
         <v>60</v>
       </c>
       <c r="G150" t="s">
@@ -11607,21 +11609,21 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B151" t="s">
-        <v>379</v>
-      </c>
-      <c r="C151" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="D151" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="E151" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151" s="2">
         <v>60</v>
       </c>
       <c r="G151" t="s">
@@ -11636,21 +11638,21 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B152" t="s">
-        <v>381</v>
-      </c>
-      <c r="C152" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="D152" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E152" s="4" t="s">
+      <c r="E152" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F152" s="3">
+      <c r="F152" s="2">
         <v>60</v>
       </c>
       <c r="G152" t="s">
@@ -11665,21 +11667,21 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B153" t="s">
-        <v>383</v>
-      </c>
-      <c r="C153" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E153" s="4" t="s">
+      <c r="E153" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153" s="2">
         <v>60</v>
       </c>
       <c r="G153" t="s">
@@ -11694,21 +11696,21 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B154" t="s">
-        <v>385</v>
-      </c>
-      <c r="C154" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="D154" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="E154" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154" s="2">
         <v>60</v>
       </c>
       <c r="G154" t="s">
@@ -11723,21 +11725,21 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B155" t="s">
-        <v>387</v>
-      </c>
-      <c r="C155" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D155" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F155" s="3">
+      <c r="F155" s="2">
         <v>60</v>
       </c>
       <c r="G155" t="s">
@@ -11752,21 +11754,21 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B156" t="s">
-        <v>389</v>
-      </c>
-      <c r="C156" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D156" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E156" s="4" t="s">
+      <c r="E156" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F156" s="3">
+      <c r="F156" s="2">
         <v>60</v>
       </c>
       <c r="G156" t="s">
@@ -11781,21 +11783,21 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B157" t="s">
-        <v>391</v>
-      </c>
-      <c r="C157" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E157" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F157" s="3">
+      <c r="F157" s="2">
         <v>60</v>
       </c>
       <c r="G157" t="s">
@@ -11810,21 +11812,21 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B158" t="s">
-        <v>393</v>
-      </c>
-      <c r="C158" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E158" s="4" t="s">
+      <c r="E158" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F158" s="3">
+      <c r="F158" s="2">
         <v>60</v>
       </c>
       <c r="G158" t="s">
@@ -11839,21 +11841,21 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B159" t="s">
-        <v>395</v>
-      </c>
-      <c r="C159" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E159" s="4" t="s">
+      <c r="E159" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159" s="2">
         <v>60</v>
       </c>
       <c r="G159" t="s">
@@ -11868,21 +11870,21 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B160" t="s">
-        <v>397</v>
-      </c>
-      <c r="C160" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E160" s="4" t="s">
+      <c r="E160" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F160" s="3">
+      <c r="F160" s="2">
         <v>60</v>
       </c>
       <c r="G160" t="s">
@@ -11897,21 +11899,21 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B161" t="s">
-        <v>399</v>
-      </c>
-      <c r="C161" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E161" s="4" t="s">
+      <c r="E161" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F161" s="3">
+      <c r="F161" s="2">
         <v>60</v>
       </c>
       <c r="G161" t="s">
@@ -11926,21 +11928,21 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B162" t="s">
-        <v>401</v>
-      </c>
-      <c r="C162" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="D162" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E162" s="4" t="s">
+      <c r="E162" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162" s="2">
         <v>60</v>
       </c>
       <c r="G162" t="s">
@@ -11955,21 +11957,21 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B163" t="s">
-        <v>403</v>
-      </c>
-      <c r="C163" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D163" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E163" s="4" t="s">
+      <c r="E163" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163" s="2">
         <v>60</v>
       </c>
       <c r="G163" t="s">
@@ -11984,21 +11986,21 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B164" t="s">
-        <v>405</v>
-      </c>
-      <c r="C164" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="D164" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E164" s="4" t="s">
+      <c r="E164" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164" s="2">
         <v>60</v>
       </c>
       <c r="G164" t="s">
@@ -12013,21 +12015,21 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B165" t="s">
-        <v>407</v>
-      </c>
-      <c r="C165" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D165" s="3" t="s">
+      <c r="D165" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E165" s="4" t="s">
+      <c r="E165" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165" s="2">
         <v>60</v>
       </c>
       <c r="G165" t="s">
@@ -12042,21 +12044,21 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B166" t="s">
-        <v>409</v>
-      </c>
-      <c r="C166" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D166" s="3" t="s">
+      <c r="D166" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E166" s="4" t="s">
+      <c r="E166" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F166" s="3">
+      <c r="F166" s="2">
         <v>60</v>
       </c>
       <c r="G166" t="s">
@@ -12071,21 +12073,21 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B167" t="s">
-        <v>411</v>
-      </c>
-      <c r="C167" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D167" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E167" s="4" t="s">
+      <c r="E167" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F167" s="3">
+      <c r="F167" s="2">
         <v>60</v>
       </c>
       <c r="G167" t="s">
@@ -12100,21 +12102,21 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B168" t="s">
-        <v>413</v>
-      </c>
-      <c r="C168" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D168" s="3" t="s">
+      <c r="D168" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E168" s="4" t="s">
+      <c r="E168" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F168" s="3">
+      <c r="F168" s="2">
         <v>60</v>
       </c>
       <c r="G168" t="s">
@@ -12129,21 +12131,21 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B169" t="s">
-        <v>415</v>
-      </c>
-      <c r="C169" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D169" s="3" t="s">
+      <c r="D169" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E169" s="4" t="s">
+      <c r="E169" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F169" s="3">
+      <c r="F169" s="2">
         <v>60</v>
       </c>
       <c r="G169" t="s">
@@ -12158,21 +12160,21 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B170" t="s">
-        <v>417</v>
-      </c>
-      <c r="C170" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D170" s="3" t="s">
+      <c r="D170" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E170" s="4" t="s">
+      <c r="E170" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F170" s="3">
+      <c r="F170" s="2">
         <v>60</v>
       </c>
       <c r="G170" t="s">
@@ -12187,21 +12189,21 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B171" t="s">
-        <v>419</v>
-      </c>
-      <c r="C171" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D171" s="3" t="s">
+      <c r="D171" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E171" s="4" t="s">
+      <c r="E171" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F171" s="3">
+      <c r="F171" s="2">
         <v>60</v>
       </c>
       <c r="G171" t="s">
@@ -12216,21 +12218,21 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B172" t="s">
-        <v>421</v>
-      </c>
-      <c r="C172" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D172" s="3" t="s">
+      <c r="D172" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E172" s="4" t="s">
+      <c r="E172" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F172" s="3">
+      <c r="F172" s="2">
         <v>60</v>
       </c>
       <c r="G172" t="s">
@@ -12245,21 +12247,21 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B173" t="s">
-        <v>423</v>
-      </c>
-      <c r="C173" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D173" s="3" t="s">
+      <c r="D173" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E173" s="4" t="s">
+      <c r="E173" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F173" s="3">
+      <c r="F173" s="2">
         <v>60</v>
       </c>
       <c r="G173" t="s">
@@ -12274,21 +12276,21 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B174" t="s">
-        <v>425</v>
-      </c>
-      <c r="C174" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D174" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E174" s="4" t="s">
+      <c r="E174" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F174" s="3">
+      <c r="F174" s="2">
         <v>60</v>
       </c>
       <c r="G174" t="s">
@@ -12303,21 +12305,21 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B175" t="s">
-        <v>427</v>
-      </c>
-      <c r="C175" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D175" s="3" t="s">
+      <c r="D175" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E175" s="4" t="s">
+      <c r="E175" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F175" s="3">
+      <c r="F175" s="2">
         <v>60</v>
       </c>
       <c r="G175" t="s">
@@ -12332,21 +12334,21 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B176" t="s">
-        <v>429</v>
-      </c>
-      <c r="C176" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D176" s="3" t="s">
+      <c r="D176" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E176" s="4" t="s">
+      <c r="E176" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F176" s="3">
+      <c r="F176" s="2">
         <v>60</v>
       </c>
       <c r="G176" t="s">
@@ -12361,21 +12363,21 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B177" t="s">
-        <v>431</v>
-      </c>
-      <c r="C177" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="D177" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E177" s="4" t="s">
+      <c r="E177" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F177" s="3">
+      <c r="F177" s="2">
         <v>60</v>
       </c>
       <c r="G177" t="s">
@@ -12390,21 +12392,21 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B178" t="s">
-        <v>433</v>
-      </c>
-      <c r="C178" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D178" s="3" t="s">
+      <c r="D178" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E178" s="4" t="s">
+      <c r="E178" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F178" s="3">
+      <c r="F178" s="2">
         <v>60</v>
       </c>
       <c r="G178" t="s">
@@ -12419,21 +12421,21 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B179" t="s">
-        <v>435</v>
-      </c>
-      <c r="C179" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D179" s="3" t="s">
+      <c r="D179" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E179" s="4" t="s">
+      <c r="E179" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F179" s="3">
+      <c r="F179" s="2">
         <v>60</v>
       </c>
       <c r="G179" t="s">
@@ -12448,21 +12450,21 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B180" t="s">
-        <v>437</v>
-      </c>
-      <c r="C180" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D180" s="3" t="s">
+      <c r="D180" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E180" s="4" t="s">
+      <c r="E180" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F180" s="3">
+      <c r="F180" s="2">
         <v>60</v>
       </c>
       <c r="G180" t="s">
@@ -12477,21 +12479,21 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B181" t="s">
-        <v>439</v>
-      </c>
-      <c r="C181" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D181" s="3" t="s">
+      <c r="D181" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="E181" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F181" s="3">
+      <c r="F181" s="2">
         <v>60</v>
       </c>
       <c r="G181" t="s">
@@ -12506,21 +12508,21 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B182" t="s">
-        <v>441</v>
-      </c>
-      <c r="C182" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D182" s="3" t="s">
+      <c r="D182" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E182" s="4" t="s">
+      <c r="E182" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F182" s="3">
+      <c r="F182" s="2">
         <v>60</v>
       </c>
       <c r="G182" t="s">
@@ -12535,21 +12537,21 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B183" t="s">
-        <v>443</v>
-      </c>
-      <c r="C183" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D183" s="3" t="s">
+      <c r="D183" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E183" s="4" t="s">
+      <c r="E183" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F183" s="3">
+      <c r="F183" s="2">
         <v>60</v>
       </c>
       <c r="G183" t="s">
@@ -12564,21 +12566,21 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B184" t="s">
-        <v>445</v>
-      </c>
-      <c r="C184" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D184" s="3" t="s">
+      <c r="D184" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E184" s="4" t="s">
+      <c r="E184" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F184" s="3">
+      <c r="F184" s="2">
         <v>60</v>
       </c>
       <c r="G184" t="s">
@@ -12593,21 +12595,21 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B185" t="s">
-        <v>447</v>
-      </c>
-      <c r="C185" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D185" s="3" t="s">
+      <c r="D185" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E185" s="4" t="s">
+      <c r="E185" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F185" s="3">
+      <c r="F185" s="2">
         <v>60</v>
       </c>
       <c r="G185" t="s">
@@ -12622,21 +12624,21 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B186" t="s">
-        <v>449</v>
-      </c>
-      <c r="C186" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D186" s="3" t="s">
+      <c r="D186" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E186" s="4" t="s">
+      <c r="E186" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F186" s="3">
+      <c r="F186" s="2">
         <v>60</v>
       </c>
       <c r="G186" t="s">
@@ -12651,21 +12653,21 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B187" t="s">
-        <v>451</v>
-      </c>
-      <c r="C187" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D187" s="3" t="s">
+      <c r="D187" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E187" s="4" t="s">
+      <c r="E187" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F187" s="3">
+      <c r="F187" s="2">
         <v>60</v>
       </c>
       <c r="G187" t="s">
@@ -12680,21 +12682,21 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B188" t="s">
-        <v>453</v>
-      </c>
-      <c r="C188" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D188" s="3" t="s">
+      <c r="D188" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E188" s="4" t="s">
+      <c r="E188" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F188" s="3">
+      <c r="F188" s="2">
         <v>60</v>
       </c>
       <c r="G188" t="s">
@@ -12709,21 +12711,21 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B189" t="s">
-        <v>455</v>
-      </c>
-      <c r="C189" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D189" s="3" t="s">
+      <c r="D189" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E189" s="4" t="s">
+      <c r="E189" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F189" s="3">
+      <c r="F189" s="2">
         <v>60</v>
       </c>
       <c r="G189" t="s">
@@ -12738,21 +12740,21 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B190" t="s">
-        <v>457</v>
-      </c>
-      <c r="C190" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D190" s="3" t="s">
+      <c r="D190" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E190" s="4" t="s">
+      <c r="E190" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F190" s="3">
+      <c r="F190" s="2">
         <v>60</v>
       </c>
       <c r="G190" t="s">
@@ -12767,21 +12769,21 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B191" t="s">
-        <v>459</v>
-      </c>
-      <c r="C191" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D191" s="3" t="s">
+      <c r="D191" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E191" s="4" t="s">
+      <c r="E191" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F191" s="3">
+      <c r="F191" s="2">
         <v>60</v>
       </c>
       <c r="G191" t="s">
@@ -12796,21 +12798,21 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B192" t="s">
-        <v>461</v>
-      </c>
-      <c r="C192" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D192" s="3" t="s">
+      <c r="D192" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E192" s="4" t="s">
+      <c r="E192" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F192" s="3">
+      <c r="F192" s="2">
         <v>60</v>
       </c>
       <c r="G192" t="s">
@@ -12825,21 +12827,21 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B193" t="s">
-        <v>463</v>
-      </c>
-      <c r="C193" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D193" s="3" t="s">
+      <c r="D193" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E193" s="4" t="s">
+      <c r="E193" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F193" s="3">
+      <c r="F193" s="2">
         <v>60</v>
       </c>
       <c r="G193" t="s">
@@ -12854,21 +12856,21 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B194" t="s">
-        <v>465</v>
-      </c>
-      <c r="C194" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D194" s="3" t="s">
+      <c r="D194" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E194" s="4" t="s">
+      <c r="E194" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F194" s="3">
+      <c r="F194" s="2">
         <v>60</v>
       </c>
       <c r="G194" t="s">
@@ -12883,21 +12885,21 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B195" t="s">
-        <v>467</v>
-      </c>
-      <c r="C195" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D195" s="3" t="s">
+      <c r="D195" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E195" s="4" t="s">
+      <c r="E195" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F195" s="3">
+      <c r="F195" s="2">
         <v>60</v>
       </c>
       <c r="G195" t="s">
@@ -12912,21 +12914,21 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B196" t="s">
-        <v>469</v>
-      </c>
-      <c r="C196" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D196" s="3" t="s">
+      <c r="D196" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E196" s="4" t="s">
+      <c r="E196" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F196" s="3">
+      <c r="F196" s="2">
         <v>60</v>
       </c>
       <c r="G196" t="s">
@@ -12941,21 +12943,21 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B197" t="s">
-        <v>471</v>
-      </c>
-      <c r="C197" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="D197" s="3" t="s">
+      <c r="D197" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="E197" s="4" t="s">
+      <c r="E197" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F197" s="3">
+      <c r="F197" s="2">
         <v>60</v>
       </c>
       <c r="G197" t="s">
@@ -12965,6 +12967,35 @@
         <v>693</v>
       </c>
       <c r="I197" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>470</v>
+      </c>
+      <c r="B198" t="s">
+        <v>471</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F198" s="2">
+        <v>60</v>
+      </c>
+      <c r="G198" t="s">
+        <v>472</v>
+      </c>
+      <c r="H198" t="s">
+        <v>693</v>
+      </c>
+      <c r="I198" t="s">
         <v>694</v>
       </c>
     </row>

--- a/Support/links_documents_EXCEL.xlsx
+++ b/Support/links_documents_EXCEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://msss365-my.sharepoint.com/personal/vincent_desrochers_med_ssss_gouv_qc_ca/Documents/Programmation/Git-Hub/emtools/Support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="8_{9B365C08-431E-40CE-980D-9CE06A7F3745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE4248E4-709E-42EA-9A5F-767D025135C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D7C9706-0417-41AB-B8CA-A13D00566971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5A9E7570-B546-46BC-9B1E-C8C8D4DF09A1}"/>
   </bookViews>
@@ -20,9 +20,22 @@
   </sheets>
   <definedNames>
     <definedName name="DonnéesExternes_1" localSheetId="1" hidden="1">'links (2)'!$A$1:$E$92</definedName>
-    <definedName name="DonnéesExternes_1" localSheetId="2" hidden="1">links_documents_csv!$A$1:$J$198</definedName>
+    <definedName name="DonnéesExternes_1" localSheetId="2" hidden="1">links_documents_csv!$A$1:$J$229</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -38,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="941">
   <si>
     <t>link_text,url,source_page,link_type,collected_at</t>
   </si>
@@ -2155,24 +2168,12 @@
     <t>https://www.chumontreal.qc.ca/sites/default/files/2022-08/239-4-Prevenir-et-traiter-incontinence-urinaire-chez-homme.pdf</t>
   </si>
   <si>
-    <t>Incontinence urinaire chez l'homme - CHUM</t>
-  </si>
-  <si>
-    <t>Incontinence urinaire chez la femme - CHUM</t>
-  </si>
-  <si>
-    <t>Incontinence urinaire chez la personne âgée - CHUM</t>
-  </si>
-  <si>
     <t>https://www.chumontreal.qc.ca/sites/default/files/2022-08/133-4-Prevenir-et-traiter-incontinence-urinaire-femme.pdf</t>
   </si>
   <si>
     <t>https://www.chumontreal.qc.ca/sites/default/files/2022-12/566-2-incontinence-urinaire-chez-la-personne-ainee-exercices-et-traitements.pdf</t>
   </si>
   <si>
-    <t>Incontinence, urinaire, vessie</t>
-  </si>
-  <si>
     <t>https://bibliotheques.cissslaval.ca/GEIDEFile/61-040-103_Otite_Moyenne_Aigue_(OMA)_conge_(2022-01-18).pdf?Archive=113169193134&amp;File=61%5F040%5F103%5Fotite%5FMoyenne%5Faigue%5F%28oMa%29%5Fconge%5F%282022%5F01%5F18%29%5Fpdf</t>
   </si>
   <si>
@@ -2552,6 +2553,327 @@
   </si>
   <si>
     <t>https://bibliotheques.cissslaval.ca/GEIDEFile/62-200-010_Ord_Insuline_IV_2021-08-18.pdf?Archive=115350293353&amp;File=62%5F200%5F010%5Ford%5Finsuline%5FiV%5F2021%5F08%5F18%5Fpdf</t>
+  </si>
+  <si>
+    <t>Paralysie de Bell</t>
+  </si>
+  <si>
+    <t>Bell, paralysie, fiche patient, info, patient</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2025-09/1150-1-paralysie-de-Bell.pdf</t>
+  </si>
+  <si>
+    <t>Soins de la bouche</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2025-12/1263-1-garder-sa-bouche-en-sante.pdf</t>
+  </si>
+  <si>
+    <t>Bouche, dents, dentiers, soins de bouche, haleine</t>
+  </si>
+  <si>
+    <t>Prendre soins des cicatrices</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2021-09/137-3-prendre-soin-de-mes-cicatrices-par-le-massage.pdf</t>
+  </si>
+  <si>
+    <t>Cicatrice, massage, adhérence, soins de peau, peau, plaie</t>
+  </si>
+  <si>
+    <t>Hygiène nasale - Adulte</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2024-01/1126-1-hygiene-nasale.pdf</t>
+  </si>
+  <si>
+    <t>Nez, nasale, sinus, rince</t>
+  </si>
+  <si>
+    <t>Épistaxis</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2026-03/1305-1-quoi-faire-quand-on-saigne%20du%20nez-arreter-une-epistaxis.pdf</t>
+  </si>
+  <si>
+    <t>Saignement, nez, épistaxis</t>
+  </si>
+  <si>
+    <t>Prendre soins de mon plâtre</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2021-11/52-4-prendre-soin-de-mon-membre-platre.pdf</t>
+  </si>
+  <si>
+    <t>Plâtre, platre, attelle, fracture, soins, orthopédie, orthopedie</t>
+  </si>
+  <si>
+    <t>Soins post-sédation</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2023-03/15_4_4005013_retour_a_la_maison_apres_26_fin_2022-11-30.pdf</t>
+  </si>
+  <si>
+    <t>Sédation, sedation, analgésie, analgesie, soins post</t>
+  </si>
+  <si>
+    <t>Précaution post-sevrage</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-04/259-3-retour-a-la-maison-apres-un-sevrage.pdf</t>
+  </si>
+  <si>
+    <t>Sevrage, alcool, conduite, convulsion</t>
+  </si>
+  <si>
+    <t>Soins de sonde</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-02/407-2-prendre-soins-d-une-sonde-dans-la-vessie.pdf</t>
+  </si>
+  <si>
+    <t>Sonde, soins, vésicale, vesicale, cathéter, catheter</t>
+  </si>
+  <si>
+    <t>Fiche patients CHUM</t>
+  </si>
+  <si>
+    <t>Pierres aux reins</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-10/638-1-pierres-aux-reins-calculs-renaux.pdf</t>
+  </si>
+  <si>
+    <t>Pierre, lithiases, reins, colique, néphrétique, nephretique</t>
+  </si>
+  <si>
+    <t>Rhizarthrose</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2025-08/1184-la-rhizarthrose.pdf</t>
+  </si>
+  <si>
+    <t>Pouce, douleur, arthrose, rizarthrose, rhizarthrose</t>
+  </si>
+  <si>
+    <t>Sécheresse vaginale</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-09/934-1-la-secheresse-vaginale.pdf</t>
+  </si>
+  <si>
+    <t>Sécheresse, secheresse, vaginisme, vaginale, ménopause, menopause</t>
+  </si>
+  <si>
+    <t>Sinusite chronique</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2024-01/1127-1-sinusite-chronique.pdf</t>
+  </si>
+  <si>
+    <t>Sinusite, chronique, sinus</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-08/99-3-acouphenes.pdf</t>
+  </si>
+  <si>
+    <t>Acouphène</t>
+  </si>
+  <si>
+    <t>Acouphene, oreille, son, ORL, audiologiste</t>
+  </si>
+  <si>
+    <t>Allergie à la pénicilline</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2023-02/1023-1-allergie-a-la-penicilline.pdf</t>
+  </si>
+  <si>
+    <t>Penicilline, allergie, provocation, allergologie</t>
+  </si>
+  <si>
+    <t>Anémie</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-09/814-1-anemie.pdf</t>
+  </si>
+  <si>
+    <t>Anemie, sang, fer, alimentation</t>
+  </si>
+  <si>
+    <t>Prurit anal</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2024-01/858-1-demangeaisons-a-l-anus-ou-prurit-anal.pdf</t>
+  </si>
+  <si>
+    <t>Demangeaison, démangeaison, anus, anal, prurit</t>
+  </si>
+  <si>
+    <t>Fissure anale</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-09/715-1-coupure-a-l-anus.pdf</t>
+  </si>
+  <si>
+    <t>Fissure, anale, anus, coupure, constipation</t>
+  </si>
+  <si>
+    <t>Hypotension orthostatique</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-08/506-1-la-baisse-de-pression-quand-on-se-leve-hypotension-orthostatique.pdf</t>
+  </si>
+  <si>
+    <t>HTO, hypotension, orthostatique, chute de pression, syncope</t>
+  </si>
+  <si>
+    <t>Céphalée médicamenteuse</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-01/109-3-cephalee-medicamenteuse.pdf</t>
+  </si>
+  <si>
+    <t>Céphalée, cephalee, tête, tete, migraine, médicaments, medicaments</t>
+  </si>
+  <si>
+    <t>Coliques néphrétiques</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2023-08/639-1-Colique-nephretique.pdf</t>
+  </si>
+  <si>
+    <t>Coliques, nephretique, rein, lithiase, pierres</t>
+  </si>
+  <si>
+    <t>Constipation</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-12/326-3-des_moyens_pour_combattre_la_constipation_0.pdf</t>
+  </si>
+  <si>
+    <t>Diverticulite</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2023-11/994-1-diverticulite.pdf</t>
+  </si>
+  <si>
+    <t>Diverticulite, abdominale, douleur, alimentation</t>
+  </si>
+  <si>
+    <t>Constipation, selles, alimentation</t>
+  </si>
+  <si>
+    <t>Douleur chroniques</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-07/505-1-vivre-avec-une-douleur-chronique.pdf</t>
+  </si>
+  <si>
+    <t>Douleur, chronique</t>
+  </si>
+  <si>
+    <t>Douleur à la vulve</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-12/186-3-les-douleurs-a-la-vulve-au-perinee-et-au-vagin.pdf</t>
+  </si>
+  <si>
+    <t>Vulvodynie, perine, périné, douleur, vagin, menopause, femme</t>
+  </si>
+  <si>
+    <t>Hématurie macroscopique</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2023-03/1063-1-avoir-du-sang-dans-les-urines-l-hematurie-macroscopique.pdf</t>
+  </si>
+  <si>
+    <t>Hematurie, sang, urine, rein, uro</t>
+  </si>
+  <si>
+    <t>Hernie discale</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-01/424-2-hernie-discale.pdf</t>
+  </si>
+  <si>
+    <t>Hernie, discale, dos, dorsalgie, cervicalgie</t>
+  </si>
+  <si>
+    <t>Incontinence urinaire - Femme</t>
+  </si>
+  <si>
+    <t>Incontinence, urinaire, femme</t>
+  </si>
+  <si>
+    <t>Incontinence urinaire - Personnes âgées</t>
+  </si>
+  <si>
+    <t>Exercices, incontinence, agee, urinaire, urine</t>
+  </si>
+  <si>
+    <t>Incontinence urinaire - Hommes</t>
+  </si>
+  <si>
+    <t>Incontinence, urinaire, homme</t>
+  </si>
+  <si>
+    <t>Cellulite infectieuse</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2022-03/399-2-soigner-une-infection-de-la-peau-cellulite-infectieuse_0.pdf</t>
+  </si>
+  <si>
+    <t>Cellulite, infection, peau</t>
+  </si>
+  <si>
+    <t>Insomnie</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2021-09/229-2-insomnie.pdf</t>
+  </si>
+  <si>
+    <t>Insomnie, sommeil</t>
+  </si>
+  <si>
+    <t>Douleur dorsale - Exercices</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-09/867-1-avoir-un-dos-en-bonne-sante-grace-a-l-activite-physique.pdf</t>
+  </si>
+  <si>
+    <t>Dorsalgie, lombalgie, douleur, dos, exercices</t>
+  </si>
+  <si>
+    <t>Prévenir la migraine</t>
+  </si>
+  <si>
+    <t>https://www.chumontreal.qc.ca/sites/default/files/2020-01/116-3-migraine-reduire-les-crises-par-vos-habuitudes-de-vie.pdf</t>
+  </si>
+  <si>
+    <t>Prevention, migraine, céphalée, cephalee</t>
+  </si>
+  <si>
+    <t>Aucun changements</t>
+  </si>
+  <si>
+    <t>Contient info clinique CHUM</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>Lien</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>Colonne1</t>
+  </si>
+  <si>
+    <t>Prescription</t>
   </si>
 </sst>
 </file>
@@ -2700,7 +3022,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2880,6 +3202,18 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -3041,7 +3375,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3050,7 +3384,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3096,9 +3437,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="16">
     <dxf>
-      <numFmt numFmtId="27" formatCode="yyyy/mm/dd\ hh:mm"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3111,6 +3460,11 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3119,22 +3473,21 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="yyyy/mm/dd\ hh:mm"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3171,8 +3524,8 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="DonnéesExternes_1" connectionId="2" xr16:uid="{0D63BF91-B9F6-47E6-873A-B89479D69DFF}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="601">
-    <queryTableFields count="10">
+  <queryTableRefresh nextId="603" unboundColumnsRight="1">
+    <queryTableFields count="11">
       <queryTableField id="1" name="title" tableColumnId="1"/>
       <queryTableField id="2" name="href" tableColumnId="2"/>
       <queryTableField id="3" name="section" tableColumnId="3"/>
@@ -3183,6 +3536,7 @@
       <queryTableField id="8" name="tags" tableColumnId="8"/>
       <queryTableField id="9" name="targetBlank" tableColumnId="9"/>
       <queryTableField id="10" name="description" tableColumnId="10"/>
+      <queryTableField id="602" dataBound="0" tableColumnId="11"/>
     </queryTableFields>
     <queryTableDeletedFields count="590">
       <deletedField name="title2"/>
@@ -3784,39 +4138,53 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DE1A692-D182-48B1-AF24-B08C3BADDDB7}" name="links" displayName="links" ref="A1:E92" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E92" xr:uid="{6DE1A692-D182-48B1-AF24-B08C3BADDDB7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8BEA4C21-4044-4079-9E1A-527E856DC298}" uniqueName="1" name="link_text" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{7C65E6FF-1686-4FDD-96F3-2AD9E0FDF1F8}" uniqueName="2" name="url" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{18BB0FCF-509C-47E0-A822-E32F6857A439}" uniqueName="3" name="source_page" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{4A776295-DFD0-4A4F-A121-D0FF62704E6D}" uniqueName="4" name="link_type" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{1C6E3148-D1F4-4F60-8957-153FC9DBB625}" uniqueName="5" name="collected_at" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8BEA4C21-4044-4079-9E1A-527E856DC298}" uniqueName="1" name="link_text" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{7C65E6FF-1686-4FDD-96F3-2AD9E0FDF1F8}" uniqueName="2" name="url" queryTableFieldId="2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{18BB0FCF-509C-47E0-A822-E32F6857A439}" uniqueName="3" name="source_page" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{4A776295-DFD0-4A4F-A121-D0FF62704E6D}" uniqueName="4" name="link_type" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{1C6E3148-D1F4-4F60-8957-153FC9DBB625}" uniqueName="5" name="collected_at" queryTableFieldId="5" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}" name="links_documents" displayName="links_documents" ref="A1:J198" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:J198" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J198">
-    <sortCondition ref="F2:F198"/>
-    <sortCondition ref="E2:E198"/>
-    <sortCondition ref="C2:C198"/>
-    <sortCondition ref="G2:G198"/>
-    <sortCondition ref="A2:A198"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}" name="links_documents" displayName="links_documents" ref="A1:K229" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:K229" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J229">
+    <sortCondition ref="F2:F229"/>
+    <sortCondition ref="E2:E229"/>
+    <sortCondition ref="A2:A229"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{487E3CF9-4E9F-41C4-A553-12FE09D4D914}" uniqueName="1" name="title" queryTableFieldId="1" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{8F61F6E0-4133-42A5-924D-8BD507F4F59B}" uniqueName="2" name="href" queryTableFieldId="2" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{0BDB0DFA-9C44-44B4-9B3D-A67A9A379DFB}" uniqueName="3" name="section" queryTableFieldId="3" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{FAE5E803-4030-4058-89B4-85BD5D0DC6D9}" uniqueName="4" name="sectionTitle" queryTableFieldId="4" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{30F11EB6-BDD8-4CE0-8231-A45CF3C5D1BF}" uniqueName="5" name="sectionDescription" queryTableFieldId="5" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{8AB440D0-3289-4225-8E8C-4A5AAAE34C2E}" uniqueName="6" name="sectionOrder" queryTableFieldId="6" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{C58EA5C6-C560-40F5-89D2-88E731450954}" uniqueName="7" name="category" queryTableFieldId="7" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{5329A6F8-5583-41CC-A1B7-F1DE77D80783}" uniqueName="8" name="tags" queryTableFieldId="8" dataDxfId="6"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{487E3CF9-4E9F-41C4-A553-12FE09D4D914}" uniqueName="1" name="title" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{8F61F6E0-4133-42A5-924D-8BD507F4F59B}" uniqueName="2" name="href" queryTableFieldId="2" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{0BDB0DFA-9C44-44B4-9B3D-A67A9A379DFB}" uniqueName="3" name="section" queryTableFieldId="3" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{FAE5E803-4030-4058-89B4-85BD5D0DC6D9}" uniqueName="4" name="sectionTitle" queryTableFieldId="4" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{30F11EB6-BDD8-4CE0-8231-A45CF3C5D1BF}" uniqueName="5" name="sectionDescription" queryTableFieldId="5" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8AB440D0-3289-4225-8E8C-4A5AAAE34C2E}" uniqueName="6" name="sectionOrder" queryTableFieldId="6" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{C58EA5C6-C560-40F5-89D2-88E731450954}" uniqueName="7" name="category" queryTableFieldId="7" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{5329A6F8-5583-41CC-A1B7-F1DE77D80783}" uniqueName="8" name="tags" queryTableFieldId="8" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{0E27ED48-B958-4B99-88D7-05C34895B6F5}" uniqueName="9" name="targetBlank" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{69081A57-C339-43AB-A50E-1E99EDDAE734}" uniqueName="10" name="description" queryTableFieldId="10" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{69081A57-C339-43AB-A50E-1E99EDDAE734}" uniqueName="10" name="description" queryTableFieldId="10" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{68A00987-CE71-4C1B-83A8-B8CEAACB9505}" uniqueName="11" name="Colonne1" queryTableFieldId="602" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{96FFDA27-F17C-417C-A872-BC88B6B2B219}" name="Tableau1" displayName="Tableau1" ref="A1:C35" totalsRowShown="0">
+  <autoFilter ref="A1:C35" xr:uid="{96FFDA27-F17C-417C-A872-BC88B6B2B219}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B35">
+    <sortCondition ref="A1:A35"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3F17AB22-4B4B-4B6A-AC7B-931C40870137}" name="Titre"/>
+    <tableColumn id="3" xr3:uid="{9A80956E-A774-4285-883E-39073F9F2F2F}" name="Commentaire"/>
+    <tableColumn id="4" xr3:uid="{3EF12785-53A1-4C6A-B7FE-D9F3BCA0E4D6}" name="Lien" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -7141,7 +7509,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FCBDD6-984D-408F-975A-1DE93A8BC72E}">
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:K229"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -7149,14 +7517,14 @@
     <col min="3" max="3" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="6" max="6" width="8" style="4" customWidth="1"/>
     <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="62.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>473</v>
       </c>
@@ -7172,7 +7540,7 @@
       <c r="E1" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>478</v>
       </c>
       <c r="G1" t="s">
@@ -7187,404 +7555,437 @@
       <c r="J1" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F2" s="7">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>708</v>
+      </c>
+      <c r="H2" t="s">
+        <v>752</v>
+      </c>
+      <c r="I2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B3" t="s">
+        <v>750</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F3" s="7">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>708</v>
+      </c>
+      <c r="H3" t="s">
+        <v>752</v>
+      </c>
+      <c r="I3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>777</v>
+      </c>
+      <c r="B4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F4" s="7">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>708</v>
+      </c>
+      <c r="I4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>778</v>
+      </c>
+      <c r="B5" t="s">
+        <v>726</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F5" s="7">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>708</v>
+      </c>
+      <c r="H5" t="s">
+        <v>831</v>
+      </c>
+      <c r="I5" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>779</v>
+      </c>
+      <c r="B6" t="s">
+        <v>768</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F6" s="7">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>708</v>
+      </c>
+      <c r="H6" t="s">
+        <v>769</v>
+      </c>
+      <c r="I6" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>781</v>
+      </c>
+      <c r="B7" t="s">
+        <v>721</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F7" s="7">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>708</v>
+      </c>
+      <c r="H7" t="s">
+        <v>763</v>
+      </c>
+      <c r="I7" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>782</v>
+      </c>
+      <c r="B8" t="s">
+        <v>718</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F8" s="7">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>708</v>
+      </c>
+      <c r="H8" t="s">
+        <v>762</v>
+      </c>
+      <c r="I8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>802</v>
+      </c>
+      <c r="B9" t="s">
+        <v>725</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F9" s="7">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>708</v>
+      </c>
+      <c r="H9" t="s">
+        <v>729</v>
+      </c>
+      <c r="I9" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>783</v>
+      </c>
+      <c r="B10" t="s">
+        <v>720</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F10" s="7">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>708</v>
+      </c>
+      <c r="H10" t="s">
+        <v>761</v>
+      </c>
+      <c r="I10" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>784</v>
       </c>
-      <c r="B2" t="s">
-        <v>753</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F2" s="2">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>712</v>
-      </c>
-      <c r="H2" t="s">
-        <v>756</v>
-      </c>
-      <c r="I2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>780</v>
-      </c>
-      <c r="B3" t="s">
-        <v>754</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F3" s="2">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>712</v>
-      </c>
-      <c r="H3" t="s">
-        <v>756</v>
-      </c>
-      <c r="I3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>781</v>
-      </c>
-      <c r="B4" t="s">
-        <v>723</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F4" s="2">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>712</v>
-      </c>
-      <c r="I4" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B11" t="s">
+        <v>715</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F5" s="2">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>712</v>
-      </c>
-      <c r="H5" t="s">
-        <v>835</v>
-      </c>
-      <c r="I5" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>783</v>
-      </c>
-      <c r="B6" t="s">
-        <v>772</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F6" s="2">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>712</v>
-      </c>
-      <c r="H6" t="s">
-        <v>773</v>
-      </c>
-      <c r="I6" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D11" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F11" s="7">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>708</v>
+      </c>
+      <c r="H11" t="s">
+        <v>760</v>
+      </c>
+      <c r="I11" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>785</v>
       </c>
-      <c r="B7" t="s">
-        <v>725</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F7" s="2">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>712</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="B12" t="s">
+        <v>717</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F12" s="7">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>708</v>
+      </c>
+      <c r="H12" t="s">
+        <v>759</v>
+      </c>
+      <c r="I12" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>786</v>
+      </c>
+      <c r="B13" t="s">
+        <v>722</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F13" s="7">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>708</v>
+      </c>
+      <c r="H13" t="s">
+        <v>758</v>
+      </c>
+      <c r="I13" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>787</v>
+      </c>
+      <c r="B14" t="s">
+        <v>710</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F14" s="7">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>708</v>
+      </c>
+      <c r="H14" t="s">
+        <v>711</v>
+      </c>
+      <c r="I14" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>788</v>
+      </c>
+      <c r="B15" t="s">
+        <v>727</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F15" s="7">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>708</v>
+      </c>
+      <c r="H15" t="s">
+        <v>728</v>
+      </c>
+      <c r="I15" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>789</v>
+      </c>
+      <c r="B16" t="s">
+        <v>766</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F16" s="7">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>708</v>
+      </c>
+      <c r="H16" t="s">
         <v>767</v>
-      </c>
-      <c r="I7" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>786</v>
-      </c>
-      <c r="B8" t="s">
-        <v>722</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F8" s="2">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>712</v>
-      </c>
-      <c r="H8" t="s">
-        <v>766</v>
-      </c>
-      <c r="I8" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>806</v>
-      </c>
-      <c r="B9" t="s">
-        <v>729</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F9" s="2">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>712</v>
-      </c>
-      <c r="H9" t="s">
-        <v>733</v>
-      </c>
-      <c r="I9" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>787</v>
-      </c>
-      <c r="B10" t="s">
-        <v>724</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F10" s="2">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>712</v>
-      </c>
-      <c r="H10" t="s">
-        <v>765</v>
-      </c>
-      <c r="I10" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>788</v>
-      </c>
-      <c r="B11" t="s">
-        <v>719</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F11" s="2">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>712</v>
-      </c>
-      <c r="H11" t="s">
-        <v>764</v>
-      </c>
-      <c r="I11" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>789</v>
-      </c>
-      <c r="B12" t="s">
-        <v>721</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F12" s="2">
-        <v>9</v>
-      </c>
-      <c r="G12" t="s">
-        <v>712</v>
-      </c>
-      <c r="H12" t="s">
-        <v>763</v>
-      </c>
-      <c r="I12" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>790</v>
-      </c>
-      <c r="B13" t="s">
-        <v>726</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F13" s="2">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>712</v>
-      </c>
-      <c r="H13" t="s">
-        <v>762</v>
-      </c>
-      <c r="I13" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>791</v>
-      </c>
-      <c r="B14" t="s">
-        <v>714</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F14" s="2">
-        <v>9</v>
-      </c>
-      <c r="G14" t="s">
-        <v>712</v>
-      </c>
-      <c r="H14" t="s">
-        <v>715</v>
-      </c>
-      <c r="I14" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>792</v>
-      </c>
-      <c r="B15" t="s">
-        <v>731</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F15" s="2">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>712</v>
-      </c>
-      <c r="H15" t="s">
-        <v>732</v>
-      </c>
-      <c r="I15" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>793</v>
-      </c>
-      <c r="B16" t="s">
-        <v>770</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F16" s="2">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>712</v>
-      </c>
-      <c r="H16" t="s">
-        <v>771</v>
       </c>
       <c r="I16" t="s">
         <v>694</v>
@@ -7592,26 +7993,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B17" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E17" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F17" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F17" s="7">
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H17" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="I17" t="s">
         <v>694</v>
@@ -7619,26 +8022,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>795</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>837</v>
+        <v>791</v>
+      </c>
+      <c r="B18" t="s">
+        <v>833</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E18" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F18" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F18" s="7">
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H18" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="I18" t="s">
         <v>694</v>
@@ -7646,26 +8051,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>796</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>836</v>
+        <v>792</v>
+      </c>
+      <c r="B19" t="s">
+        <v>832</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D19" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E19" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F19" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F19" s="7">
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H19" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="I19" t="s">
         <v>694</v>
@@ -7673,26 +8080,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B20" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E20" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F20" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F20" s="7">
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H20" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="I20" t="s">
         <v>694</v>
@@ -7700,26 +8109,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>809</v>
+      </c>
+      <c r="B21" t="s">
+        <v>808</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F21" s="7">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>708</v>
+      </c>
+      <c r="H21" t="s">
         <v>813</v>
-      </c>
-      <c r="B21" t="s">
-        <v>812</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F21" s="2">
-        <v>9</v>
-      </c>
-      <c r="G21" t="s">
-        <v>712</v>
-      </c>
-      <c r="H21" t="s">
-        <v>817</v>
       </c>
       <c r="I21" t="s">
         <v>694</v>
@@ -7727,26 +8138,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B22" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E22" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F22" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F22" s="7">
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H22" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I22" t="s">
         <v>694</v>
@@ -7754,26 +8167,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B23" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E23" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F23" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F23" s="7">
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H23" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="I23" t="s">
         <v>694</v>
@@ -7781,26 +8196,28 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B24" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E24" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F24" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F24" s="7">
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H24" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="I24" t="s">
         <v>694</v>
@@ -7808,26 +8225,28 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B25" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D25" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E25" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F25" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F25" s="7">
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H25" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="I25" t="s">
         <v>694</v>
@@ -7835,26 +8254,28 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B26" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E26" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F26" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F26" s="7">
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H26" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="I26" t="s">
         <v>694</v>
@@ -7862,26 +8283,28 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B27" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E27" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F27" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F27" s="7">
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H27" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="I27" t="s">
         <v>694</v>
@@ -7889,26 +8312,28 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B28" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E28" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F28" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F28" s="7">
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H28" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="I28" t="s">
         <v>694</v>
@@ -7916,26 +8341,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B29" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E29" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F29" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F29" s="7">
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H29" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="I29" t="s">
         <v>694</v>
@@ -7943,26 +8370,28 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B30" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D30" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E30" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F30" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F30" s="7">
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H30" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="I30" t="s">
         <v>694</v>
@@ -7970,26 +8399,28 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B31" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E31" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F31" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F31" s="7">
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H31" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="I31" t="s">
         <v>694</v>
@@ -7997,26 +8428,28 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B32" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D32" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E32" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F32" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F32" s="7">
+        <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H32" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="I32" t="s">
         <v>694</v>
@@ -8024,26 +8457,28 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B33" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D33" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E33" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F33" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F33" s="7">
+        <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H33" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="I33" t="s">
         <v>694</v>
@@ -8051,26 +8486,28 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B34" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>709</v>
+      </c>
       <c r="E34" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="F34" s="2">
-        <v>9</v>
+        <v>709</v>
+      </c>
+      <c r="F34" s="7">
+        <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="H34" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="I34" t="s">
         <v>694</v>
@@ -8078,20 +8515,25 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="B35" t="s">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="F35" s="2">
-        <v>9</v>
+        <v>730</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F35" s="7">
+        <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="I35" t="s">
         <v>694</v>
@@ -8099,17 +8541,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>738</v>
+        <v>712</v>
       </c>
       <c r="B36" t="s">
-        <v>739</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="F36" s="2">
-        <v>9</v>
+        <v>713</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F36" s="7">
+        <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>740</v>
+        <v>714</v>
       </c>
       <c r="I36" t="s">
         <v>694</v>
@@ -8131,8 +8581,8 @@
       <c r="E37" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F37" s="2">
-        <v>10</v>
+      <c r="F37" s="7">
+        <v>20</v>
       </c>
       <c r="G37" t="s">
         <v>289</v>
@@ -8163,8 +8613,8 @@
       <c r="E38" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F38" s="2">
-        <v>10</v>
+      <c r="F38" s="7">
+        <v>20</v>
       </c>
       <c r="G38" t="s">
         <v>289</v>
@@ -8195,8 +8645,8 @@
       <c r="E39" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F39" s="2">
-        <v>10</v>
+      <c r="F39" s="7">
+        <v>20</v>
       </c>
       <c r="G39" t="s">
         <v>289</v>
@@ -8227,8 +8677,8 @@
       <c r="E40" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F40" s="2">
-        <v>10</v>
+      <c r="F40" s="7">
+        <v>20</v>
       </c>
       <c r="G40" t="s">
         <v>289</v>
@@ -8259,8 +8709,8 @@
       <c r="E41" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F41" s="2">
-        <v>10</v>
+      <c r="F41" s="7">
+        <v>20</v>
       </c>
       <c r="G41" t="s">
         <v>289</v>
@@ -8291,8 +8741,8 @@
       <c r="E42" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F42" s="2">
-        <v>10</v>
+      <c r="F42" s="7">
+        <v>20</v>
       </c>
       <c r="G42" t="s">
         <v>289</v>
@@ -8309,31 +8759,31 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="B43" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F43" s="2">
-        <v>20</v>
+        <v>536</v>
+      </c>
+      <c r="F43" s="7">
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>289</v>
+        <v>537</v>
       </c>
       <c r="H43" t="s">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="I43" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J43" t="s">
         <v>289</v>
@@ -8341,228 +8791,213 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>505</v>
+        <v>875</v>
       </c>
       <c r="B44" t="s">
-        <v>506</v>
+        <v>874</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F44" s="2">
-        <v>20</v>
+        <v>536</v>
+      </c>
+      <c r="F44" s="7">
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>289</v>
+        <v>861</v>
       </c>
       <c r="H44" t="s">
-        <v>510</v>
+        <v>876</v>
       </c>
       <c r="I44" t="s">
         <v>694</v>
-      </c>
-      <c r="J44" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>521</v>
+        <v>821</v>
       </c>
       <c r="B45" t="s">
-        <v>522</v>
+        <v>822</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F45" s="2">
+        <v>536</v>
+      </c>
+      <c r="F45" s="7">
         <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>523</v>
+        <v>819</v>
       </c>
       <c r="H45" t="s">
-        <v>524</v>
+        <v>820</v>
       </c>
       <c r="I45" t="s">
         <v>694</v>
-      </c>
-      <c r="J45" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>525</v>
+        <v>877</v>
       </c>
       <c r="B46" t="s">
-        <v>526</v>
+        <v>878</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F46" s="2">
+        <v>536</v>
+      </c>
+      <c r="F46" s="7">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>523</v>
+        <v>861</v>
       </c>
       <c r="H46" t="s">
-        <v>527</v>
+        <v>879</v>
       </c>
       <c r="I46" t="s">
         <v>694</v>
-      </c>
-      <c r="J46" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>528</v>
+        <v>880</v>
       </c>
       <c r="B47" t="s">
-        <v>529</v>
+        <v>881</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F47" s="2">
+        <v>536</v>
+      </c>
+      <c r="F47" s="7">
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>530</v>
+        <v>861</v>
       </c>
       <c r="H47" t="s">
-        <v>531</v>
+        <v>882</v>
       </c>
       <c r="I47" t="s">
         <v>694</v>
-      </c>
-      <c r="J47" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>514</v>
+        <v>922</v>
       </c>
       <c r="B48" t="s">
-        <v>515</v>
+        <v>923</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F48" s="2">
+        <v>536</v>
+      </c>
+      <c r="F48" s="7">
         <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>519</v>
+        <v>861</v>
       </c>
       <c r="H48" t="s">
-        <v>520</v>
+        <v>924</v>
       </c>
       <c r="I48" t="s">
         <v>694</v>
-      </c>
-      <c r="J48" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>697</v>
+        <v>892</v>
       </c>
       <c r="B49" t="s">
-        <v>696</v>
+        <v>893</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F49" s="2">
+        <v>536</v>
+      </c>
+      <c r="F49" s="7">
         <v>30</v>
       </c>
+      <c r="G49" t="s">
+        <v>861</v>
+      </c>
       <c r="H49" t="s">
-        <v>701</v>
+        <v>894</v>
       </c>
       <c r="I49" t="s">
         <v>694</v>
-      </c>
-      <c r="J49" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>698</v>
+        <v>895</v>
       </c>
       <c r="B50" t="s">
-        <v>699</v>
+        <v>896</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F50" s="2">
+        <v>536</v>
+      </c>
+      <c r="F50" s="7">
         <v>30</v>
       </c>
+      <c r="G50" t="s">
+        <v>861</v>
+      </c>
       <c r="H50" t="s">
-        <v>700</v>
+        <v>897</v>
       </c>
       <c r="I50" t="s">
         <v>694</v>
-      </c>
-      <c r="J50" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>825</v>
+        <v>898</v>
       </c>
       <c r="B51" t="s">
-        <v>826</v>
+        <v>899</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>534</v>
@@ -8573,14 +9008,14 @@
       <c r="E51" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F51" s="2">
-        <v>40</v>
+      <c r="F51" s="7">
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>823</v>
+        <v>861</v>
       </c>
       <c r="H51" t="s">
-        <v>824</v>
+        <v>903</v>
       </c>
       <c r="I51" t="s">
         <v>694</v>
@@ -8588,10 +9023,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>830</v>
+        <v>737</v>
       </c>
       <c r="B52" t="s">
-        <v>831</v>
+        <v>738</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>534</v>
@@ -8602,25 +9037,28 @@
       <c r="E52" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F52" s="2">
-        <v>40</v>
+      <c r="F52" s="7">
+        <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>823</v>
+        <v>739</v>
       </c>
       <c r="H52" t="s">
-        <v>829</v>
+        <v>740</v>
       </c>
       <c r="I52" t="s">
         <v>694</v>
+      </c>
+      <c r="J52" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>827</v>
+        <v>742</v>
       </c>
       <c r="B53" t="s">
-        <v>828</v>
+        <v>743</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>534</v>
@@ -8631,25 +9069,28 @@
       <c r="E53" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F53" s="2">
-        <v>40</v>
+      <c r="F53" s="7">
+        <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>823</v>
+        <v>739</v>
       </c>
       <c r="H53" t="s">
-        <v>829</v>
+        <v>744</v>
       </c>
       <c r="I53" t="s">
         <v>694</v>
+      </c>
+      <c r="J53" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>821</v>
+        <v>900</v>
       </c>
       <c r="B54" t="s">
-        <v>822</v>
+        <v>901</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>534</v>
@@ -8660,14 +9101,14 @@
       <c r="E54" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F54" s="2">
-        <v>40</v>
+      <c r="F54" s="7">
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>823</v>
+        <v>861</v>
       </c>
       <c r="H54" t="s">
-        <v>824</v>
+        <v>902</v>
       </c>
       <c r="I54" t="s">
         <v>694</v>
@@ -8675,10 +9116,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>741</v>
+        <v>907</v>
       </c>
       <c r="B55" t="s">
-        <v>742</v>
+        <v>908</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>534</v>
@@ -8689,28 +9130,25 @@
       <c r="E55" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F55" s="2">
-        <v>40</v>
+      <c r="F55" s="7">
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>743</v>
+        <v>861</v>
       </c>
       <c r="H55" t="s">
-        <v>744</v>
+        <v>909</v>
       </c>
       <c r="I55" t="s">
         <v>694</v>
-      </c>
-      <c r="J55" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>746</v>
+        <v>904</v>
       </c>
       <c r="B56" t="s">
-        <v>747</v>
+        <v>905</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>534</v>
@@ -8721,28 +9159,25 @@
       <c r="E56" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F56" s="2">
-        <v>40</v>
+      <c r="F56" s="7">
+        <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>743</v>
+        <v>861</v>
       </c>
       <c r="H56" t="s">
-        <v>748</v>
+        <v>906</v>
       </c>
       <c r="I56" t="s">
         <v>694</v>
-      </c>
-      <c r="J56" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>554</v>
+        <v>928</v>
       </c>
       <c r="B57" t="s">
-        <v>555</v>
+        <v>929</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>534</v>
@@ -8753,28 +9188,25 @@
       <c r="E57" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F57" s="2">
-        <v>40</v>
+      <c r="F57" s="7">
+        <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>743</v>
+        <v>861</v>
       </c>
       <c r="H57" t="s">
-        <v>556</v>
+        <v>930</v>
       </c>
       <c r="I57" t="s">
         <v>694</v>
-      </c>
-      <c r="J57" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>545</v>
+        <v>846</v>
       </c>
       <c r="B58" t="s">
-        <v>546</v>
+        <v>847</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>534</v>
@@ -8785,28 +9217,25 @@
       <c r="E58" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F58" s="2">
-        <v>40</v>
+      <c r="F58" s="7">
+        <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H58" t="s">
-        <v>547</v>
+        <v>848</v>
       </c>
       <c r="I58" t="s">
-        <v>695</v>
-      </c>
-      <c r="J58" t="s">
-        <v>289</v>
+        <v>694</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>532</v>
+        <v>886</v>
       </c>
       <c r="B59" t="s">
-        <v>533</v>
+        <v>887</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>534</v>
@@ -8817,28 +9246,25 @@
       <c r="E59" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F59" s="2">
-        <v>40</v>
+      <c r="F59" s="7">
+        <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H59" t="s">
-        <v>538</v>
+        <v>888</v>
       </c>
       <c r="I59" t="s">
         <v>694</v>
-      </c>
-      <c r="J59" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="B60" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>534</v>
@@ -8849,14 +9275,14 @@
       <c r="E60" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F60" s="2">
-        <v>40</v>
+      <c r="F60" s="7">
+        <v>30</v>
       </c>
       <c r="G60" t="s">
         <v>537</v>
       </c>
       <c r="H60" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I60" t="s">
         <v>694</v>
@@ -8867,10 +9293,10 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="B61" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>534</v>
@@ -8881,14 +9307,14 @@
       <c r="E61" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F61" s="2">
-        <v>40</v>
+      <c r="F61" s="7">
+        <v>30</v>
       </c>
       <c r="G61" t="s">
         <v>537</v>
       </c>
       <c r="H61" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="I61" t="s">
         <v>694</v>
@@ -8899,10 +9325,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B62" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>534</v>
@@ -8913,14 +9339,14 @@
       <c r="E62" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F62" s="2">
-        <v>40</v>
+      <c r="F62" s="7">
+        <v>30</v>
       </c>
       <c r="G62" t="s">
         <v>537</v>
       </c>
       <c r="H62" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="I62" t="s">
         <v>694</v>
@@ -8931,10 +9357,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>548</v>
+        <v>910</v>
       </c>
       <c r="B63" t="s">
-        <v>549</v>
+        <v>911</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>534</v>
@@ -8945,590 +9371,536 @@
       <c r="E63" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F63" s="2">
-        <v>40</v>
+      <c r="F63" s="7">
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H63" t="s">
-        <v>550</v>
+        <v>912</v>
       </c>
       <c r="I63" t="s">
         <v>694</v>
-      </c>
-      <c r="J63" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>613</v>
+        <v>913</v>
       </c>
       <c r="B64" t="s">
-        <v>614</v>
+        <v>914</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F64" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F64" s="7">
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>615</v>
+        <v>861</v>
       </c>
       <c r="H64" t="s">
-        <v>616</v>
+        <v>915</v>
       </c>
       <c r="I64" t="s">
         <v>694</v>
       </c>
-      <c r="J64" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>673</v>
+        <v>843</v>
       </c>
       <c r="B65" t="s">
-        <v>674</v>
+        <v>844</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F65" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F65" s="7">
+        <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>675</v>
+        <v>861</v>
       </c>
       <c r="H65" t="s">
-        <v>676</v>
+        <v>845</v>
       </c>
       <c r="I65" t="s">
         <v>694</v>
       </c>
-      <c r="J65" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>681</v>
+        <v>889</v>
       </c>
       <c r="B66" t="s">
-        <v>682</v>
+        <v>890</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F66" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F66" s="7">
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>675</v>
+        <v>861</v>
       </c>
       <c r="H66" t="s">
-        <v>683</v>
+        <v>891</v>
       </c>
       <c r="I66" t="s">
         <v>694</v>
       </c>
-      <c r="J66" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>590</v>
+        <v>916</v>
       </c>
       <c r="B67" t="s">
-        <v>591</v>
+        <v>705</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F67" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F67" s="7">
+        <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>584</v>
+        <v>861</v>
       </c>
       <c r="H67" t="s">
-        <v>592</v>
+        <v>917</v>
       </c>
       <c r="I67" t="s">
         <v>694</v>
       </c>
-      <c r="J67" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>586</v>
+        <v>920</v>
       </c>
       <c r="B68" t="s">
-        <v>587</v>
+        <v>704</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F68" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F68" s="7">
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>584</v>
+        <v>861</v>
       </c>
       <c r="H68" t="s">
-        <v>585</v>
+        <v>921</v>
       </c>
       <c r="I68" t="s">
         <v>694</v>
       </c>
-      <c r="J68" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>582</v>
+        <v>918</v>
       </c>
       <c r="B69" t="s">
-        <v>583</v>
+        <v>706</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F69" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F69" s="7">
+        <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>584</v>
+        <v>861</v>
       </c>
       <c r="H69" t="s">
-        <v>585</v>
+        <v>919</v>
       </c>
       <c r="I69" t="s">
         <v>694</v>
       </c>
-      <c r="J69" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>588</v>
+        <v>826</v>
       </c>
       <c r="B70" t="s">
-        <v>589</v>
+        <v>827</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F70" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F70" s="7">
+        <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>584</v>
+        <v>819</v>
       </c>
       <c r="H70" t="s">
-        <v>585</v>
+        <v>825</v>
       </c>
       <c r="I70" t="s">
         <v>694</v>
       </c>
-      <c r="J70" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>593</v>
+        <v>925</v>
       </c>
       <c r="B71" t="s">
-        <v>594</v>
+        <v>926</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F71" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F71" s="7">
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>584</v>
+        <v>861</v>
       </c>
       <c r="H71" t="s">
-        <v>592</v>
+        <v>927</v>
       </c>
       <c r="I71" t="s">
         <v>694</v>
       </c>
-      <c r="J71" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>629</v>
+        <v>823</v>
       </c>
       <c r="B72" t="s">
-        <v>630</v>
+        <v>824</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F72" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F72" s="7">
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>619</v>
+        <v>819</v>
       </c>
       <c r="H72" t="s">
-        <v>631</v>
+        <v>825</v>
       </c>
       <c r="I72" t="s">
         <v>694</v>
       </c>
-      <c r="J72" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>626</v>
+        <v>817</v>
       </c>
       <c r="B73" t="s">
-        <v>627</v>
+        <v>818</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F73" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F73" s="7">
+        <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>619</v>
+        <v>819</v>
       </c>
       <c r="H73" t="s">
-        <v>628</v>
+        <v>820</v>
       </c>
       <c r="I73" t="s">
         <v>694</v>
       </c>
-      <c r="J73" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>617</v>
+        <v>834</v>
       </c>
       <c r="B74" t="s">
-        <v>618</v>
+        <v>836</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F74" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F74" s="7">
+        <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>619</v>
+        <v>861</v>
       </c>
       <c r="H74" t="s">
-        <v>620</v>
+        <v>835</v>
       </c>
       <c r="I74" t="s">
         <v>694</v>
       </c>
-      <c r="J74" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>624</v>
+        <v>862</v>
       </c>
       <c r="B75" t="s">
-        <v>625</v>
+        <v>863</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F75" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F75" s="7">
+        <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>619</v>
+        <v>861</v>
       </c>
       <c r="H75" t="s">
-        <v>623</v>
+        <v>864</v>
       </c>
       <c r="I75" t="s">
         <v>694</v>
       </c>
-      <c r="J75" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>621</v>
+        <v>855</v>
       </c>
       <c r="B76" t="s">
-        <v>622</v>
+        <v>856</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F76" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F76" s="7">
+        <v>30</v>
       </c>
       <c r="G76" t="s">
-        <v>619</v>
+        <v>861</v>
       </c>
       <c r="H76" t="s">
-        <v>623</v>
+        <v>857</v>
       </c>
       <c r="I76" t="s">
         <v>694</v>
       </c>
-      <c r="J76" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>565</v>
+        <v>849</v>
       </c>
       <c r="B77" t="s">
-        <v>566</v>
+        <v>850</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F77" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F77" s="7">
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>570</v>
+        <v>861</v>
       </c>
       <c r="H77" t="s">
-        <v>735</v>
+        <v>851</v>
       </c>
       <c r="I77" t="s">
         <v>694</v>
       </c>
-      <c r="J77" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>577</v>
+        <v>840</v>
       </c>
       <c r="B78" t="s">
-        <v>578</v>
+        <v>841</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F78" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F78" s="7">
+        <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>570</v>
+        <v>861</v>
       </c>
       <c r="H78" t="s">
-        <v>576</v>
+        <v>842</v>
       </c>
       <c r="I78" t="s">
         <v>694</v>
       </c>
-      <c r="J78" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>574</v>
+        <v>931</v>
       </c>
       <c r="B79" t="s">
-        <v>575</v>
+        <v>932</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F79" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F79" s="7">
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>570</v>
+        <v>861</v>
       </c>
       <c r="H79" t="s">
-        <v>576</v>
+        <v>933</v>
       </c>
       <c r="I79" t="s">
         <v>694</v>
       </c>
-      <c r="J79" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>579</v>
+        <v>883</v>
       </c>
       <c r="B80" t="s">
-        <v>580</v>
+        <v>884</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F80" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F80" s="7">
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>570</v>
+        <v>861</v>
       </c>
       <c r="H80" t="s">
-        <v>581</v>
+        <v>885</v>
       </c>
       <c r="I80" t="s">
         <v>694</v>
-      </c>
-      <c r="J80" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>571</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F81" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F81" s="7">
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="H81" t="s">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="I81" t="s">
         <v>694</v>
@@ -9539,60 +9911,57 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>642</v>
+        <v>865</v>
       </c>
       <c r="B82" t="s">
-        <v>643</v>
+        <v>866</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F82" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F82" s="7">
+        <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>644</v>
+        <v>861</v>
       </c>
       <c r="H82" t="s">
-        <v>645</v>
+        <v>867</v>
       </c>
       <c r="I82" t="s">
         <v>694</v>
-      </c>
-      <c r="J82" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>636</v>
+        <v>554</v>
       </c>
       <c r="B83" t="s">
-        <v>637</v>
+        <v>555</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F83" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F83" s="7">
+        <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>634</v>
+        <v>739</v>
       </c>
       <c r="H83" t="s">
-        <v>635</v>
+        <v>556</v>
       </c>
       <c r="I83" t="s">
         <v>694</v>
@@ -9603,188 +9972,173 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>632</v>
+        <v>868</v>
       </c>
       <c r="B84" t="s">
-        <v>633</v>
+        <v>869</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F84" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F84" s="7">
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>634</v>
+        <v>861</v>
       </c>
       <c r="H84" t="s">
-        <v>635</v>
+        <v>870</v>
       </c>
       <c r="I84" t="s">
         <v>694</v>
-      </c>
-      <c r="J84" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>610</v>
+        <v>871</v>
       </c>
       <c r="B85" t="s">
-        <v>611</v>
+        <v>872</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F85" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F85" s="7">
+        <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>608</v>
+        <v>861</v>
       </c>
       <c r="H85" t="s">
-        <v>612</v>
+        <v>873</v>
       </c>
       <c r="I85" t="s">
         <v>694</v>
-      </c>
-      <c r="J85" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>606</v>
+        <v>837</v>
       </c>
       <c r="B86" t="s">
-        <v>607</v>
+        <v>838</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F86" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F86" s="7">
+        <v>30</v>
       </c>
       <c r="G86" t="s">
-        <v>608</v>
+        <v>861</v>
       </c>
       <c r="H86" t="s">
-        <v>609</v>
+        <v>839</v>
       </c>
       <c r="I86" t="s">
         <v>694</v>
-      </c>
-      <c r="J86" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>602</v>
+        <v>858</v>
       </c>
       <c r="B87" t="s">
-        <v>603</v>
+        <v>859</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F87" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F87" s="7">
+        <v>30</v>
       </c>
       <c r="G87" t="s">
-        <v>604</v>
+        <v>861</v>
       </c>
       <c r="H87" t="s">
-        <v>605</v>
+        <v>860</v>
       </c>
       <c r="I87" t="s">
         <v>694</v>
-      </c>
-      <c r="J87" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>638</v>
+        <v>852</v>
       </c>
       <c r="B88" t="s">
-        <v>639</v>
+        <v>853</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F88" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F88" s="7">
+        <v>30</v>
       </c>
       <c r="G88" t="s">
-        <v>640</v>
+        <v>861</v>
       </c>
       <c r="H88" t="s">
-        <v>641</v>
+        <v>854</v>
       </c>
       <c r="I88" t="s">
         <v>694</v>
-      </c>
-      <c r="J88" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>654</v>
+        <v>548</v>
       </c>
       <c r="B89" t="s">
-        <v>655</v>
+        <v>549</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F89" s="2">
-        <v>50</v>
+        <v>536</v>
+      </c>
+      <c r="F89" s="7">
+        <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>656</v>
+        <v>537</v>
       </c>
       <c r="H89" t="s">
-        <v>657</v>
+        <v>550</v>
       </c>
       <c r="I89" t="s">
         <v>694</v>
@@ -9795,28 +10149,28 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>658</v>
+        <v>521</v>
       </c>
       <c r="B90" t="s">
-        <v>659</v>
+        <v>522</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F90" s="2">
-        <v>50</v>
+        <v>518</v>
+      </c>
+      <c r="F90" s="7">
+        <v>40</v>
       </c>
       <c r="G90" t="s">
-        <v>656</v>
+        <v>523</v>
       </c>
       <c r="H90" t="s">
-        <v>657</v>
+        <v>524</v>
       </c>
       <c r="I90" t="s">
         <v>694</v>
@@ -9827,28 +10181,28 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>600</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s">
-        <v>601</v>
+        <v>515</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F91" s="2">
-        <v>50</v>
+        <v>518</v>
+      </c>
+      <c r="F91" s="7">
+        <v>40</v>
       </c>
       <c r="G91" t="s">
-        <v>597</v>
+        <v>519</v>
       </c>
       <c r="H91" t="s">
-        <v>597</v>
+        <v>520</v>
       </c>
       <c r="I91" t="s">
         <v>694</v>
@@ -9859,28 +10213,28 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>595</v>
+        <v>525</v>
       </c>
       <c r="B92" t="s">
-        <v>596</v>
+        <v>526</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F92" s="2">
-        <v>50</v>
+        <v>518</v>
+      </c>
+      <c r="F92" s="7">
+        <v>40</v>
       </c>
       <c r="G92" t="s">
-        <v>597</v>
+        <v>523</v>
       </c>
       <c r="H92" t="s">
-        <v>597</v>
+        <v>527</v>
       </c>
       <c r="I92" t="s">
         <v>694</v>
@@ -9891,28 +10245,28 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>598</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s">
-        <v>599</v>
+        <v>529</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F93" s="2">
-        <v>50</v>
+        <v>518</v>
+      </c>
+      <c r="F93" s="7">
+        <v>40</v>
       </c>
       <c r="G93" t="s">
-        <v>597</v>
+        <v>530</v>
       </c>
       <c r="H93" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="I93" t="s">
         <v>694</v>
@@ -9923,92 +10277,86 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>663</v>
+        <v>697</v>
       </c>
       <c r="B94" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F94" s="2">
-        <v>50</v>
-      </c>
-      <c r="G94" t="s">
-        <v>665</v>
+        <v>518</v>
+      </c>
+      <c r="F94" s="7">
+        <v>40</v>
       </c>
       <c r="H94" t="s">
-        <v>666</v>
+        <v>701</v>
       </c>
       <c r="I94" t="s">
         <v>694</v>
       </c>
       <c r="J94" t="s">
-        <v>289</v>
+        <v>703</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="B95" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F95" s="2">
-        <v>50</v>
-      </c>
-      <c r="G95" t="s">
-        <v>665</v>
+        <v>518</v>
+      </c>
+      <c r="F95" s="7">
+        <v>40</v>
       </c>
       <c r="H95" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="I95" t="s">
         <v>694</v>
       </c>
       <c r="J95" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>677</v>
+        <v>511</v>
       </c>
       <c r="B96" t="s">
-        <v>678</v>
+        <v>512</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F96" s="2">
+        <v>509</v>
+      </c>
+      <c r="F96" s="7">
         <v>50</v>
       </c>
       <c r="G96" t="s">
-        <v>679</v>
+        <v>289</v>
       </c>
       <c r="H96" t="s">
-        <v>680</v>
+        <v>513</v>
       </c>
       <c r="I96" t="s">
         <v>694</v>
@@ -10019,28 +10367,28 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>684</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s">
-        <v>685</v>
+        <v>506</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F97" s="2">
+        <v>509</v>
+      </c>
+      <c r="F97" s="7">
         <v>50</v>
       </c>
       <c r="G97" t="s">
-        <v>679</v>
+        <v>289</v>
       </c>
       <c r="H97" t="s">
-        <v>686</v>
+        <v>510</v>
       </c>
       <c r="I97" t="s">
         <v>694</v>
@@ -10051,10 +10399,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>667</v>
+        <v>590</v>
       </c>
       <c r="B98" t="s">
-        <v>668</v>
+        <v>591</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>567</v>
@@ -10065,14 +10413,14 @@
       <c r="E98" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F98" s="2">
-        <v>50</v>
+      <c r="F98" s="7">
+        <v>60</v>
       </c>
       <c r="G98" t="s">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="H98" t="s">
-        <v>669</v>
+        <v>592</v>
       </c>
       <c r="I98" t="s">
         <v>694</v>
@@ -10083,10 +10431,10 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B99" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>567</v>
@@ -10097,14 +10445,14 @@
       <c r="E99" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F99" s="2">
-        <v>50</v>
+      <c r="F99" s="7">
+        <v>60</v>
       </c>
       <c r="G99" t="s">
-        <v>537</v>
+        <v>675</v>
       </c>
       <c r="H99" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="I99" t="s">
         <v>694</v>
@@ -10115,10 +10463,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="B100" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>567</v>
@@ -10129,14 +10477,14 @@
       <c r="E100" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F100" s="2">
-        <v>50</v>
+      <c r="F100" s="7">
+        <v>60</v>
       </c>
       <c r="G100" t="s">
-        <v>537</v>
+        <v>675</v>
       </c>
       <c r="H100" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="I100" t="s">
         <v>694</v>
@@ -10147,10 +10495,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>706</v>
+        <v>610</v>
       </c>
       <c r="B101" t="s">
-        <v>708</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>567</v>
@@ -10161,25 +10509,28 @@
       <c r="E101" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F101" s="2">
-        <v>50</v>
+      <c r="F101" s="7">
+        <v>60</v>
       </c>
       <c r="G101" t="s">
-        <v>648</v>
+        <v>608</v>
       </c>
       <c r="H101" t="s">
-        <v>710</v>
+        <v>612</v>
       </c>
       <c r="I101" t="s">
         <v>694</v>
+      </c>
+      <c r="J101" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>707</v>
+        <v>586</v>
       </c>
       <c r="B102" t="s">
-        <v>709</v>
+        <v>587</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>567</v>
@@ -10190,25 +10541,28 @@
       <c r="E102" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F102" s="2">
-        <v>50</v>
+      <c r="F102" s="7">
+        <v>60</v>
       </c>
       <c r="G102" t="s">
-        <v>648</v>
+        <v>584</v>
       </c>
       <c r="H102" t="s">
-        <v>710</v>
+        <v>585</v>
       </c>
       <c r="I102" t="s">
         <v>694</v>
+      </c>
+      <c r="J102" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>705</v>
+        <v>582</v>
       </c>
       <c r="B103" t="s">
-        <v>704</v>
+        <v>583</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>567</v>
@@ -10219,25 +10573,28 @@
       <c r="E103" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F103" s="2">
-        <v>50</v>
+      <c r="F103" s="7">
+        <v>60</v>
       </c>
       <c r="G103" t="s">
-        <v>648</v>
+        <v>584</v>
       </c>
       <c r="H103" t="s">
-        <v>710</v>
+        <v>585</v>
       </c>
       <c r="I103" t="s">
         <v>694</v>
+      </c>
+      <c r="J103" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>646</v>
+        <v>588</v>
       </c>
       <c r="B104" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>567</v>
@@ -10248,14 +10605,14 @@
       <c r="E104" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F104" s="2">
-        <v>50</v>
+      <c r="F104" s="7">
+        <v>60</v>
       </c>
       <c r="G104" t="s">
-        <v>648</v>
+        <v>584</v>
       </c>
       <c r="H104" t="s">
-        <v>649</v>
+        <v>585</v>
       </c>
       <c r="I104" t="s">
         <v>694</v>
@@ -10266,10 +10623,10 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>650</v>
+        <v>565</v>
       </c>
       <c r="B105" t="s">
-        <v>651</v>
+        <v>566</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>567</v>
@@ -10280,14 +10637,14 @@
       <c r="E105" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F105" s="2">
-        <v>50</v>
+      <c r="F105" s="7">
+        <v>60</v>
       </c>
       <c r="G105" t="s">
-        <v>652</v>
+        <v>570</v>
       </c>
       <c r="H105" t="s">
-        <v>653</v>
+        <v>731</v>
       </c>
       <c r="I105" t="s">
         <v>694</v>
@@ -10298,973 +10655,1066 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>561</v>
+        <v>606</v>
       </c>
       <c r="B106" t="s">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F106" s="2">
-        <v>50</v>
+        <v>569</v>
+      </c>
+      <c r="F106" s="7">
+        <v>60</v>
       </c>
       <c r="G106" t="s">
+        <v>608</v>
+      </c>
+      <c r="H106" t="s">
+        <v>609</v>
+      </c>
+      <c r="I106" t="s">
+        <v>694</v>
+      </c>
+      <c r="J106" t="s">
         <v>289</v>
-      </c>
-      <c r="H106" t="s">
-        <v>563</v>
-      </c>
-      <c r="I106" t="s">
-        <v>694</v>
-      </c>
-      <c r="J106" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>557</v>
+        <v>629</v>
       </c>
       <c r="B107" t="s">
-        <v>558</v>
+        <v>630</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F107" s="2">
-        <v>50</v>
+        <v>569</v>
+      </c>
+      <c r="F107" s="7">
+        <v>60</v>
       </c>
       <c r="G107" t="s">
+        <v>619</v>
+      </c>
+      <c r="H107" t="s">
+        <v>631</v>
+      </c>
+      <c r="I107" t="s">
+        <v>694</v>
+      </c>
+      <c r="J107" t="s">
         <v>289</v>
-      </c>
-      <c r="H107" t="s">
-        <v>559</v>
-      </c>
-      <c r="I107" t="s">
-        <v>694</v>
-      </c>
-      <c r="J107" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>290</v>
+        <v>626</v>
       </c>
       <c r="B108" t="s">
-        <v>291</v>
+        <v>627</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F108" s="2">
+        <v>569</v>
+      </c>
+      <c r="F108" s="7">
         <v>60</v>
       </c>
       <c r="G108" t="s">
-        <v>472</v>
+        <v>619</v>
       </c>
       <c r="H108" t="s">
-        <v>693</v>
+        <v>628</v>
       </c>
       <c r="I108" t="s">
         <v>694</v>
+      </c>
+      <c r="J108" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>292</v>
+        <v>617</v>
       </c>
       <c r="B109" t="s">
-        <v>293</v>
+        <v>618</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F109" s="2">
+        <v>569</v>
+      </c>
+      <c r="F109" s="7">
         <v>60</v>
       </c>
       <c r="G109" t="s">
-        <v>472</v>
+        <v>619</v>
       </c>
       <c r="H109" t="s">
-        <v>693</v>
+        <v>620</v>
       </c>
       <c r="I109" t="s">
         <v>694</v>
+      </c>
+      <c r="J109" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>294</v>
+        <v>624</v>
       </c>
       <c r="B110" t="s">
-        <v>295</v>
+        <v>625</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F110" s="2">
+        <v>569</v>
+      </c>
+      <c r="F110" s="7">
         <v>60</v>
       </c>
       <c r="G110" t="s">
-        <v>472</v>
+        <v>619</v>
       </c>
       <c r="H110" t="s">
-        <v>693</v>
+        <v>623</v>
       </c>
       <c r="I110" t="s">
         <v>694</v>
+      </c>
+      <c r="J110" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>296</v>
+        <v>621</v>
       </c>
       <c r="B111" t="s">
-        <v>297</v>
+        <v>622</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F111" s="2">
+        <v>569</v>
+      </c>
+      <c r="F111" s="7">
         <v>60</v>
       </c>
       <c r="G111" t="s">
-        <v>472</v>
+        <v>619</v>
       </c>
       <c r="H111" t="s">
-        <v>693</v>
+        <v>623</v>
       </c>
       <c r="I111" t="s">
         <v>694</v>
+      </c>
+      <c r="J111" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>298</v>
+        <v>613</v>
       </c>
       <c r="B112" t="s">
-        <v>299</v>
+        <v>614</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F112" s="2">
+        <v>569</v>
+      </c>
+      <c r="F112" s="7">
         <v>60</v>
       </c>
       <c r="G112" t="s">
-        <v>472</v>
+        <v>615</v>
       </c>
       <c r="H112" t="s">
-        <v>693</v>
+        <v>616</v>
       </c>
       <c r="I112" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J112" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>300</v>
+        <v>667</v>
       </c>
       <c r="B113" t="s">
-        <v>301</v>
+        <v>668</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F113" s="2">
+        <v>569</v>
+      </c>
+      <c r="F113" s="7">
         <v>60</v>
       </c>
       <c r="G113" t="s">
-        <v>472</v>
+        <v>537</v>
       </c>
       <c r="H113" t="s">
-        <v>693</v>
+        <v>669</v>
       </c>
       <c r="I113" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J113" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>302</v>
+        <v>677</v>
       </c>
       <c r="B114" t="s">
-        <v>303</v>
+        <v>678</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F114" s="2">
+        <v>569</v>
+      </c>
+      <c r="F114" s="7">
         <v>60</v>
       </c>
       <c r="G114" t="s">
-        <v>472</v>
+        <v>679</v>
       </c>
       <c r="H114" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="I114" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J114" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>304</v>
+        <v>663</v>
       </c>
       <c r="B115" t="s">
-        <v>305</v>
+        <v>664</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F115" s="2">
+        <v>569</v>
+      </c>
+      <c r="F115" s="7">
         <v>60</v>
       </c>
       <c r="G115" t="s">
-        <v>472</v>
+        <v>665</v>
       </c>
       <c r="H115" t="s">
-        <v>693</v>
+        <v>666</v>
       </c>
       <c r="I115" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J115" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>306</v>
+        <v>684</v>
       </c>
       <c r="B116" t="s">
-        <v>307</v>
+        <v>685</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F116" s="2">
+        <v>569</v>
+      </c>
+      <c r="F116" s="7">
         <v>60</v>
       </c>
       <c r="G116" t="s">
-        <v>472</v>
+        <v>679</v>
       </c>
       <c r="H116" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="I116" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J116" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>308</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s">
-        <v>309</v>
+        <v>578</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F117" s="2">
+        <v>569</v>
+      </c>
+      <c r="F117" s="7">
         <v>60</v>
       </c>
       <c r="G117" t="s">
-        <v>472</v>
+        <v>570</v>
       </c>
       <c r="H117" t="s">
-        <v>693</v>
+        <v>576</v>
       </c>
       <c r="I117" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J117" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>310</v>
+        <v>574</v>
       </c>
       <c r="B118" t="s">
-        <v>311</v>
+        <v>575</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F118" s="2">
+        <v>569</v>
+      </c>
+      <c r="F118" s="7">
         <v>60</v>
       </c>
       <c r="G118" t="s">
-        <v>472</v>
+        <v>570</v>
       </c>
       <c r="H118" t="s">
-        <v>693</v>
+        <v>576</v>
       </c>
       <c r="I118" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J118" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>312</v>
+        <v>636</v>
       </c>
       <c r="B119" t="s">
-        <v>313</v>
+        <v>637</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F119" s="2">
+        <v>569</v>
+      </c>
+      <c r="F119" s="7">
         <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>472</v>
+        <v>634</v>
       </c>
       <c r="H119" t="s">
-        <v>693</v>
+        <v>635</v>
       </c>
       <c r="I119" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J119" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>314</v>
+        <v>632</v>
       </c>
       <c r="B120" t="s">
-        <v>315</v>
+        <v>633</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F120" s="2">
+        <v>569</v>
+      </c>
+      <c r="F120" s="7">
         <v>60</v>
       </c>
       <c r="G120" t="s">
-        <v>472</v>
+        <v>634</v>
       </c>
       <c r="H120" t="s">
-        <v>693</v>
+        <v>635</v>
       </c>
       <c r="I120" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J120" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>316</v>
+        <v>602</v>
       </c>
       <c r="B121" t="s">
-        <v>317</v>
+        <v>603</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F121" s="2">
+        <v>569</v>
+      </c>
+      <c r="F121" s="7">
         <v>60</v>
       </c>
       <c r="G121" t="s">
-        <v>472</v>
+        <v>604</v>
       </c>
       <c r="H121" t="s">
-        <v>693</v>
+        <v>605</v>
       </c>
       <c r="I121" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J121" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>318</v>
+        <v>650</v>
       </c>
       <c r="B122" t="s">
-        <v>319</v>
+        <v>651</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F122" s="2">
+        <v>569</v>
+      </c>
+      <c r="F122" s="7">
         <v>60</v>
       </c>
       <c r="G122" t="s">
-        <v>472</v>
+        <v>652</v>
       </c>
       <c r="H122" t="s">
-        <v>693</v>
+        <v>653</v>
       </c>
       <c r="I122" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J122" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>320</v>
+        <v>579</v>
       </c>
       <c r="B123" t="s">
-        <v>321</v>
+        <v>580</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F123" s="2">
+        <v>569</v>
+      </c>
+      <c r="F123" s="7">
         <v>60</v>
       </c>
       <c r="G123" t="s">
-        <v>472</v>
+        <v>570</v>
       </c>
       <c r="H123" t="s">
-        <v>693</v>
+        <v>581</v>
       </c>
       <c r="I123" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J123" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>322</v>
+        <v>654</v>
       </c>
       <c r="B124" t="s">
-        <v>323</v>
+        <v>655</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F124" s="2">
+        <v>569</v>
+      </c>
+      <c r="F124" s="7">
         <v>60</v>
       </c>
       <c r="G124" t="s">
-        <v>472</v>
+        <v>656</v>
       </c>
       <c r="H124" t="s">
-        <v>693</v>
+        <v>657</v>
       </c>
       <c r="I124" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J124" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>324</v>
+        <v>658</v>
       </c>
       <c r="B125" t="s">
-        <v>325</v>
+        <v>659</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F125" s="2">
+        <v>569</v>
+      </c>
+      <c r="F125" s="7">
         <v>60</v>
       </c>
       <c r="G125" t="s">
-        <v>472</v>
+        <v>656</v>
       </c>
       <c r="H125" t="s">
-        <v>693</v>
+        <v>657</v>
       </c>
       <c r="I125" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J125" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>326</v>
+        <v>571</v>
       </c>
       <c r="B126" t="s">
-        <v>327</v>
+        <v>572</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F126" s="2">
+        <v>569</v>
+      </c>
+      <c r="F126" s="7">
         <v>60</v>
       </c>
       <c r="G126" t="s">
-        <v>472</v>
+        <v>570</v>
       </c>
       <c r="H126" t="s">
-        <v>693</v>
+        <v>573</v>
       </c>
       <c r="I126" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J126" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>328</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s">
-        <v>329</v>
+        <v>594</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F127" s="2">
+        <v>569</v>
+      </c>
+      <c r="F127" s="7">
         <v>60</v>
       </c>
       <c r="G127" t="s">
-        <v>472</v>
+        <v>584</v>
       </c>
       <c r="H127" t="s">
-        <v>693</v>
+        <v>592</v>
       </c>
       <c r="I127" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J127" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>330</v>
+        <v>638</v>
       </c>
       <c r="B128" t="s">
-        <v>331</v>
+        <v>639</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F128" s="2">
+        <v>569</v>
+      </c>
+      <c r="F128" s="7">
         <v>60</v>
       </c>
       <c r="G128" t="s">
-        <v>472</v>
+        <v>640</v>
       </c>
       <c r="H128" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="I128" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J128" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>332</v>
+        <v>646</v>
       </c>
       <c r="B129" t="s">
-        <v>333</v>
+        <v>647</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F129" s="2">
+        <v>569</v>
+      </c>
+      <c r="F129" s="7">
         <v>60</v>
       </c>
       <c r="G129" t="s">
-        <v>472</v>
+        <v>648</v>
       </c>
       <c r="H129" t="s">
-        <v>693</v>
+        <v>649</v>
       </c>
       <c r="I129" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J129" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>334</v>
+        <v>670</v>
       </c>
       <c r="B130" t="s">
-        <v>335</v>
+        <v>671</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F130" s="2">
+        <v>569</v>
+      </c>
+      <c r="F130" s="7">
         <v>60</v>
       </c>
       <c r="G130" t="s">
-        <v>472</v>
+        <v>537</v>
       </c>
       <c r="H130" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="I130" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J130" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>336</v>
+        <v>687</v>
       </c>
       <c r="B131" t="s">
-        <v>337</v>
+        <v>688</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F131" s="2">
+        <v>569</v>
+      </c>
+      <c r="F131" s="7">
         <v>60</v>
       </c>
       <c r="G131" t="s">
-        <v>472</v>
+        <v>665</v>
       </c>
       <c r="H131" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="I131" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J131" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>338</v>
+        <v>660</v>
       </c>
       <c r="B132" t="s">
-        <v>339</v>
+        <v>661</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F132" s="2">
+        <v>569</v>
+      </c>
+      <c r="F132" s="7">
         <v>60</v>
       </c>
       <c r="G132" t="s">
-        <v>472</v>
+        <v>537</v>
       </c>
       <c r="H132" t="s">
-        <v>693</v>
+        <v>662</v>
       </c>
       <c r="I132" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J132" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>340</v>
+        <v>600</v>
       </c>
       <c r="B133" t="s">
-        <v>341</v>
+        <v>601</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F133" s="2">
+        <v>569</v>
+      </c>
+      <c r="F133" s="7">
         <v>60</v>
       </c>
       <c r="G133" t="s">
-        <v>472</v>
+        <v>597</v>
       </c>
       <c r="H133" t="s">
-        <v>693</v>
+        <v>597</v>
       </c>
       <c r="I133" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J133" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>342</v>
+        <v>595</v>
       </c>
       <c r="B134" t="s">
-        <v>343</v>
+        <v>596</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F134" s="2">
+        <v>569</v>
+      </c>
+      <c r="F134" s="7">
         <v>60</v>
       </c>
       <c r="G134" t="s">
-        <v>472</v>
+        <v>597</v>
       </c>
       <c r="H134" t="s">
-        <v>693</v>
+        <v>597</v>
       </c>
       <c r="I134" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J134" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>344</v>
+        <v>598</v>
       </c>
       <c r="B135" t="s">
-        <v>345</v>
+        <v>599</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F135" s="2">
+        <v>569</v>
+      </c>
+      <c r="F135" s="7">
         <v>60</v>
       </c>
       <c r="G135" t="s">
-        <v>472</v>
+        <v>597</v>
       </c>
       <c r="H135" t="s">
-        <v>693</v>
+        <v>597</v>
       </c>
       <c r="I135" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J135" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>346</v>
+        <v>642</v>
       </c>
       <c r="B136" t="s">
-        <v>347</v>
+        <v>643</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F136" s="2">
+        <v>569</v>
+      </c>
+      <c r="F136" s="7">
         <v>60</v>
       </c>
       <c r="G136" t="s">
-        <v>472</v>
+        <v>644</v>
       </c>
       <c r="H136" t="s">
-        <v>693</v>
+        <v>645</v>
       </c>
       <c r="I136" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J136" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>348</v>
+        <v>561</v>
       </c>
       <c r="B137" t="s">
-        <v>349</v>
+        <v>562</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>690</v>
+        <v>534</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>691</v>
+        <v>535</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F137" s="2">
+        <v>536</v>
+      </c>
+      <c r="F137" s="7">
         <v>60</v>
       </c>
       <c r="G137" t="s">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="H137" t="s">
-        <v>693</v>
+        <v>563</v>
       </c>
       <c r="I137" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J137" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>350</v>
+        <v>557</v>
       </c>
       <c r="B138" t="s">
-        <v>351</v>
+        <v>558</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>690</v>
+        <v>534</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>691</v>
+        <v>535</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F138" s="2">
+        <v>536</v>
+      </c>
+      <c r="F138" s="7">
         <v>60</v>
       </c>
       <c r="G138" t="s">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="H138" t="s">
-        <v>693</v>
+        <v>559</v>
       </c>
       <c r="I138" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J138" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="B139" t="s">
-        <v>353</v>
+        <v>291</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>690</v>
@@ -11275,8 +11725,8 @@
       <c r="E139" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F139" s="2">
-        <v>60</v>
+      <c r="F139" s="7">
+        <v>70</v>
       </c>
       <c r="G139" t="s">
         <v>472</v>
@@ -11288,12 +11738,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="B140" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>690</v>
@@ -11304,8 +11754,8 @@
       <c r="E140" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F140" s="2">
-        <v>60</v>
+      <c r="F140" s="7">
+        <v>70</v>
       </c>
       <c r="G140" t="s">
         <v>472</v>
@@ -11317,12 +11767,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="B141" t="s">
-        <v>357</v>
+        <v>295</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>690</v>
@@ -11333,8 +11783,8 @@
       <c r="E141" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F141" s="2">
-        <v>60</v>
+      <c r="F141" s="7">
+        <v>70</v>
       </c>
       <c r="G141" t="s">
         <v>472</v>
@@ -11346,12 +11796,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>358</v>
+        <v>296</v>
       </c>
       <c r="B142" t="s">
-        <v>359</v>
+        <v>297</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>690</v>
@@ -11362,8 +11812,8 @@
       <c r="E142" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F142" s="2">
-        <v>60</v>
+      <c r="F142" s="7">
+        <v>70</v>
       </c>
       <c r="G142" t="s">
         <v>472</v>
@@ -11375,12 +11825,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>360</v>
+        <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>690</v>
@@ -11391,8 +11841,8 @@
       <c r="E143" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F143" s="2">
-        <v>60</v>
+      <c r="F143" s="7">
+        <v>70</v>
       </c>
       <c r="G143" t="s">
         <v>472</v>
@@ -11404,12 +11854,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>363</v>
+        <v>301</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>690</v>
@@ -11420,8 +11870,8 @@
       <c r="E144" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F144" s="2">
-        <v>60</v>
+      <c r="F144" s="7">
+        <v>70</v>
       </c>
       <c r="G144" t="s">
         <v>472</v>
@@ -11435,10 +11885,10 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="B145" t="s">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>690</v>
@@ -11449,8 +11899,8 @@
       <c r="E145" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F145" s="2">
-        <v>60</v>
+      <c r="F145" s="7">
+        <v>70</v>
       </c>
       <c r="G145" t="s">
         <v>472</v>
@@ -11464,10 +11914,10 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>366</v>
+        <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>690</v>
@@ -11478,8 +11928,8 @@
       <c r="E146" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F146" s="2">
-        <v>60</v>
+      <c r="F146" s="7">
+        <v>70</v>
       </c>
       <c r="G146" t="s">
         <v>472</v>
@@ -11493,10 +11943,10 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="B147" t="s">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>690</v>
@@ -11507,8 +11957,8 @@
       <c r="E147" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F147" s="2">
-        <v>60</v>
+      <c r="F147" s="7">
+        <v>70</v>
       </c>
       <c r="G147" t="s">
         <v>472</v>
@@ -11522,10 +11972,10 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="B148" t="s">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>690</v>
@@ -11536,8 +11986,8 @@
       <c r="E148" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F148" s="2">
-        <v>60</v>
+      <c r="F148" s="7">
+        <v>70</v>
       </c>
       <c r="G148" t="s">
         <v>472</v>
@@ -11551,10 +12001,10 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>372</v>
+        <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>690</v>
@@ -11565,8 +12015,8 @@
       <c r="E149" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F149" s="2">
-        <v>60</v>
+      <c r="F149" s="7">
+        <v>70</v>
       </c>
       <c r="G149" t="s">
         <v>472</v>
@@ -11580,10 +12030,10 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>375</v>
+        <v>313</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>690</v>
@@ -11594,8 +12044,8 @@
       <c r="E150" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F150" s="2">
-        <v>60</v>
+      <c r="F150" s="7">
+        <v>70</v>
       </c>
       <c r="G150" t="s">
         <v>472</v>
@@ -11609,10 +12059,10 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="B151" t="s">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>690</v>
@@ -11623,8 +12073,8 @@
       <c r="E151" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F151" s="2">
-        <v>60</v>
+      <c r="F151" s="7">
+        <v>70</v>
       </c>
       <c r="G151" t="s">
         <v>472</v>
@@ -11638,10 +12088,10 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>378</v>
+        <v>316</v>
       </c>
       <c r="B152" t="s">
-        <v>379</v>
+        <v>317</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>690</v>
@@ -11652,8 +12102,8 @@
       <c r="E152" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F152" s="2">
-        <v>60</v>
+      <c r="F152" s="7">
+        <v>70</v>
       </c>
       <c r="G152" t="s">
         <v>472</v>
@@ -11667,10 +12117,10 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>380</v>
+        <v>318</v>
       </c>
       <c r="B153" t="s">
-        <v>381</v>
+        <v>319</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>690</v>
@@ -11681,8 +12131,8 @@
       <c r="E153" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F153" s="2">
-        <v>60</v>
+      <c r="F153" s="7">
+        <v>70</v>
       </c>
       <c r="G153" t="s">
         <v>472</v>
@@ -11696,10 +12146,10 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>382</v>
+        <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>690</v>
@@ -11710,8 +12160,8 @@
       <c r="E154" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F154" s="2">
-        <v>60</v>
+      <c r="F154" s="7">
+        <v>70</v>
       </c>
       <c r="G154" t="s">
         <v>472</v>
@@ -11725,10 +12175,10 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>384</v>
+        <v>322</v>
       </c>
       <c r="B155" t="s">
-        <v>385</v>
+        <v>323</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>690</v>
@@ -11739,8 +12189,8 @@
       <c r="E155" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F155" s="2">
-        <v>60</v>
+      <c r="F155" s="7">
+        <v>70</v>
       </c>
       <c r="G155" t="s">
         <v>472</v>
@@ -11754,10 +12204,10 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>386</v>
+        <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>387</v>
+        <v>325</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>690</v>
@@ -11768,8 +12218,8 @@
       <c r="E156" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F156" s="2">
-        <v>60</v>
+      <c r="F156" s="7">
+        <v>70</v>
       </c>
       <c r="G156" t="s">
         <v>472</v>
@@ -11783,10 +12233,10 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>388</v>
+        <v>326</v>
       </c>
       <c r="B157" t="s">
-        <v>389</v>
+        <v>327</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>690</v>
@@ -11797,8 +12247,8 @@
       <c r="E157" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F157" s="2">
-        <v>60</v>
+      <c r="F157" s="7">
+        <v>70</v>
       </c>
       <c r="G157" t="s">
         <v>472</v>
@@ -11812,10 +12262,10 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>390</v>
+        <v>328</v>
       </c>
       <c r="B158" t="s">
-        <v>391</v>
+        <v>329</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>690</v>
@@ -11826,8 +12276,8 @@
       <c r="E158" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F158" s="2">
-        <v>60</v>
+      <c r="F158" s="7">
+        <v>70</v>
       </c>
       <c r="G158" t="s">
         <v>472</v>
@@ -11841,10 +12291,10 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="B159" t="s">
-        <v>393</v>
+        <v>331</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>690</v>
@@ -11855,8 +12305,8 @@
       <c r="E159" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F159" s="2">
-        <v>60</v>
+      <c r="F159" s="7">
+        <v>70</v>
       </c>
       <c r="G159" t="s">
         <v>472</v>
@@ -11870,10 +12320,10 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="B160" t="s">
-        <v>395</v>
+        <v>333</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>690</v>
@@ -11884,8 +12334,8 @@
       <c r="E160" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F160" s="2">
-        <v>60</v>
+      <c r="F160" s="7">
+        <v>70</v>
       </c>
       <c r="G160" t="s">
         <v>472</v>
@@ -11899,10 +12349,10 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>396</v>
+        <v>334</v>
       </c>
       <c r="B161" t="s">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>690</v>
@@ -11913,8 +12363,8 @@
       <c r="E161" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F161" s="2">
-        <v>60</v>
+      <c r="F161" s="7">
+        <v>70</v>
       </c>
       <c r="G161" t="s">
         <v>472</v>
@@ -11928,10 +12378,10 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>398</v>
+        <v>336</v>
       </c>
       <c r="B162" t="s">
-        <v>399</v>
+        <v>337</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>690</v>
@@ -11942,8 +12392,8 @@
       <c r="E162" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F162" s="2">
-        <v>60</v>
+      <c r="F162" s="7">
+        <v>70</v>
       </c>
       <c r="G162" t="s">
         <v>472</v>
@@ -11957,10 +12407,10 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>400</v>
+        <v>338</v>
       </c>
       <c r="B163" t="s">
-        <v>401</v>
+        <v>339</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>690</v>
@@ -11971,8 +12421,8 @@
       <c r="E163" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F163" s="2">
-        <v>60</v>
+      <c r="F163" s="7">
+        <v>70</v>
       </c>
       <c r="G163" t="s">
         <v>472</v>
@@ -11986,10 +12436,10 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>402</v>
+        <v>340</v>
       </c>
       <c r="B164" t="s">
-        <v>403</v>
+        <v>341</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>690</v>
@@ -12000,8 +12450,8 @@
       <c r="E164" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F164" s="2">
-        <v>60</v>
+      <c r="F164" s="7">
+        <v>70</v>
       </c>
       <c r="G164" t="s">
         <v>472</v>
@@ -12015,10 +12465,10 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>404</v>
+        <v>342</v>
       </c>
       <c r="B165" t="s">
-        <v>405</v>
+        <v>343</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>690</v>
@@ -12029,8 +12479,8 @@
       <c r="E165" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F165" s="2">
-        <v>60</v>
+      <c r="F165" s="7">
+        <v>70</v>
       </c>
       <c r="G165" t="s">
         <v>472</v>
@@ -12044,10 +12494,10 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>406</v>
+        <v>344</v>
       </c>
       <c r="B166" t="s">
-        <v>407</v>
+        <v>345</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>690</v>
@@ -12058,8 +12508,8 @@
       <c r="E166" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F166" s="2">
-        <v>60</v>
+      <c r="F166" s="7">
+        <v>70</v>
       </c>
       <c r="G166" t="s">
         <v>472</v>
@@ -12073,10 +12523,10 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>408</v>
+        <v>346</v>
       </c>
       <c r="B167" t="s">
-        <v>409</v>
+        <v>347</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>690</v>
@@ -12087,8 +12537,8 @@
       <c r="E167" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F167" s="2">
-        <v>60</v>
+      <c r="F167" s="7">
+        <v>70</v>
       </c>
       <c r="G167" t="s">
         <v>472</v>
@@ -12102,10 +12552,10 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>410</v>
+        <v>348</v>
       </c>
       <c r="B168" t="s">
-        <v>411</v>
+        <v>349</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>690</v>
@@ -12116,8 +12566,8 @@
       <c r="E168" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F168" s="2">
-        <v>60</v>
+      <c r="F168" s="7">
+        <v>70</v>
       </c>
       <c r="G168" t="s">
         <v>472</v>
@@ -12131,10 +12581,10 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>412</v>
+        <v>350</v>
       </c>
       <c r="B169" t="s">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>690</v>
@@ -12145,8 +12595,8 @@
       <c r="E169" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F169" s="2">
-        <v>60</v>
+      <c r="F169" s="7">
+        <v>70</v>
       </c>
       <c r="G169" t="s">
         <v>472</v>
@@ -12160,10 +12610,10 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>414</v>
+        <v>352</v>
       </c>
       <c r="B170" t="s">
-        <v>415</v>
+        <v>353</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>690</v>
@@ -12174,8 +12624,8 @@
       <c r="E170" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F170" s="2">
-        <v>60</v>
+      <c r="F170" s="7">
+        <v>70</v>
       </c>
       <c r="G170" t="s">
         <v>472</v>
@@ -12189,10 +12639,10 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>416</v>
+        <v>354</v>
       </c>
       <c r="B171" t="s">
-        <v>417</v>
+        <v>355</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>690</v>
@@ -12203,8 +12653,8 @@
       <c r="E171" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F171" s="2">
-        <v>60</v>
+      <c r="F171" s="7">
+        <v>70</v>
       </c>
       <c r="G171" t="s">
         <v>472</v>
@@ -12218,10 +12668,10 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>418</v>
+        <v>356</v>
       </c>
       <c r="B172" t="s">
-        <v>419</v>
+        <v>357</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>690</v>
@@ -12232,8 +12682,8 @@
       <c r="E172" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F172" s="2">
-        <v>60</v>
+      <c r="F172" s="7">
+        <v>70</v>
       </c>
       <c r="G172" t="s">
         <v>472</v>
@@ -12247,10 +12697,10 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>420</v>
+        <v>358</v>
       </c>
       <c r="B173" t="s">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>690</v>
@@ -12261,8 +12711,8 @@
       <c r="E173" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F173" s="2">
-        <v>60</v>
+      <c r="F173" s="7">
+        <v>70</v>
       </c>
       <c r="G173" t="s">
         <v>472</v>
@@ -12276,10 +12726,10 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>422</v>
+        <v>360</v>
       </c>
       <c r="B174" t="s">
-        <v>423</v>
+        <v>361</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>690</v>
@@ -12290,8 +12740,8 @@
       <c r="E174" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F174" s="2">
-        <v>60</v>
+      <c r="F174" s="7">
+        <v>70</v>
       </c>
       <c r="G174" t="s">
         <v>472</v>
@@ -12305,10 +12755,10 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>424</v>
+        <v>362</v>
       </c>
       <c r="B175" t="s">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>690</v>
@@ -12319,8 +12769,8 @@
       <c r="E175" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F175" s="2">
-        <v>60</v>
+      <c r="F175" s="7">
+        <v>70</v>
       </c>
       <c r="G175" t="s">
         <v>472</v>
@@ -12334,10 +12784,10 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="B176" t="s">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>690</v>
@@ -12348,8 +12798,8 @@
       <c r="E176" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F176" s="2">
-        <v>60</v>
+      <c r="F176" s="7">
+        <v>70</v>
       </c>
       <c r="G176" t="s">
         <v>472</v>
@@ -12363,10 +12813,10 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>428</v>
+        <v>366</v>
       </c>
       <c r="B177" t="s">
-        <v>429</v>
+        <v>367</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>690</v>
@@ -12377,8 +12827,8 @@
       <c r="E177" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F177" s="2">
-        <v>60</v>
+      <c r="F177" s="7">
+        <v>70</v>
       </c>
       <c r="G177" t="s">
         <v>472</v>
@@ -12392,10 +12842,10 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>430</v>
+        <v>368</v>
       </c>
       <c r="B178" t="s">
-        <v>431</v>
+        <v>369</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>690</v>
@@ -12406,8 +12856,8 @@
       <c r="E178" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F178" s="2">
-        <v>60</v>
+      <c r="F178" s="7">
+        <v>70</v>
       </c>
       <c r="G178" t="s">
         <v>472</v>
@@ -12421,10 +12871,10 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>432</v>
+        <v>370</v>
       </c>
       <c r="B179" t="s">
-        <v>433</v>
+        <v>371</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>690</v>
@@ -12435,8 +12885,8 @@
       <c r="E179" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F179" s="2">
-        <v>60</v>
+      <c r="F179" s="7">
+        <v>70</v>
       </c>
       <c r="G179" t="s">
         <v>472</v>
@@ -12450,10 +12900,10 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="B180" t="s">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>690</v>
@@ -12464,8 +12914,8 @@
       <c r="E180" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F180" s="2">
-        <v>60</v>
+      <c r="F180" s="7">
+        <v>70</v>
       </c>
       <c r="G180" t="s">
         <v>472</v>
@@ -12479,10 +12929,10 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>436</v>
+        <v>374</v>
       </c>
       <c r="B181" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>690</v>
@@ -12493,8 +12943,8 @@
       <c r="E181" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F181" s="2">
-        <v>60</v>
+      <c r="F181" s="7">
+        <v>70</v>
       </c>
       <c r="G181" t="s">
         <v>472</v>
@@ -12508,10 +12958,10 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>438</v>
+        <v>376</v>
       </c>
       <c r="B182" t="s">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>690</v>
@@ -12522,8 +12972,8 @@
       <c r="E182" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F182" s="2">
-        <v>60</v>
+      <c r="F182" s="7">
+        <v>70</v>
       </c>
       <c r="G182" t="s">
         <v>472</v>
@@ -12537,10 +12987,10 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>440</v>
+        <v>378</v>
       </c>
       <c r="B183" t="s">
-        <v>441</v>
+        <v>379</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>690</v>
@@ -12551,8 +13001,8 @@
       <c r="E183" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F183" s="2">
-        <v>60</v>
+      <c r="F183" s="7">
+        <v>70</v>
       </c>
       <c r="G183" t="s">
         <v>472</v>
@@ -12566,10 +13016,10 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="B184" t="s">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>690</v>
@@ -12580,8 +13030,8 @@
       <c r="E184" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F184" s="2">
-        <v>60</v>
+      <c r="F184" s="7">
+        <v>70</v>
       </c>
       <c r="G184" t="s">
         <v>472</v>
@@ -12595,10 +13045,10 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>444</v>
+        <v>382</v>
       </c>
       <c r="B185" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>690</v>
@@ -12609,8 +13059,8 @@
       <c r="E185" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F185" s="2">
-        <v>60</v>
+      <c r="F185" s="7">
+        <v>70</v>
       </c>
       <c r="G185" t="s">
         <v>472</v>
@@ -12624,10 +13074,10 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>446</v>
+        <v>384</v>
       </c>
       <c r="B186" t="s">
-        <v>447</v>
+        <v>385</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>690</v>
@@ -12638,8 +13088,8 @@
       <c r="E186" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F186" s="2">
-        <v>60</v>
+      <c r="F186" s="7">
+        <v>70</v>
       </c>
       <c r="G186" t="s">
         <v>472</v>
@@ -12653,10 +13103,10 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>448</v>
+        <v>386</v>
       </c>
       <c r="B187" t="s">
-        <v>449</v>
+        <v>387</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>690</v>
@@ -12667,8 +13117,8 @@
       <c r="E187" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F187" s="2">
-        <v>60</v>
+      <c r="F187" s="7">
+        <v>70</v>
       </c>
       <c r="G187" t="s">
         <v>472</v>
@@ -12682,10 +13132,10 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
       <c r="B188" t="s">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>690</v>
@@ -12696,8 +13146,8 @@
       <c r="E188" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F188" s="2">
-        <v>60</v>
+      <c r="F188" s="7">
+        <v>70</v>
       </c>
       <c r="G188" t="s">
         <v>472</v>
@@ -12711,10 +13161,10 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>452</v>
+        <v>390</v>
       </c>
       <c r="B189" t="s">
-        <v>453</v>
+        <v>391</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>690</v>
@@ -12725,8 +13175,8 @@
       <c r="E189" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F189" s="2">
-        <v>60</v>
+      <c r="F189" s="7">
+        <v>70</v>
       </c>
       <c r="G189" t="s">
         <v>472</v>
@@ -12740,10 +13190,10 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>454</v>
+        <v>392</v>
       </c>
       <c r="B190" t="s">
-        <v>455</v>
+        <v>393</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>690</v>
@@ -12754,8 +13204,8 @@
       <c r="E190" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F190" s="2">
-        <v>60</v>
+      <c r="F190" s="7">
+        <v>70</v>
       </c>
       <c r="G190" t="s">
         <v>472</v>
@@ -12769,10 +13219,10 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B191" t="s">
-        <v>457</v>
+        <v>395</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>690</v>
@@ -12783,8 +13233,8 @@
       <c r="E191" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F191" s="2">
-        <v>60</v>
+      <c r="F191" s="7">
+        <v>70</v>
       </c>
       <c r="G191" t="s">
         <v>472</v>
@@ -12798,10 +13248,10 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>458</v>
+        <v>396</v>
       </c>
       <c r="B192" t="s">
-        <v>459</v>
+        <v>397</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>690</v>
@@ -12812,8 +13262,8 @@
       <c r="E192" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F192" s="2">
-        <v>60</v>
+      <c r="F192" s="7">
+        <v>70</v>
       </c>
       <c r="G192" t="s">
         <v>472</v>
@@ -12827,10 +13277,10 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>460</v>
+        <v>398</v>
       </c>
       <c r="B193" t="s">
-        <v>461</v>
+        <v>399</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>690</v>
@@ -12841,8 +13291,8 @@
       <c r="E193" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F193" s="2">
-        <v>60</v>
+      <c r="F193" s="7">
+        <v>70</v>
       </c>
       <c r="G193" t="s">
         <v>472</v>
@@ -12856,10 +13306,10 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>462</v>
+        <v>400</v>
       </c>
       <c r="B194" t="s">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>690</v>
@@ -12870,8 +13320,8 @@
       <c r="E194" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F194" s="2">
-        <v>60</v>
+      <c r="F194" s="7">
+        <v>70</v>
       </c>
       <c r="G194" t="s">
         <v>472</v>
@@ -12885,10 +13335,10 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="B195" t="s">
-        <v>465</v>
+        <v>403</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>690</v>
@@ -12899,8 +13349,8 @@
       <c r="E195" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F195" s="2">
-        <v>60</v>
+      <c r="F195" s="7">
+        <v>70</v>
       </c>
       <c r="G195" t="s">
         <v>472</v>
@@ -12914,10 +13364,10 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
       <c r="B196" t="s">
-        <v>467</v>
+        <v>405</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>690</v>
@@ -12928,8 +13378,8 @@
       <c r="E196" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F196" s="2">
-        <v>60</v>
+      <c r="F196" s="7">
+        <v>70</v>
       </c>
       <c r="G196" t="s">
         <v>472</v>
@@ -12943,10 +13393,10 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>468</v>
+        <v>406</v>
       </c>
       <c r="B197" t="s">
-        <v>469</v>
+        <v>407</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>690</v>
@@ -12957,8 +13407,8 @@
       <c r="E197" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F197" s="2">
-        <v>60</v>
+      <c r="F197" s="7">
+        <v>70</v>
       </c>
       <c r="G197" t="s">
         <v>472</v>
@@ -12972,10 +13422,10 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="B198" t="s">
-        <v>471</v>
+        <v>409</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>690</v>
@@ -12986,8 +13436,8 @@
       <c r="E198" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F198" s="2">
-        <v>60</v>
+      <c r="F198" s="7">
+        <v>70</v>
       </c>
       <c r="G198" t="s">
         <v>472</v>
@@ -12996,6 +13446,905 @@
         <v>693</v>
       </c>
       <c r="I198" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>410</v>
+      </c>
+      <c r="B199" t="s">
+        <v>411</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F199" s="7">
+        <v>70</v>
+      </c>
+      <c r="G199" t="s">
+        <v>472</v>
+      </c>
+      <c r="H199" t="s">
+        <v>693</v>
+      </c>
+      <c r="I199" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>412</v>
+      </c>
+      <c r="B200" t="s">
+        <v>413</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F200" s="7">
+        <v>70</v>
+      </c>
+      <c r="G200" t="s">
+        <v>472</v>
+      </c>
+      <c r="H200" t="s">
+        <v>693</v>
+      </c>
+      <c r="I200" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>414</v>
+      </c>
+      <c r="B201" t="s">
+        <v>415</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F201" s="7">
+        <v>70</v>
+      </c>
+      <c r="G201" t="s">
+        <v>472</v>
+      </c>
+      <c r="H201" t="s">
+        <v>693</v>
+      </c>
+      <c r="I201" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>416</v>
+      </c>
+      <c r="B202" t="s">
+        <v>417</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F202" s="7">
+        <v>70</v>
+      </c>
+      <c r="G202" t="s">
+        <v>472</v>
+      </c>
+      <c r="H202" t="s">
+        <v>693</v>
+      </c>
+      <c r="I202" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>418</v>
+      </c>
+      <c r="B203" t="s">
+        <v>419</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F203" s="7">
+        <v>70</v>
+      </c>
+      <c r="G203" t="s">
+        <v>472</v>
+      </c>
+      <c r="H203" t="s">
+        <v>693</v>
+      </c>
+      <c r="I203" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>420</v>
+      </c>
+      <c r="B204" t="s">
+        <v>421</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F204" s="7">
+        <v>70</v>
+      </c>
+      <c r="G204" t="s">
+        <v>472</v>
+      </c>
+      <c r="H204" t="s">
+        <v>693</v>
+      </c>
+      <c r="I204" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>422</v>
+      </c>
+      <c r="B205" t="s">
+        <v>423</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F205" s="7">
+        <v>70</v>
+      </c>
+      <c r="G205" t="s">
+        <v>472</v>
+      </c>
+      <c r="H205" t="s">
+        <v>693</v>
+      </c>
+      <c r="I205" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>424</v>
+      </c>
+      <c r="B206" t="s">
+        <v>425</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F206" s="7">
+        <v>70</v>
+      </c>
+      <c r="G206" t="s">
+        <v>472</v>
+      </c>
+      <c r="H206" t="s">
+        <v>693</v>
+      </c>
+      <c r="I206" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>426</v>
+      </c>
+      <c r="B207" t="s">
+        <v>427</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F207" s="7">
+        <v>70</v>
+      </c>
+      <c r="G207" t="s">
+        <v>472</v>
+      </c>
+      <c r="H207" t="s">
+        <v>693</v>
+      </c>
+      <c r="I207" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>428</v>
+      </c>
+      <c r="B208" t="s">
+        <v>429</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F208" s="7">
+        <v>70</v>
+      </c>
+      <c r="G208" t="s">
+        <v>472</v>
+      </c>
+      <c r="H208" t="s">
+        <v>693</v>
+      </c>
+      <c r="I208" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>430</v>
+      </c>
+      <c r="B209" t="s">
+        <v>431</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F209" s="7">
+        <v>70</v>
+      </c>
+      <c r="G209" t="s">
+        <v>472</v>
+      </c>
+      <c r="H209" t="s">
+        <v>693</v>
+      </c>
+      <c r="I209" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>432</v>
+      </c>
+      <c r="B210" t="s">
+        <v>433</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F210" s="7">
+        <v>70</v>
+      </c>
+      <c r="G210" t="s">
+        <v>472</v>
+      </c>
+      <c r="H210" t="s">
+        <v>693</v>
+      </c>
+      <c r="I210" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>434</v>
+      </c>
+      <c r="B211" t="s">
+        <v>435</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F211" s="7">
+        <v>70</v>
+      </c>
+      <c r="G211" t="s">
+        <v>472</v>
+      </c>
+      <c r="H211" t="s">
+        <v>693</v>
+      </c>
+      <c r="I211" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>436</v>
+      </c>
+      <c r="B212" t="s">
+        <v>437</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F212" s="7">
+        <v>70</v>
+      </c>
+      <c r="G212" t="s">
+        <v>472</v>
+      </c>
+      <c r="H212" t="s">
+        <v>693</v>
+      </c>
+      <c r="I212" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>438</v>
+      </c>
+      <c r="B213" t="s">
+        <v>439</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F213" s="7">
+        <v>70</v>
+      </c>
+      <c r="G213" t="s">
+        <v>472</v>
+      </c>
+      <c r="H213" t="s">
+        <v>693</v>
+      </c>
+      <c r="I213" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>440</v>
+      </c>
+      <c r="B214" t="s">
+        <v>441</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F214" s="7">
+        <v>70</v>
+      </c>
+      <c r="G214" t="s">
+        <v>472</v>
+      </c>
+      <c r="H214" t="s">
+        <v>693</v>
+      </c>
+      <c r="I214" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>442</v>
+      </c>
+      <c r="B215" t="s">
+        <v>443</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F215" s="7">
+        <v>70</v>
+      </c>
+      <c r="G215" t="s">
+        <v>472</v>
+      </c>
+      <c r="H215" t="s">
+        <v>693</v>
+      </c>
+      <c r="I215" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>444</v>
+      </c>
+      <c r="B216" t="s">
+        <v>445</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F216" s="7">
+        <v>70</v>
+      </c>
+      <c r="G216" t="s">
+        <v>472</v>
+      </c>
+      <c r="H216" t="s">
+        <v>693</v>
+      </c>
+      <c r="I216" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>446</v>
+      </c>
+      <c r="B217" t="s">
+        <v>447</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F217" s="7">
+        <v>70</v>
+      </c>
+      <c r="G217" t="s">
+        <v>472</v>
+      </c>
+      <c r="H217" t="s">
+        <v>693</v>
+      </c>
+      <c r="I217" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>448</v>
+      </c>
+      <c r="B218" t="s">
+        <v>449</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F218" s="7">
+        <v>70</v>
+      </c>
+      <c r="G218" t="s">
+        <v>472</v>
+      </c>
+      <c r="H218" t="s">
+        <v>693</v>
+      </c>
+      <c r="I218" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>450</v>
+      </c>
+      <c r="B219" t="s">
+        <v>451</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F219" s="7">
+        <v>70</v>
+      </c>
+      <c r="G219" t="s">
+        <v>472</v>
+      </c>
+      <c r="H219" t="s">
+        <v>693</v>
+      </c>
+      <c r="I219" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>452</v>
+      </c>
+      <c r="B220" t="s">
+        <v>453</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F220" s="7">
+        <v>70</v>
+      </c>
+      <c r="G220" t="s">
+        <v>472</v>
+      </c>
+      <c r="H220" t="s">
+        <v>693</v>
+      </c>
+      <c r="I220" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>454</v>
+      </c>
+      <c r="B221" t="s">
+        <v>455</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F221" s="7">
+        <v>70</v>
+      </c>
+      <c r="G221" t="s">
+        <v>472</v>
+      </c>
+      <c r="H221" t="s">
+        <v>693</v>
+      </c>
+      <c r="I221" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>456</v>
+      </c>
+      <c r="B222" t="s">
+        <v>457</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F222" s="7">
+        <v>70</v>
+      </c>
+      <c r="G222" t="s">
+        <v>472</v>
+      </c>
+      <c r="H222" t="s">
+        <v>693</v>
+      </c>
+      <c r="I222" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>458</v>
+      </c>
+      <c r="B223" t="s">
+        <v>459</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F223" s="7">
+        <v>70</v>
+      </c>
+      <c r="G223" t="s">
+        <v>472</v>
+      </c>
+      <c r="H223" t="s">
+        <v>693</v>
+      </c>
+      <c r="I223" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>460</v>
+      </c>
+      <c r="B224" t="s">
+        <v>461</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F224" s="7">
+        <v>70</v>
+      </c>
+      <c r="G224" t="s">
+        <v>472</v>
+      </c>
+      <c r="H224" t="s">
+        <v>693</v>
+      </c>
+      <c r="I224" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>462</v>
+      </c>
+      <c r="B225" t="s">
+        <v>463</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F225" s="7">
+        <v>70</v>
+      </c>
+      <c r="G225" t="s">
+        <v>472</v>
+      </c>
+      <c r="H225" t="s">
+        <v>693</v>
+      </c>
+      <c r="I225" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>464</v>
+      </c>
+      <c r="B226" t="s">
+        <v>465</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F226" s="7">
+        <v>70</v>
+      </c>
+      <c r="G226" t="s">
+        <v>472</v>
+      </c>
+      <c r="H226" t="s">
+        <v>693</v>
+      </c>
+      <c r="I226" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>466</v>
+      </c>
+      <c r="B227" t="s">
+        <v>467</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F227" s="7">
+        <v>70</v>
+      </c>
+      <c r="G227" t="s">
+        <v>472</v>
+      </c>
+      <c r="H227" t="s">
+        <v>693</v>
+      </c>
+      <c r="I227" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>468</v>
+      </c>
+      <c r="B228" t="s">
+        <v>469</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F228" s="7">
+        <v>70</v>
+      </c>
+      <c r="G228" t="s">
+        <v>472</v>
+      </c>
+      <c r="H228" t="s">
+        <v>693</v>
+      </c>
+      <c r="I228" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>470</v>
+      </c>
+      <c r="B229" t="s">
+        <v>471</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F229" s="7">
+        <v>70</v>
+      </c>
+      <c r="G229" t="s">
+        <v>472</v>
+      </c>
+      <c r="H229" t="s">
+        <v>693</v>
+      </c>
+      <c r="I229" t="s">
         <v>694</v>
       </c>
     </row>
@@ -13010,10 +14359,404 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBCCFDC-4EB7-4695-AF08-ED1833819D06}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="128" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C1" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>853</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/Support/links_documents_EXCEL.xlsx
+++ b/Support/links_documents_EXCEL.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://msss365-my.sharepoint.com/personal/vincent_desrochers_med_ssss_gouv_qc_ca/Documents/Programmation/Git-Hub/emtools/Support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D7C9706-0417-41AB-B8CA-A13D00566971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{9D7C9706-0417-41AB-B8CA-A13D00566971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E617B630-AC09-4F88-BDC1-97914BCA67F8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5A9E7570-B546-46BC-9B1E-C8C8D4DF09A1}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{5A9E7570-B546-46BC-9B1E-C8C8D4DF09A1}"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
     <sheet name="links (2)" sheetId="3" r:id="rId2"/>
     <sheet name="links_documents_csv" sheetId="4" r:id="rId3"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId4"/>
+    <sheet name="Lien brisés" sheetId="6" r:id="rId4"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="DonnéesExternes_1" localSheetId="1" hidden="1">'links (2)'!$A$1:$E$92</definedName>
-    <definedName name="DonnéesExternes_1" localSheetId="2" hidden="1">links_documents_csv!$A$1:$J$229</definedName>
+    <definedName name="DonnéesExternes_1" localSheetId="2" hidden="1">links_documents_csv!$A$1:$J$233</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2656" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="955">
   <si>
     <t>link_text,url,source_page,link_type,collected_at</t>
   </si>
@@ -2874,13 +2875,55 @@
   </si>
   <si>
     <t>Prescription</t>
+  </si>
+  <si>
+    <t>https://bibliotheques.cissslaval.ca/Record.htm?idlist=1&amp;record=19351472124911796549</t>
+  </si>
+  <si>
+    <t>Liste des liens brisés</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Bundle colique néphrétique</t>
+  </si>
+  <si>
+    <t>Bundle Pneumonie</t>
+  </si>
+  <si>
+    <t>Support/Bundle_pneumonie.pdf</t>
+  </si>
+  <si>
+    <t>Support/Bundle_CN.pdf</t>
+  </si>
+  <si>
+    <t>Pneumonie, suivi, bundle</t>
+  </si>
+  <si>
+    <t>Colique, nephretique, néphrétique, suivi, bundle</t>
+  </si>
+  <si>
+    <t>Bundle CNESST</t>
+  </si>
+  <si>
+    <t>Bundle_CNESST.pdf</t>
+  </si>
+  <si>
+    <t>Bundle SAAQ</t>
+  </si>
+  <si>
+    <t>Bundle_SAAQ.pdf</t>
+  </si>
+  <si>
+    <t>SAAQ, Bundle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3017,6 +3060,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3389,9 +3439,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3439,15 +3487,30 @@
   </cellStyles>
   <dxfs count="16">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="27" formatCode="yyyy/mm/dd\ hh:mm"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3464,30 +3527,15 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="27" formatCode="yyyy/mm/dd\ hh:mm"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4138,42 +4186,53 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DE1A692-D182-48B1-AF24-B08C3BADDDB7}" name="links" displayName="links" ref="A1:E92" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E92" xr:uid="{6DE1A692-D182-48B1-AF24-B08C3BADDDB7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8BEA4C21-4044-4079-9E1A-527E856DC298}" uniqueName="1" name="link_text" queryTableFieldId="1" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{7C65E6FF-1686-4FDD-96F3-2AD9E0FDF1F8}" uniqueName="2" name="url" queryTableFieldId="2" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{18BB0FCF-509C-47E0-A822-E32F6857A439}" uniqueName="3" name="source_page" queryTableFieldId="3" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{4A776295-DFD0-4A4F-A121-D0FF62704E6D}" uniqueName="4" name="link_type" queryTableFieldId="4" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{1C6E3148-D1F4-4F60-8957-153FC9DBB625}" uniqueName="5" name="collected_at" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8BEA4C21-4044-4079-9E1A-527E856DC298}" uniqueName="1" name="link_text" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7C65E6FF-1686-4FDD-96F3-2AD9E0FDF1F8}" uniqueName="2" name="url" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{18BB0FCF-509C-47E0-A822-E32F6857A439}" uniqueName="3" name="source_page" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{4A776295-DFD0-4A4F-A121-D0FF62704E6D}" uniqueName="4" name="link_type" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{1C6E3148-D1F4-4F60-8957-153FC9DBB625}" uniqueName="5" name="collected_at" queryTableFieldId="5" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}" name="links_documents" displayName="links_documents" ref="A1:K229" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:K229" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J229">
-    <sortCondition ref="F2:F229"/>
-    <sortCondition ref="E2:E229"/>
-    <sortCondition ref="A2:A229"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}" name="links_documents" displayName="links_documents" ref="A1:K233" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:K233" xr:uid="{3FD28E63-B293-4805-B0E0-3021DBF1AD62}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K233">
+    <sortCondition ref="F4:F233"/>
+    <sortCondition ref="E4:E233"/>
+    <sortCondition ref="A4:A233"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{487E3CF9-4E9F-41C4-A553-12FE09D4D914}" uniqueName="1" name="title" queryTableFieldId="1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{8F61F6E0-4133-42A5-924D-8BD507F4F59B}" uniqueName="2" name="href" queryTableFieldId="2" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{0BDB0DFA-9C44-44B4-9B3D-A67A9A379DFB}" uniqueName="3" name="section" queryTableFieldId="3" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{FAE5E803-4030-4058-89B4-85BD5D0DC6D9}" uniqueName="4" name="sectionTitle" queryTableFieldId="4" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{30F11EB6-BDD8-4CE0-8231-A45CF3C5D1BF}" uniqueName="5" name="sectionDescription" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{8AB440D0-3289-4225-8E8C-4A5AAAE34C2E}" uniqueName="6" name="sectionOrder" queryTableFieldId="6" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{C58EA5C6-C560-40F5-89D2-88E731450954}" uniqueName="7" name="category" queryTableFieldId="7" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{5329A6F8-5583-41CC-A1B7-F1DE77D80783}" uniqueName="8" name="tags" queryTableFieldId="8" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{487E3CF9-4E9F-41C4-A553-12FE09D4D914}" uniqueName="1" name="title" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{8F61F6E0-4133-42A5-924D-8BD507F4F59B}" uniqueName="2" name="href" queryTableFieldId="2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{0BDB0DFA-9C44-44B4-9B3D-A67A9A379DFB}" uniqueName="3" name="section" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{FAE5E803-4030-4058-89B4-85BD5D0DC6D9}" uniqueName="4" name="sectionTitle" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{30F11EB6-BDD8-4CE0-8231-A45CF3C5D1BF}" uniqueName="5" name="sectionDescription" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{8AB440D0-3289-4225-8E8C-4A5AAAE34C2E}" uniqueName="6" name="sectionOrder" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{C58EA5C6-C560-40F5-89D2-88E731450954}" uniqueName="7" name="category" queryTableFieldId="7" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{5329A6F8-5583-41CC-A1B7-F1DE77D80783}" uniqueName="8" name="tags" queryTableFieldId="8" dataDxfId="8"/>
     <tableColumn id="9" xr3:uid="{0E27ED48-B958-4B99-88D7-05C34895B6F5}" uniqueName="9" name="targetBlank" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{69081A57-C339-43AB-A50E-1E99EDDAE734}" uniqueName="10" name="description" queryTableFieldId="10" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{68A00987-CE71-4C1B-83A8-B8CEAACB9505}" uniqueName="11" name="Colonne1" queryTableFieldId="602" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{69081A57-C339-43AB-A50E-1E99EDDAE734}" uniqueName="10" name="description" queryTableFieldId="10" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{68A00987-CE71-4C1B-83A8-B8CEAACB9505}" uniqueName="11" name="Colonne1" queryTableFieldId="602" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5C1BEDD6-6E67-4BB7-86E3-2008D05D0C65}" name="Tableau2" displayName="Tableau2" ref="A4:B5" totalsRowShown="0">
+  <autoFilter ref="A4:B5" xr:uid="{5C1BEDD6-6E67-4BB7-86E3-2008D05D0C65}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1048F849-D3CE-431B-9EEB-38E66844127A}" name="Titre"/>
+    <tableColumn id="2" xr3:uid="{C09978AD-63A5-44FF-8D99-F18F71E81946}" name="Lien"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{96FFDA27-F17C-417C-A872-BC88B6B2B219}" name="Tableau1" displayName="Tableau1" ref="A1:C35" totalsRowShown="0">
   <autoFilter ref="A1:C35" xr:uid="{96FFDA27-F17C-417C-A872-BC88B6B2B219}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B35">
@@ -4182,7 +4241,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3F17AB22-4B4B-4B6A-AC7B-931C40870137}" name="Titre"/>
     <tableColumn id="3" xr3:uid="{9A80956E-A774-4285-883E-39073F9F2F2F}" name="Commentaire"/>
-    <tableColumn id="4" xr3:uid="{3EF12785-53A1-4C6A-B7FE-D9F3BCA0E4D6}" name="Lien" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{3EF12785-53A1-4C6A-B7FE-D9F3BCA0E4D6}" name="Lien" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7509,7 +7568,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FCBDD6-984D-408F-975A-1DE93A8BC72E}">
-  <dimension ref="A1:K229"/>
+  <dimension ref="A1:K233"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.42578125" customWidth="1"/>
@@ -7575,7 +7634,7 @@
       <c r="E2" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="2">
         <v>10</v>
       </c>
       <c r="G2" t="s">
@@ -7604,7 +7663,7 @@
       <c r="E3" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="2">
         <v>10</v>
       </c>
       <c r="G3" t="s">
@@ -7633,7 +7692,7 @@
       <c r="E4" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="2">
         <v>10</v>
       </c>
       <c r="G4" t="s">
@@ -7659,7 +7718,7 @@
       <c r="E5" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="2">
         <v>10</v>
       </c>
       <c r="G5" t="s">
@@ -7688,7 +7747,7 @@
       <c r="E6" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="2">
         <v>10</v>
       </c>
       <c r="G6" t="s">
@@ -7717,7 +7776,7 @@
       <c r="E7" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="2">
         <v>10</v>
       </c>
       <c r="G7" t="s">
@@ -7746,7 +7805,7 @@
       <c r="E8" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="2">
         <v>10</v>
       </c>
       <c r="G8" t="s">
@@ -7775,7 +7834,7 @@
       <c r="E9" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="2">
         <v>10</v>
       </c>
       <c r="G9" t="s">
@@ -7790,10 +7849,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>783</v>
+        <v>944</v>
       </c>
       <c r="B10" t="s">
-        <v>720</v>
+        <v>947</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>730</v>
@@ -7804,14 +7863,14 @@
       <c r="E10" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="2">
         <v>10</v>
       </c>
       <c r="G10" t="s">
         <v>708</v>
       </c>
       <c r="H10" t="s">
-        <v>761</v>
+        <v>949</v>
       </c>
       <c r="I10" t="s">
         <v>694</v>
@@ -7819,10 +7878,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>784</v>
+        <v>945</v>
       </c>
       <c r="B11" t="s">
-        <v>715</v>
+        <v>946</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>730</v>
@@ -7833,14 +7892,14 @@
       <c r="E11" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="2">
         <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>708</v>
       </c>
       <c r="H11" t="s">
-        <v>760</v>
+        <v>948</v>
       </c>
       <c r="I11" t="s">
         <v>694</v>
@@ -7848,10 +7907,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B12" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>730</v>
@@ -7862,14 +7921,14 @@
       <c r="E12" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="2">
         <v>10</v>
       </c>
       <c r="G12" t="s">
         <v>708</v>
       </c>
       <c r="H12" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="I12" t="s">
         <v>694</v>
@@ -7877,10 +7936,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B13" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>730</v>
@@ -7891,14 +7950,14 @@
       <c r="E13" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="2">
         <v>10</v>
       </c>
       <c r="G13" t="s">
         <v>708</v>
       </c>
       <c r="H13" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="I13" t="s">
         <v>694</v>
@@ -7906,10 +7965,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B14" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>730</v>
@@ -7920,14 +7979,14 @@
       <c r="E14" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="2">
         <v>10</v>
       </c>
       <c r="G14" t="s">
         <v>708</v>
       </c>
       <c r="H14" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="I14" t="s">
         <v>694</v>
@@ -7935,10 +7994,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B15" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>730</v>
@@ -7949,14 +8008,14 @@
       <c r="E15" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="2">
         <v>10</v>
       </c>
       <c r="G15" t="s">
         <v>708</v>
       </c>
       <c r="H15" t="s">
-        <v>728</v>
+        <v>758</v>
       </c>
       <c r="I15" t="s">
         <v>694</v>
@@ -7964,10 +8023,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B16" t="s">
-        <v>766</v>
+        <v>710</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>730</v>
@@ -7978,14 +8037,14 @@
       <c r="E16" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="2">
         <v>10</v>
       </c>
       <c r="G16" t="s">
         <v>708</v>
       </c>
       <c r="H16" t="s">
-        <v>767</v>
+        <v>711</v>
       </c>
       <c r="I16" t="s">
         <v>694</v>
@@ -7993,10 +8052,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B17" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>730</v>
@@ -8007,14 +8066,14 @@
       <c r="E17" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="2">
         <v>10</v>
       </c>
       <c r="G17" t="s">
         <v>708</v>
       </c>
       <c r="H17" t="s">
-        <v>757</v>
+        <v>728</v>
       </c>
       <c r="I17" t="s">
         <v>694</v>
@@ -8022,10 +8081,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B18" t="s">
-        <v>833</v>
+        <v>766</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>730</v>
@@ -8036,14 +8095,14 @@
       <c r="E18" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="2">
         <v>10</v>
       </c>
       <c r="G18" t="s">
         <v>708</v>
       </c>
       <c r="H18" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="I18" t="s">
         <v>694</v>
@@ -8051,10 +8110,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B19" t="s">
-        <v>832</v>
+        <v>724</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>730</v>
@@ -8065,14 +8124,14 @@
       <c r="E19" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="2">
         <v>10</v>
       </c>
       <c r="G19" t="s">
         <v>708</v>
       </c>
       <c r="H19" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="I19" t="s">
         <v>694</v>
@@ -8080,10 +8139,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="B20" t="s">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>730</v>
@@ -8094,14 +8153,14 @@
       <c r="E20" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="2">
         <v>10</v>
       </c>
       <c r="G20" t="s">
         <v>708</v>
       </c>
       <c r="H20" t="s">
-        <v>812</v>
+        <v>756</v>
       </c>
       <c r="I20" t="s">
         <v>694</v>
@@ -8109,10 +8168,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="B21" t="s">
-        <v>808</v>
+        <v>832</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>730</v>
@@ -8123,14 +8182,14 @@
       <c r="E21" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="2">
         <v>10</v>
       </c>
       <c r="G21" t="s">
         <v>708</v>
       </c>
       <c r="H21" t="s">
-        <v>813</v>
+        <v>755</v>
       </c>
       <c r="I21" t="s">
         <v>694</v>
@@ -8138,10 +8197,10 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="B22" t="s">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>730</v>
@@ -8152,14 +8211,14 @@
       <c r="E22" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="2">
         <v>10</v>
       </c>
       <c r="G22" t="s">
         <v>708</v>
       </c>
       <c r="H22" t="s">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="I22" t="s">
         <v>694</v>
@@ -8167,10 +8226,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="B23" t="s">
-        <v>707</v>
+        <v>808</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>730</v>
@@ -8181,14 +8240,14 @@
       <c r="E23" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="2">
         <v>10</v>
       </c>
       <c r="G23" t="s">
         <v>708</v>
       </c>
       <c r="H23" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="I23" t="s">
         <v>694</v>
@@ -8196,10 +8255,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>804</v>
+        <v>828</v>
       </c>
       <c r="B24" t="s">
-        <v>805</v>
+        <v>829</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>730</v>
@@ -8210,14 +8269,14 @@
       <c r="E24" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="2">
         <v>10</v>
       </c>
       <c r="G24" t="s">
         <v>708</v>
       </c>
       <c r="H24" t="s">
-        <v>807</v>
+        <v>830</v>
       </c>
       <c r="I24" t="s">
         <v>694</v>
@@ -8225,10 +8284,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="B25" t="s">
-        <v>773</v>
+        <v>707</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>730</v>
@@ -8239,14 +8298,14 @@
       <c r="E25" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="2">
         <v>10</v>
       </c>
       <c r="G25" t="s">
         <v>708</v>
       </c>
       <c r="H25" t="s">
-        <v>774</v>
+        <v>806</v>
       </c>
       <c r="I25" t="s">
         <v>694</v>
@@ -8254,10 +8313,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B26" t="s">
-        <v>770</v>
+        <v>941</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>730</v>
@@ -8268,14 +8327,14 @@
       <c r="E26" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="2">
         <v>10</v>
       </c>
       <c r="G26" t="s">
         <v>708</v>
       </c>
       <c r="H26" t="s">
-        <v>775</v>
+        <v>807</v>
       </c>
       <c r="I26" t="s">
         <v>694</v>
@@ -8283,10 +8342,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B27" t="s">
-        <v>723</v>
+        <v>773</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>730</v>
@@ -8297,14 +8356,14 @@
       <c r="E27" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="2">
         <v>10</v>
       </c>
       <c r="G27" t="s">
         <v>708</v>
       </c>
       <c r="H27" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="I27" t="s">
         <v>694</v>
@@ -8312,10 +8371,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B28" t="s">
-        <v>732</v>
+        <v>770</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>730</v>
@@ -8326,14 +8385,14 @@
       <c r="E28" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="2">
         <v>10</v>
       </c>
       <c r="G28" t="s">
         <v>708</v>
       </c>
       <c r="H28" t="s">
-        <v>733</v>
+        <v>775</v>
       </c>
       <c r="I28" t="s">
         <v>694</v>
@@ -8341,10 +8400,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B29" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>730</v>
@@ -8355,14 +8414,14 @@
       <c r="E29" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="2">
         <v>10</v>
       </c>
       <c r="G29" t="s">
         <v>708</v>
       </c>
       <c r="H29" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="I29" t="s">
         <v>694</v>
@@ -8370,10 +8429,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B30" t="s">
-        <v>764</v>
+        <v>732</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>730</v>
@@ -8384,14 +8443,14 @@
       <c r="E30" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="2">
         <v>10</v>
       </c>
       <c r="G30" t="s">
         <v>708</v>
       </c>
       <c r="H30" t="s">
-        <v>765</v>
+        <v>733</v>
       </c>
       <c r="I30" t="s">
         <v>694</v>
@@ -8399,10 +8458,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B31" t="s">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>730</v>
@@ -8413,14 +8472,14 @@
       <c r="E31" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="2">
         <v>10</v>
       </c>
       <c r="G31" t="s">
         <v>708</v>
       </c>
       <c r="H31" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="I31" t="s">
         <v>694</v>
@@ -8428,10 +8487,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B32" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>730</v>
@@ -8442,14 +8501,14 @@
       <c r="E32" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="2">
         <v>10</v>
       </c>
       <c r="G32" t="s">
         <v>708</v>
       </c>
       <c r="H32" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="I32" t="s">
         <v>694</v>
@@ -8457,10 +8516,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="B33" t="s">
-        <v>815</v>
+        <v>716</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>730</v>
@@ -8471,14 +8530,14 @@
       <c r="E33" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="2">
         <v>10</v>
       </c>
       <c r="G33" t="s">
         <v>708</v>
       </c>
       <c r="H33" t="s">
-        <v>816</v>
+        <v>753</v>
       </c>
       <c r="I33" t="s">
         <v>694</v>
@@ -8486,10 +8545,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B34" t="s">
-        <v>771</v>
+        <v>748</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>730</v>
@@ -8500,14 +8559,14 @@
       <c r="E34" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="2">
         <v>10</v>
       </c>
       <c r="G34" t="s">
         <v>708</v>
       </c>
       <c r="H34" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="I34" t="s">
         <v>694</v>
@@ -8515,25 +8574,28 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>734</v>
+        <v>814</v>
       </c>
       <c r="B35" t="s">
-        <v>735</v>
+        <v>815</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="D35" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F35" s="2">
         <v>10</v>
       </c>
+      <c r="G35" t="s">
+        <v>708</v>
+      </c>
       <c r="H35" t="s">
-        <v>736</v>
+        <v>816</v>
       </c>
       <c r="I35" t="s">
         <v>694</v>
@@ -8541,25 +8603,28 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>712</v>
+        <v>801</v>
       </c>
       <c r="B36" t="s">
-        <v>713</v>
+        <v>771</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="D36" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="F36" s="2">
         <v>10</v>
       </c>
+      <c r="G36" t="s">
+        <v>708</v>
+      </c>
       <c r="H36" t="s">
-        <v>714</v>
+        <v>772</v>
       </c>
       <c r="I36" t="s">
         <v>694</v>
@@ -8567,74 +8632,62 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>489</v>
+        <v>734</v>
       </c>
       <c r="B37" t="s">
-        <v>490</v>
+        <v>735</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>485</v>
+        <v>730</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="F37" s="7">
-        <v>20</v>
-      </c>
-      <c r="G37" t="s">
-        <v>289</v>
+        <v>940</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>491</v>
+        <v>736</v>
       </c>
       <c r="I37" t="s">
         <v>694</v>
-      </c>
-      <c r="J37" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>498</v>
+        <v>712</v>
       </c>
       <c r="B38" t="s">
-        <v>499</v>
+        <v>713</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>485</v>
+        <v>730</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="F38" s="7">
-        <v>20</v>
-      </c>
-      <c r="G38" t="s">
-        <v>289</v>
+        <v>940</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>500</v>
+        <v>714</v>
       </c>
       <c r="I38" t="s">
         <v>694</v>
-      </c>
-      <c r="J38" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B39" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>485</v>
@@ -8645,28 +8698,28 @@
       <c r="E39" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="2">
         <v>20</v>
       </c>
       <c r="G39" t="s">
         <v>289</v>
       </c>
       <c r="H39" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="I39" t="s">
         <v>694</v>
       </c>
       <c r="J39" t="s">
-        <v>504</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B40" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>485</v>
@@ -8677,14 +8730,14 @@
       <c r="E40" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="2">
         <v>20</v>
       </c>
       <c r="G40" t="s">
         <v>289</v>
       </c>
       <c r="H40" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="I40" t="s">
         <v>694</v>
@@ -8695,10 +8748,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B41" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>485</v>
@@ -8709,28 +8762,28 @@
       <c r="E41" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="2">
         <v>20</v>
       </c>
       <c r="G41" t="s">
         <v>289</v>
       </c>
       <c r="H41" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="I41" t="s">
         <v>694</v>
       </c>
       <c r="J41" t="s">
-        <v>289</v>
+        <v>504</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B42" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>485</v>
@@ -8741,14 +8794,14 @@
       <c r="E42" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="2">
         <v>20</v>
       </c>
       <c r="G42" t="s">
         <v>289</v>
       </c>
       <c r="H42" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="I42" t="s">
         <v>694</v>
@@ -8759,31 +8812,31 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>545</v>
+        <v>492</v>
       </c>
       <c r="B43" t="s">
-        <v>546</v>
+        <v>493</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>534</v>
+        <v>485</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>535</v>
+        <v>486</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F43" s="7">
-        <v>30</v>
+        <v>487</v>
+      </c>
+      <c r="F43" s="2">
+        <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>537</v>
+        <v>289</v>
       </c>
       <c r="H43" t="s">
-        <v>547</v>
+        <v>494</v>
       </c>
       <c r="I43" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="J43" t="s">
         <v>289</v>
@@ -8791,39 +8844,42 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>875</v>
+        <v>495</v>
       </c>
       <c r="B44" t="s">
-        <v>874</v>
+        <v>496</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>534</v>
+        <v>485</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>535</v>
+        <v>486</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F44" s="7">
-        <v>30</v>
+        <v>487</v>
+      </c>
+      <c r="F44" s="2">
+        <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>861</v>
+        <v>289</v>
       </c>
       <c r="H44" t="s">
-        <v>876</v>
+        <v>497</v>
       </c>
       <c r="I44" t="s">
         <v>694</v>
+      </c>
+      <c r="J44" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>821</v>
+        <v>545</v>
       </c>
       <c r="B45" t="s">
-        <v>822</v>
+        <v>546</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>534</v>
@@ -8834,25 +8890,28 @@
       <c r="E45" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="2">
         <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>819</v>
+        <v>537</v>
       </c>
       <c r="H45" t="s">
-        <v>820</v>
+        <v>547</v>
       </c>
       <c r="I45" t="s">
-        <v>694</v>
+        <v>695</v>
+      </c>
+      <c r="J45" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B46" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>534</v>
@@ -8863,14 +8922,14 @@
       <c r="E46" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="2">
         <v>30</v>
       </c>
       <c r="G46" t="s">
         <v>861</v>
       </c>
       <c r="H46" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="I46" t="s">
         <v>694</v>
@@ -8878,10 +8937,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>880</v>
+        <v>821</v>
       </c>
       <c r="B47" t="s">
-        <v>881</v>
+        <v>822</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>534</v>
@@ -8892,14 +8951,14 @@
       <c r="E47" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="2">
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>861</v>
+        <v>819</v>
       </c>
       <c r="H47" t="s">
-        <v>882</v>
+        <v>820</v>
       </c>
       <c r="I47" t="s">
         <v>694</v>
@@ -8907,10 +8966,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>922</v>
+        <v>877</v>
       </c>
       <c r="B48" t="s">
-        <v>923</v>
+        <v>878</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>534</v>
@@ -8921,14 +8980,14 @@
       <c r="E48" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="2">
         <v>30</v>
       </c>
       <c r="G48" t="s">
         <v>861</v>
       </c>
       <c r="H48" t="s">
-        <v>924</v>
+        <v>879</v>
       </c>
       <c r="I48" t="s">
         <v>694</v>
@@ -8936,10 +8995,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="B49" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>534</v>
@@ -8950,14 +9009,14 @@
       <c r="E49" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="2">
         <v>30</v>
       </c>
       <c r="G49" t="s">
         <v>861</v>
       </c>
       <c r="H49" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="I49" t="s">
         <v>694</v>
@@ -8965,10 +9024,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>895</v>
+        <v>922</v>
       </c>
       <c r="B50" t="s">
-        <v>896</v>
+        <v>923</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>534</v>
@@ -8979,14 +9038,14 @@
       <c r="E50" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="2">
         <v>30</v>
       </c>
       <c r="G50" t="s">
         <v>861</v>
       </c>
       <c r="H50" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="I50" t="s">
         <v>694</v>
@@ -8994,10 +9053,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="B51" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>534</v>
@@ -9008,14 +9067,14 @@
       <c r="E51" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="2">
         <v>30</v>
       </c>
       <c r="G51" t="s">
         <v>861</v>
       </c>
       <c r="H51" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="I51" t="s">
         <v>694</v>
@@ -9023,10 +9082,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>737</v>
+        <v>895</v>
       </c>
       <c r="B52" t="s">
-        <v>738</v>
+        <v>896</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>534</v>
@@ -9037,28 +9096,25 @@
       <c r="E52" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="2">
         <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>739</v>
+        <v>861</v>
       </c>
       <c r="H52" t="s">
-        <v>740</v>
+        <v>897</v>
       </c>
       <c r="I52" t="s">
         <v>694</v>
-      </c>
-      <c r="J52" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>742</v>
+        <v>898</v>
       </c>
       <c r="B53" t="s">
-        <v>743</v>
+        <v>899</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>534</v>
@@ -9069,28 +9125,25 @@
       <c r="E53" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="2">
         <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>739</v>
+        <v>861</v>
       </c>
       <c r="H53" t="s">
-        <v>744</v>
+        <v>903</v>
       </c>
       <c r="I53" t="s">
         <v>694</v>
-      </c>
-      <c r="J53" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>900</v>
+        <v>737</v>
       </c>
       <c r="B54" t="s">
-        <v>901</v>
+        <v>738</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>534</v>
@@ -9101,25 +9154,28 @@
       <c r="E54" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="2">
         <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>861</v>
+        <v>739</v>
       </c>
       <c r="H54" t="s">
-        <v>902</v>
+        <v>740</v>
       </c>
       <c r="I54" t="s">
         <v>694</v>
+      </c>
+      <c r="J54" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>907</v>
+        <v>742</v>
       </c>
       <c r="B55" t="s">
-        <v>908</v>
+        <v>743</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>534</v>
@@ -9130,25 +9186,28 @@
       <c r="E55" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55" s="2">
         <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>861</v>
+        <v>739</v>
       </c>
       <c r="H55" t="s">
-        <v>909</v>
+        <v>744</v>
       </c>
       <c r="I55" t="s">
         <v>694</v>
+      </c>
+      <c r="J55" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B56" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>534</v>
@@ -9159,14 +9218,14 @@
       <c r="E56" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="2">
         <v>30</v>
       </c>
       <c r="G56" t="s">
         <v>861</v>
       </c>
       <c r="H56" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="I56" t="s">
         <v>694</v>
@@ -9174,10 +9233,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="B57" t="s">
-        <v>929</v>
+        <v>908</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>534</v>
@@ -9188,14 +9247,14 @@
       <c r="E57" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="2">
         <v>30</v>
       </c>
       <c r="G57" t="s">
         <v>861</v>
       </c>
       <c r="H57" t="s">
-        <v>930</v>
+        <v>909</v>
       </c>
       <c r="I57" t="s">
         <v>694</v>
@@ -9203,10 +9262,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>846</v>
+        <v>904</v>
       </c>
       <c r="B58" t="s">
-        <v>847</v>
+        <v>905</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>534</v>
@@ -9217,14 +9276,14 @@
       <c r="E58" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="2">
         <v>30</v>
       </c>
       <c r="G58" t="s">
         <v>861</v>
       </c>
       <c r="H58" t="s">
-        <v>848</v>
+        <v>906</v>
       </c>
       <c r="I58" t="s">
         <v>694</v>
@@ -9232,10 +9291,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>886</v>
+        <v>928</v>
       </c>
       <c r="B59" t="s">
-        <v>887</v>
+        <v>929</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>534</v>
@@ -9246,14 +9305,14 @@
       <c r="E59" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="2">
         <v>30</v>
       </c>
       <c r="G59" t="s">
         <v>861</v>
       </c>
       <c r="H59" t="s">
-        <v>888</v>
+        <v>930</v>
       </c>
       <c r="I59" t="s">
         <v>694</v>
@@ -9261,10 +9320,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>532</v>
+        <v>846</v>
       </c>
       <c r="B60" t="s">
-        <v>533</v>
+        <v>847</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>534</v>
@@ -9275,28 +9334,25 @@
       <c r="E60" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="2">
         <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H60" t="s">
-        <v>538</v>
+        <v>848</v>
       </c>
       <c r="I60" t="s">
         <v>694</v>
-      </c>
-      <c r="J60" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>539</v>
+        <v>886</v>
       </c>
       <c r="B61" t="s">
-        <v>540</v>
+        <v>887</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>534</v>
@@ -9307,28 +9363,25 @@
       <c r="E61" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="2">
         <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H61" t="s">
-        <v>541</v>
+        <v>888</v>
       </c>
       <c r="I61" t="s">
         <v>694</v>
-      </c>
-      <c r="J61" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>534</v>
@@ -9339,14 +9392,14 @@
       <c r="E62" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="2">
         <v>30</v>
       </c>
       <c r="G62" t="s">
         <v>537</v>
       </c>
       <c r="H62" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="I62" t="s">
         <v>694</v>
@@ -9357,10 +9410,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>910</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s">
-        <v>911</v>
+        <v>540</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>534</v>
@@ -9371,25 +9424,28 @@
       <c r="E63" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="2">
         <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>861</v>
+        <v>537</v>
       </c>
       <c r="H63" t="s">
-        <v>912</v>
+        <v>541</v>
       </c>
       <c r="I63" t="s">
         <v>694</v>
+      </c>
+      <c r="J63" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>913</v>
+        <v>551</v>
       </c>
       <c r="B64" t="s">
-        <v>914</v>
+        <v>552</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>534</v>
@@ -9400,25 +9456,28 @@
       <c r="E64" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="2">
         <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>861</v>
+        <v>537</v>
       </c>
       <c r="H64" t="s">
-        <v>915</v>
+        <v>553</v>
       </c>
       <c r="I64" t="s">
         <v>694</v>
+      </c>
+      <c r="J64" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>843</v>
+        <v>910</v>
       </c>
       <c r="B65" t="s">
-        <v>844</v>
+        <v>911</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>534</v>
@@ -9429,14 +9488,14 @@
       <c r="E65" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="2">
         <v>30</v>
       </c>
       <c r="G65" t="s">
         <v>861</v>
       </c>
       <c r="H65" t="s">
-        <v>845</v>
+        <v>912</v>
       </c>
       <c r="I65" t="s">
         <v>694</v>
@@ -9444,10 +9503,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
       <c r="B66" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>534</v>
@@ -9458,14 +9517,14 @@
       <c r="E66" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="2">
         <v>30</v>
       </c>
       <c r="G66" t="s">
         <v>861</v>
       </c>
       <c r="H66" t="s">
-        <v>891</v>
+        <v>915</v>
       </c>
       <c r="I66" t="s">
         <v>694</v>
@@ -9473,10 +9532,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>916</v>
+        <v>843</v>
       </c>
       <c r="B67" t="s">
-        <v>705</v>
+        <v>844</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>534</v>
@@ -9487,14 +9546,14 @@
       <c r="E67" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="2">
         <v>30</v>
       </c>
       <c r="G67" t="s">
         <v>861</v>
       </c>
       <c r="H67" t="s">
-        <v>917</v>
+        <v>845</v>
       </c>
       <c r="I67" t="s">
         <v>694</v>
@@ -9502,10 +9561,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>920</v>
+        <v>889</v>
       </c>
       <c r="B68" t="s">
-        <v>704</v>
+        <v>890</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>534</v>
@@ -9516,14 +9575,14 @@
       <c r="E68" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="2">
         <v>30</v>
       </c>
       <c r="G68" t="s">
         <v>861</v>
       </c>
       <c r="H68" t="s">
-        <v>921</v>
+        <v>891</v>
       </c>
       <c r="I68" t="s">
         <v>694</v>
@@ -9531,10 +9590,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B69" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>534</v>
@@ -9545,14 +9604,14 @@
       <c r="E69" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="2">
         <v>30</v>
       </c>
       <c r="G69" t="s">
         <v>861</v>
       </c>
       <c r="H69" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="I69" t="s">
         <v>694</v>
@@ -9560,10 +9619,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>826</v>
+        <v>920</v>
       </c>
       <c r="B70" t="s">
-        <v>827</v>
+        <v>704</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>534</v>
@@ -9574,14 +9633,14 @@
       <c r="E70" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="2">
         <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>819</v>
+        <v>861</v>
       </c>
       <c r="H70" t="s">
-        <v>825</v>
+        <v>921</v>
       </c>
       <c r="I70" t="s">
         <v>694</v>
@@ -9589,10 +9648,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="B71" t="s">
-        <v>926</v>
+        <v>706</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>534</v>
@@ -9603,14 +9662,14 @@
       <c r="E71" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="2">
         <v>30</v>
       </c>
       <c r="G71" t="s">
         <v>861</v>
       </c>
       <c r="H71" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="I71" t="s">
         <v>694</v>
@@ -9618,10 +9677,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B72" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>534</v>
@@ -9632,7 +9691,7 @@
       <c r="E72" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="2">
         <v>30</v>
       </c>
       <c r="G72" t="s">
@@ -9647,10 +9706,10 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>817</v>
+        <v>925</v>
       </c>
       <c r="B73" t="s">
-        <v>818</v>
+        <v>926</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>534</v>
@@ -9661,14 +9720,14 @@
       <c r="E73" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73" s="2">
         <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>819</v>
+        <v>861</v>
       </c>
       <c r="H73" t="s">
-        <v>820</v>
+        <v>927</v>
       </c>
       <c r="I73" t="s">
         <v>694</v>
@@ -9676,10 +9735,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="B74" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>534</v>
@@ -9690,14 +9749,14 @@
       <c r="E74" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="2">
         <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>861</v>
+        <v>819</v>
       </c>
       <c r="H74" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="I74" t="s">
         <v>694</v>
@@ -9705,10 +9764,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>862</v>
+        <v>817</v>
       </c>
       <c r="B75" t="s">
-        <v>863</v>
+        <v>818</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>534</v>
@@ -9719,14 +9778,14 @@
       <c r="E75" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75" s="2">
         <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>861</v>
+        <v>819</v>
       </c>
       <c r="H75" t="s">
-        <v>864</v>
+        <v>820</v>
       </c>
       <c r="I75" t="s">
         <v>694</v>
@@ -9734,10 +9793,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>855</v>
+        <v>834</v>
       </c>
       <c r="B76" t="s">
-        <v>856</v>
+        <v>836</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>534</v>
@@ -9748,14 +9807,14 @@
       <c r="E76" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="2">
         <v>30</v>
       </c>
       <c r="G76" t="s">
         <v>861</v>
       </c>
       <c r="H76" t="s">
-        <v>857</v>
+        <v>835</v>
       </c>
       <c r="I76" t="s">
         <v>694</v>
@@ -9763,10 +9822,10 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="B77" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>534</v>
@@ -9777,14 +9836,14 @@
       <c r="E77" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="2">
         <v>30</v>
       </c>
       <c r="G77" t="s">
         <v>861</v>
       </c>
       <c r="H77" t="s">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="I77" t="s">
         <v>694</v>
@@ -9792,10 +9851,10 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="B78" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>534</v>
@@ -9806,14 +9865,14 @@
       <c r="E78" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="2">
         <v>30</v>
       </c>
       <c r="G78" t="s">
         <v>861</v>
       </c>
       <c r="H78" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="I78" t="s">
         <v>694</v>
@@ -9821,10 +9880,10 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>931</v>
+        <v>849</v>
       </c>
       <c r="B79" t="s">
-        <v>932</v>
+        <v>850</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>534</v>
@@ -9835,14 +9894,14 @@
       <c r="E79" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="2">
         <v>30</v>
       </c>
       <c r="G79" t="s">
         <v>861</v>
       </c>
       <c r="H79" t="s">
-        <v>933</v>
+        <v>851</v>
       </c>
       <c r="I79" t="s">
         <v>694</v>
@@ -9850,10 +9909,10 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>883</v>
+        <v>840</v>
       </c>
       <c r="B80" t="s">
-        <v>884</v>
+        <v>841</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>534</v>
@@ -9864,14 +9923,14 @@
       <c r="E80" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="2">
         <v>30</v>
       </c>
       <c r="G80" t="s">
         <v>861</v>
       </c>
       <c r="H80" t="s">
-        <v>885</v>
+        <v>842</v>
       </c>
       <c r="I80" t="s">
         <v>694</v>
@@ -9879,10 +9938,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>542</v>
+        <v>931</v>
       </c>
       <c r="B81" t="s">
-        <v>543</v>
+        <v>932</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>534</v>
@@ -9893,28 +9952,25 @@
       <c r="E81" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="2">
         <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H81" t="s">
-        <v>544</v>
+        <v>933</v>
       </c>
       <c r="I81" t="s">
         <v>694</v>
-      </c>
-      <c r="J81" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="B82" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>534</v>
@@ -9925,14 +9981,14 @@
       <c r="E82" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="2">
         <v>30</v>
       </c>
       <c r="G82" t="s">
         <v>861</v>
       </c>
       <c r="H82" t="s">
-        <v>867</v>
+        <v>885</v>
       </c>
       <c r="I82" t="s">
         <v>694</v>
@@ -9940,10 +9996,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>534</v>
@@ -9954,14 +10010,14 @@
       <c r="E83" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="2">
         <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>739</v>
+        <v>537</v>
       </c>
       <c r="H83" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="I83" t="s">
         <v>694</v>
@@ -9972,10 +10028,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B84" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>534</v>
@@ -9986,14 +10042,14 @@
       <c r="E84" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="2">
         <v>30</v>
       </c>
       <c r="G84" t="s">
         <v>861</v>
       </c>
       <c r="H84" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="I84" t="s">
         <v>694</v>
@@ -10001,10 +10057,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>871</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s">
-        <v>872</v>
+        <v>555</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>534</v>
@@ -10015,25 +10071,28 @@
       <c r="E85" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F85" s="2">
         <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>861</v>
+        <v>739</v>
       </c>
       <c r="H85" t="s">
-        <v>873</v>
+        <v>556</v>
       </c>
       <c r="I85" t="s">
         <v>694</v>
+      </c>
+      <c r="J85" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>837</v>
+        <v>868</v>
       </c>
       <c r="B86" t="s">
-        <v>838</v>
+        <v>869</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>534</v>
@@ -10044,14 +10103,14 @@
       <c r="E86" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="2">
         <v>30</v>
       </c>
       <c r="G86" t="s">
         <v>861</v>
       </c>
       <c r="H86" t="s">
-        <v>839</v>
+        <v>870</v>
       </c>
       <c r="I86" t="s">
         <v>694</v>
@@ -10059,10 +10118,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="B87" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>534</v>
@@ -10073,14 +10132,14 @@
       <c r="E87" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F87" s="7">
+      <c r="F87" s="2">
         <v>30</v>
       </c>
       <c r="G87" t="s">
         <v>861</v>
       </c>
       <c r="H87" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="I87" t="s">
         <v>694</v>
@@ -10088,10 +10147,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="B88" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>534</v>
@@ -10102,14 +10161,14 @@
       <c r="E88" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="2">
         <v>30</v>
       </c>
       <c r="G88" t="s">
         <v>861</v>
       </c>
       <c r="H88" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="I88" t="s">
         <v>694</v>
@@ -10117,10 +10176,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>548</v>
+        <v>858</v>
       </c>
       <c r="B89" t="s">
-        <v>549</v>
+        <v>859</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>534</v>
@@ -10131,78 +10190,72 @@
       <c r="E89" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="2">
         <v>30</v>
       </c>
       <c r="G89" t="s">
-        <v>537</v>
+        <v>861</v>
       </c>
       <c r="H89" t="s">
-        <v>550</v>
+        <v>860</v>
       </c>
       <c r="I89" t="s">
         <v>694</v>
-      </c>
-      <c r="J89" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>521</v>
+        <v>852</v>
       </c>
       <c r="B90" t="s">
-        <v>522</v>
+        <v>853</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F90" s="7">
-        <v>40</v>
+        <v>536</v>
+      </c>
+      <c r="F90" s="2">
+        <v>30</v>
       </c>
       <c r="G90" t="s">
-        <v>523</v>
+        <v>861</v>
       </c>
       <c r="H90" t="s">
-        <v>524</v>
+        <v>854</v>
       </c>
       <c r="I90" t="s">
         <v>694</v>
-      </c>
-      <c r="J90" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="F91" s="7">
-        <v>40</v>
+        <v>536</v>
+      </c>
+      <c r="F91" s="2">
+        <v>30</v>
       </c>
       <c r="G91" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="H91" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="I91" t="s">
         <v>694</v>
@@ -10213,10 +10266,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>516</v>
@@ -10227,14 +10280,14 @@
       <c r="E92" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="2">
         <v>40</v>
       </c>
       <c r="G92" t="s">
         <v>523</v>
       </c>
       <c r="H92" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="I92" t="s">
         <v>694</v>
@@ -10245,10 +10298,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="B93" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>516</v>
@@ -10259,14 +10312,14 @@
       <c r="E93" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="2">
         <v>40</v>
       </c>
       <c r="G93" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="H93" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="I93" t="s">
         <v>694</v>
@@ -10277,10 +10330,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>697</v>
+        <v>525</v>
       </c>
       <c r="B94" t="s">
-        <v>696</v>
+        <v>526</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>516</v>
@@ -10291,25 +10344,28 @@
       <c r="E94" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F94" s="2">
         <v>40</v>
       </c>
+      <c r="G94" t="s">
+        <v>523</v>
+      </c>
       <c r="H94" t="s">
-        <v>701</v>
+        <v>527</v>
       </c>
       <c r="I94" t="s">
         <v>694</v>
       </c>
       <c r="J94" t="s">
-        <v>703</v>
+        <v>289</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>698</v>
+        <v>528</v>
       </c>
       <c r="B95" t="s">
-        <v>699</v>
+        <v>529</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>516</v>
@@ -10320,107 +10376,104 @@
       <c r="E95" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F95" s="2">
         <v>40</v>
       </c>
+      <c r="G95" t="s">
+        <v>530</v>
+      </c>
       <c r="H95" t="s">
-        <v>700</v>
+        <v>531</v>
       </c>
       <c r="I95" t="s">
         <v>694</v>
       </c>
       <c r="J95" t="s">
-        <v>702</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>511</v>
+        <v>697</v>
       </c>
       <c r="B96" t="s">
-        <v>512</v>
+        <v>696</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F96" s="7">
-        <v>50</v>
-      </c>
-      <c r="G96" t="s">
-        <v>289</v>
+        <v>518</v>
+      </c>
+      <c r="F96" s="2">
+        <v>40</v>
       </c>
       <c r="H96" t="s">
-        <v>513</v>
+        <v>701</v>
       </c>
       <c r="I96" t="s">
         <v>694</v>
       </c>
       <c r="J96" t="s">
-        <v>289</v>
+        <v>703</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>505</v>
+        <v>698</v>
       </c>
       <c r="B97" t="s">
-        <v>506</v>
+        <v>699</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F97" s="7">
-        <v>50</v>
-      </c>
-      <c r="G97" t="s">
-        <v>289</v>
+        <v>518</v>
+      </c>
+      <c r="F97" s="2">
+        <v>40</v>
       </c>
       <c r="H97" t="s">
-        <v>510</v>
+        <v>700</v>
       </c>
       <c r="I97" t="s">
         <v>694</v>
       </c>
       <c r="J97" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>590</v>
+        <v>511</v>
       </c>
       <c r="B98" t="s">
-        <v>591</v>
+        <v>512</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F98" s="7">
-        <v>60</v>
+        <v>509</v>
+      </c>
+      <c r="F98" s="2">
+        <v>50</v>
       </c>
       <c r="G98" t="s">
-        <v>584</v>
+        <v>289</v>
       </c>
       <c r="H98" t="s">
-        <v>592</v>
+        <v>513</v>
       </c>
       <c r="I98" t="s">
         <v>694</v>
@@ -10431,28 +10484,28 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>673</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s">
-        <v>674</v>
+        <v>506</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>568</v>
+        <v>508</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F99" s="7">
-        <v>60</v>
+        <v>509</v>
+      </c>
+      <c r="F99" s="2">
+        <v>50</v>
       </c>
       <c r="G99" t="s">
-        <v>675</v>
+        <v>289</v>
       </c>
       <c r="H99" t="s">
-        <v>676</v>
+        <v>510</v>
       </c>
       <c r="I99" t="s">
         <v>694</v>
@@ -10463,10 +10516,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>681</v>
+        <v>590</v>
       </c>
       <c r="B100" t="s">
-        <v>682</v>
+        <v>591</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>567</v>
@@ -10477,14 +10530,14 @@
       <c r="E100" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F100" s="2">
         <v>60</v>
       </c>
       <c r="G100" t="s">
-        <v>675</v>
+        <v>584</v>
       </c>
       <c r="H100" t="s">
-        <v>683</v>
+        <v>592</v>
       </c>
       <c r="I100" t="s">
         <v>694</v>
@@ -10495,10 +10548,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>610</v>
+        <v>673</v>
       </c>
       <c r="B101" t="s">
-        <v>611</v>
+        <v>674</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>567</v>
@@ -10509,14 +10562,14 @@
       <c r="E101" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F101" s="7">
+      <c r="F101" s="2">
         <v>60</v>
       </c>
       <c r="G101" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="H101" t="s">
-        <v>612</v>
+        <v>676</v>
       </c>
       <c r="I101" t="s">
         <v>694</v>
@@ -10527,10 +10580,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>586</v>
+        <v>681</v>
       </c>
       <c r="B102" t="s">
-        <v>587</v>
+        <v>682</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>567</v>
@@ -10541,14 +10594,14 @@
       <c r="E102" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="2">
         <v>60</v>
       </c>
       <c r="G102" t="s">
-        <v>584</v>
+        <v>675</v>
       </c>
       <c r="H102" t="s">
-        <v>585</v>
+        <v>683</v>
       </c>
       <c r="I102" t="s">
         <v>694</v>
@@ -10559,10 +10612,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="B103" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>567</v>
@@ -10573,14 +10626,14 @@
       <c r="E103" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="2">
         <v>60</v>
       </c>
       <c r="G103" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="H103" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="I103" t="s">
         <v>694</v>
@@ -10591,10 +10644,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>588</v>
+        <v>950</v>
       </c>
       <c r="B104" t="s">
-        <v>589</v>
+        <v>951</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>567</v>
@@ -10605,7 +10658,7 @@
       <c r="E104" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="2">
         <v>60</v>
       </c>
       <c r="G104" t="s">
@@ -10617,16 +10670,13 @@
       <c r="I104" t="s">
         <v>694</v>
       </c>
-      <c r="J104" t="s">
-        <v>289</v>
-      </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>565</v>
+        <v>952</v>
       </c>
       <c r="B105" t="s">
-        <v>566</v>
+        <v>953</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>567</v>
@@ -10637,28 +10687,25 @@
       <c r="E105" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="2">
         <v>60</v>
       </c>
       <c r="G105" t="s">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="H105" t="s">
-        <v>731</v>
+        <v>954</v>
       </c>
       <c r="I105" t="s">
         <v>694</v>
-      </c>
-      <c r="J105" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="B106" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>567</v>
@@ -10669,14 +10716,14 @@
       <c r="E106" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="2">
         <v>60</v>
       </c>
       <c r="G106" t="s">
-        <v>608</v>
+        <v>584</v>
       </c>
       <c r="H106" t="s">
-        <v>609</v>
+        <v>585</v>
       </c>
       <c r="I106" t="s">
         <v>694</v>
@@ -10687,10 +10734,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>629</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s">
-        <v>630</v>
+        <v>583</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>567</v>
@@ -10701,14 +10748,14 @@
       <c r="E107" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="2">
         <v>60</v>
       </c>
       <c r="G107" t="s">
-        <v>619</v>
+        <v>584</v>
       </c>
       <c r="H107" t="s">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="I107" t="s">
         <v>694</v>
@@ -10719,10 +10766,10 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>626</v>
+        <v>588</v>
       </c>
       <c r="B108" t="s">
-        <v>627</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>567</v>
@@ -10733,14 +10780,14 @@
       <c r="E108" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="2">
         <v>60</v>
       </c>
       <c r="G108" t="s">
-        <v>619</v>
+        <v>584</v>
       </c>
       <c r="H108" t="s">
-        <v>628</v>
+        <v>585</v>
       </c>
       <c r="I108" t="s">
         <v>694</v>
@@ -10751,10 +10798,10 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>617</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s">
-        <v>618</v>
+        <v>566</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>567</v>
@@ -10765,14 +10812,14 @@
       <c r="E109" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="2">
         <v>60</v>
       </c>
       <c r="G109" t="s">
-        <v>619</v>
+        <v>570</v>
       </c>
       <c r="H109" t="s">
-        <v>620</v>
+        <v>731</v>
       </c>
       <c r="I109" t="s">
         <v>694</v>
@@ -10783,10 +10830,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="B110" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>567</v>
@@ -10797,14 +10844,14 @@
       <c r="E110" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F110" s="2">
         <v>60</v>
       </c>
       <c r="G110" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="H110" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="I110" t="s">
         <v>694</v>
@@ -10815,10 +10862,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B111" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>567</v>
@@ -10829,14 +10876,14 @@
       <c r="E111" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="2">
         <v>60</v>
       </c>
       <c r="G111" t="s">
         <v>619</v>
       </c>
       <c r="H111" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="I111" t="s">
         <v>694</v>
@@ -10847,10 +10894,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>613</v>
+        <v>626</v>
       </c>
       <c r="B112" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>567</v>
@@ -10861,14 +10908,14 @@
       <c r="E112" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="2">
         <v>60</v>
       </c>
       <c r="G112" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="H112" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="I112" t="s">
         <v>694</v>
@@ -10879,10 +10926,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>667</v>
+        <v>617</v>
       </c>
       <c r="B113" t="s">
-        <v>668</v>
+        <v>618</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>567</v>
@@ -10893,14 +10940,14 @@
       <c r="E113" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="2">
         <v>60</v>
       </c>
       <c r="G113" t="s">
-        <v>537</v>
+        <v>619</v>
       </c>
       <c r="H113" t="s">
-        <v>669</v>
+        <v>620</v>
       </c>
       <c r="I113" t="s">
         <v>694</v>
@@ -10911,10 +10958,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>677</v>
+        <v>624</v>
       </c>
       <c r="B114" t="s">
-        <v>678</v>
+        <v>625</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>567</v>
@@ -10925,14 +10972,14 @@
       <c r="E114" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="2">
         <v>60</v>
       </c>
       <c r="G114" t="s">
-        <v>679</v>
+        <v>619</v>
       </c>
       <c r="H114" t="s">
-        <v>680</v>
+        <v>623</v>
       </c>
       <c r="I114" t="s">
         <v>694</v>
@@ -10943,10 +10990,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>663</v>
+        <v>621</v>
       </c>
       <c r="B115" t="s">
-        <v>664</v>
+        <v>622</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>567</v>
@@ -10957,14 +11004,14 @@
       <c r="E115" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F115" s="7">
+      <c r="F115" s="2">
         <v>60</v>
       </c>
       <c r="G115" t="s">
-        <v>665</v>
+        <v>619</v>
       </c>
       <c r="H115" t="s">
-        <v>666</v>
+        <v>623</v>
       </c>
       <c r="I115" t="s">
         <v>694</v>
@@ -10975,10 +11022,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>684</v>
+        <v>613</v>
       </c>
       <c r="B116" t="s">
-        <v>685</v>
+        <v>614</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>567</v>
@@ -10989,14 +11036,14 @@
       <c r="E116" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F116" s="7">
+      <c r="F116" s="2">
         <v>60</v>
       </c>
       <c r="G116" t="s">
-        <v>679</v>
+        <v>615</v>
       </c>
       <c r="H116" t="s">
-        <v>686</v>
+        <v>616</v>
       </c>
       <c r="I116" t="s">
         <v>694</v>
@@ -11007,10 +11054,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>577</v>
+        <v>667</v>
       </c>
       <c r="B117" t="s">
-        <v>578</v>
+        <v>668</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>567</v>
@@ -11021,14 +11068,14 @@
       <c r="E117" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F117" s="7">
+      <c r="F117" s="2">
         <v>60</v>
       </c>
       <c r="G117" t="s">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="H117" t="s">
-        <v>576</v>
+        <v>669</v>
       </c>
       <c r="I117" t="s">
         <v>694</v>
@@ -11039,10 +11086,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>574</v>
+        <v>677</v>
       </c>
       <c r="B118" t="s">
-        <v>575</v>
+        <v>678</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>567</v>
@@ -11053,14 +11100,14 @@
       <c r="E118" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F118" s="7">
+      <c r="F118" s="2">
         <v>60</v>
       </c>
       <c r="G118" t="s">
-        <v>570</v>
+        <v>679</v>
       </c>
       <c r="H118" t="s">
-        <v>576</v>
+        <v>680</v>
       </c>
       <c r="I118" t="s">
         <v>694</v>
@@ -11071,10 +11118,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="B119" t="s">
-        <v>637</v>
+        <v>664</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>567</v>
@@ -11085,14 +11132,14 @@
       <c r="E119" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F119" s="2">
         <v>60</v>
       </c>
       <c r="G119" t="s">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="H119" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="I119" t="s">
         <v>694</v>
@@ -11103,10 +11150,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>632</v>
+        <v>684</v>
       </c>
       <c r="B120" t="s">
-        <v>633</v>
+        <v>685</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>567</v>
@@ -11117,14 +11164,14 @@
       <c r="E120" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F120" s="2">
         <v>60</v>
       </c>
       <c r="G120" t="s">
-        <v>634</v>
+        <v>679</v>
       </c>
       <c r="H120" t="s">
-        <v>635</v>
+        <v>686</v>
       </c>
       <c r="I120" t="s">
         <v>694</v>
@@ -11135,10 +11182,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="B121" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>567</v>
@@ -11149,14 +11196,14 @@
       <c r="E121" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F121" s="7">
+      <c r="F121" s="2">
         <v>60</v>
       </c>
       <c r="G121" t="s">
-        <v>604</v>
+        <v>570</v>
       </c>
       <c r="H121" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="I121" t="s">
         <v>694</v>
@@ -11167,10 +11214,10 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>650</v>
+        <v>574</v>
       </c>
       <c r="B122" t="s">
-        <v>651</v>
+        <v>575</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>567</v>
@@ -11181,14 +11228,14 @@
       <c r="E122" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="2">
         <v>60</v>
       </c>
       <c r="G122" t="s">
-        <v>652</v>
+        <v>570</v>
       </c>
       <c r="H122" t="s">
-        <v>653</v>
+        <v>576</v>
       </c>
       <c r="I122" t="s">
         <v>694</v>
@@ -11199,10 +11246,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>579</v>
+        <v>636</v>
       </c>
       <c r="B123" t="s">
-        <v>580</v>
+        <v>637</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>567</v>
@@ -11213,14 +11260,14 @@
       <c r="E123" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="2">
         <v>60</v>
       </c>
       <c r="G123" t="s">
-        <v>570</v>
+        <v>634</v>
       </c>
       <c r="H123" t="s">
-        <v>581</v>
+        <v>635</v>
       </c>
       <c r="I123" t="s">
         <v>694</v>
@@ -11231,10 +11278,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="B124" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>567</v>
@@ -11245,14 +11292,14 @@
       <c r="E124" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="2">
         <v>60</v>
       </c>
       <c r="G124" t="s">
-        <v>656</v>
+        <v>634</v>
       </c>
       <c r="H124" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
       <c r="I124" t="s">
         <v>694</v>
@@ -11263,10 +11310,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>658</v>
+        <v>602</v>
       </c>
       <c r="B125" t="s">
-        <v>659</v>
+        <v>603</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>567</v>
@@ -11277,14 +11324,14 @@
       <c r="E125" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="2">
         <v>60</v>
       </c>
       <c r="G125" t="s">
-        <v>656</v>
+        <v>604</v>
       </c>
       <c r="H125" t="s">
-        <v>657</v>
+        <v>605</v>
       </c>
       <c r="I125" t="s">
         <v>694</v>
@@ -11295,10 +11342,10 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>571</v>
+        <v>650</v>
       </c>
       <c r="B126" t="s">
-        <v>572</v>
+        <v>651</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>567</v>
@@ -11309,14 +11356,14 @@
       <c r="E126" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F126" s="2">
         <v>60</v>
       </c>
       <c r="G126" t="s">
-        <v>570</v>
+        <v>652</v>
       </c>
       <c r="H126" t="s">
-        <v>573</v>
+        <v>653</v>
       </c>
       <c r="I126" t="s">
         <v>694</v>
@@ -11327,10 +11374,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B127" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>567</v>
@@ -11341,14 +11388,14 @@
       <c r="E127" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F127" s="2">
         <v>60</v>
       </c>
       <c r="G127" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="H127" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="I127" t="s">
         <v>694</v>
@@ -11359,10 +11406,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="B128" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>567</v>
@@ -11373,14 +11420,14 @@
       <c r="E128" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F128" s="7">
+      <c r="F128" s="2">
         <v>60</v>
       </c>
       <c r="G128" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="H128" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="I128" t="s">
         <v>694</v>
@@ -11391,10 +11438,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B129" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>567</v>
@@ -11405,14 +11452,14 @@
       <c r="E129" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F129" s="7">
+      <c r="F129" s="2">
         <v>60</v>
       </c>
       <c r="G129" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="H129" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="I129" t="s">
         <v>694</v>
@@ -11423,10 +11470,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>670</v>
+        <v>571</v>
       </c>
       <c r="B130" t="s">
-        <v>671</v>
+        <v>572</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>567</v>
@@ -11437,14 +11484,14 @@
       <c r="E130" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F130" s="7">
+      <c r="F130" s="2">
         <v>60</v>
       </c>
       <c r="G130" t="s">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="H130" t="s">
-        <v>672</v>
+        <v>573</v>
       </c>
       <c r="I130" t="s">
         <v>694</v>
@@ -11455,10 +11502,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>687</v>
+        <v>593</v>
       </c>
       <c r="B131" t="s">
-        <v>688</v>
+        <v>594</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>567</v>
@@ -11469,14 +11516,14 @@
       <c r="E131" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F131" s="7">
+      <c r="F131" s="2">
         <v>60</v>
       </c>
       <c r="G131" t="s">
-        <v>665</v>
+        <v>584</v>
       </c>
       <c r="H131" t="s">
-        <v>689</v>
+        <v>592</v>
       </c>
       <c r="I131" t="s">
         <v>694</v>
@@ -11487,10 +11534,10 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>660</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s">
-        <v>661</v>
+        <v>639</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>567</v>
@@ -11501,14 +11548,14 @@
       <c r="E132" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F132" s="7">
+      <c r="F132" s="2">
         <v>60</v>
       </c>
       <c r="G132" t="s">
-        <v>537</v>
+        <v>640</v>
       </c>
       <c r="H132" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="I132" t="s">
         <v>694</v>
@@ -11519,10 +11566,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>600</v>
+        <v>646</v>
       </c>
       <c r="B133" t="s">
-        <v>601</v>
+        <v>647</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>567</v>
@@ -11533,14 +11580,14 @@
       <c r="E133" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F133" s="7">
+      <c r="F133" s="2">
         <v>60</v>
       </c>
       <c r="G133" t="s">
-        <v>597</v>
+        <v>648</v>
       </c>
       <c r="H133" t="s">
-        <v>597</v>
+        <v>649</v>
       </c>
       <c r="I133" t="s">
         <v>694</v>
@@ -11551,10 +11598,10 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>595</v>
+        <v>670</v>
       </c>
       <c r="B134" t="s">
-        <v>596</v>
+        <v>671</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>567</v>
@@ -11565,14 +11612,14 @@
       <c r="E134" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F134" s="7">
+      <c r="F134" s="2">
         <v>60</v>
       </c>
       <c r="G134" t="s">
-        <v>597</v>
+        <v>537</v>
       </c>
       <c r="H134" t="s">
-        <v>597</v>
+        <v>672</v>
       </c>
       <c r="I134" t="s">
         <v>694</v>
@@ -11583,10 +11630,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>598</v>
+        <v>687</v>
       </c>
       <c r="B135" t="s">
-        <v>599</v>
+        <v>688</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>567</v>
@@ -11597,14 +11644,14 @@
       <c r="E135" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F135" s="7">
+      <c r="F135" s="2">
         <v>60</v>
       </c>
       <c r="G135" t="s">
-        <v>597</v>
+        <v>665</v>
       </c>
       <c r="H135" t="s">
-        <v>597</v>
+        <v>689</v>
       </c>
       <c r="I135" t="s">
         <v>694</v>
@@ -11615,10 +11662,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="B136" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>567</v>
@@ -11629,14 +11676,14 @@
       <c r="E136" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F136" s="7">
+      <c r="F136" s="2">
         <v>60</v>
       </c>
       <c r="G136" t="s">
-        <v>644</v>
+        <v>537</v>
       </c>
       <c r="H136" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="I136" t="s">
         <v>694</v>
@@ -11647,190 +11694,202 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>561</v>
+        <v>600</v>
       </c>
       <c r="B137" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F137" s="7">
+        <v>569</v>
+      </c>
+      <c r="F137" s="2">
         <v>60</v>
       </c>
       <c r="G137" t="s">
+        <v>597</v>
+      </c>
+      <c r="H137" t="s">
+        <v>597</v>
+      </c>
+      <c r="I137" t="s">
+        <v>694</v>
+      </c>
+      <c r="J137" t="s">
         <v>289</v>
-      </c>
-      <c r="H137" t="s">
-        <v>563</v>
-      </c>
-      <c r="I137" t="s">
-        <v>694</v>
-      </c>
-      <c r="J137" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="B138" t="s">
-        <v>558</v>
+        <v>596</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>534</v>
+        <v>567</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>535</v>
+        <v>568</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="F138" s="7">
+        <v>569</v>
+      </c>
+      <c r="F138" s="2">
         <v>60</v>
       </c>
       <c r="G138" t="s">
+        <v>597</v>
+      </c>
+      <c r="H138" t="s">
+        <v>597</v>
+      </c>
+      <c r="I138" t="s">
+        <v>694</v>
+      </c>
+      <c r="J138" t="s">
         <v>289</v>
-      </c>
-      <c r="H138" t="s">
-        <v>559</v>
-      </c>
-      <c r="I138" t="s">
-        <v>694</v>
-      </c>
-      <c r="J138" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>290</v>
+        <v>598</v>
       </c>
       <c r="B139" t="s">
-        <v>291</v>
+        <v>599</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F139" s="7">
-        <v>70</v>
+        <v>569</v>
+      </c>
+      <c r="F139" s="2">
+        <v>60</v>
       </c>
       <c r="G139" t="s">
-        <v>472</v>
+        <v>597</v>
       </c>
       <c r="H139" t="s">
-        <v>693</v>
+        <v>597</v>
       </c>
       <c r="I139" t="s">
         <v>694</v>
+      </c>
+      <c r="J139" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>292</v>
+        <v>642</v>
       </c>
       <c r="B140" t="s">
-        <v>293</v>
+        <v>643</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>691</v>
+        <v>568</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F140" s="7">
-        <v>70</v>
+        <v>569</v>
+      </c>
+      <c r="F140" s="2">
+        <v>60</v>
       </c>
       <c r="G140" t="s">
-        <v>472</v>
+        <v>644</v>
       </c>
       <c r="H140" t="s">
-        <v>693</v>
+        <v>645</v>
       </c>
       <c r="I140" t="s">
         <v>694</v>
+      </c>
+      <c r="J140" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>294</v>
+        <v>561</v>
       </c>
       <c r="B141" t="s">
-        <v>295</v>
+        <v>562</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>690</v>
+        <v>534</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>691</v>
+        <v>535</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F141" s="7">
-        <v>70</v>
+        <v>536</v>
+      </c>
+      <c r="F141" s="2">
+        <v>60</v>
       </c>
       <c r="G141" t="s">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="H141" t="s">
-        <v>693</v>
+        <v>563</v>
       </c>
       <c r="I141" t="s">
         <v>694</v>
+      </c>
+      <c r="J141" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>296</v>
+        <v>557</v>
       </c>
       <c r="B142" t="s">
-        <v>297</v>
+        <v>558</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>690</v>
+        <v>534</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>691</v>
+        <v>535</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F142" s="7">
-        <v>70</v>
+        <v>536</v>
+      </c>
+      <c r="F142" s="2">
+        <v>60</v>
       </c>
       <c r="G142" t="s">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="H142" t="s">
-        <v>693</v>
+        <v>559</v>
       </c>
       <c r="I142" t="s">
         <v>694</v>
+      </c>
+      <c r="J142" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B143" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>690</v>
@@ -11841,7 +11900,7 @@
       <c r="E143" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F143" s="7">
+      <c r="F143" s="2">
         <v>70</v>
       </c>
       <c r="G143" t="s">
@@ -11856,10 +11915,10 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B144" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>690</v>
@@ -11870,7 +11929,7 @@
       <c r="E144" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F144" s="2">
         <v>70</v>
       </c>
       <c r="G144" t="s">
@@ -11885,10 +11944,10 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B145" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>690</v>
@@ -11899,7 +11958,7 @@
       <c r="E145" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F145" s="7">
+      <c r="F145" s="2">
         <v>70</v>
       </c>
       <c r="G145" t="s">
@@ -11914,10 +11973,10 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B146" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>690</v>
@@ -11928,7 +11987,7 @@
       <c r="E146" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F146" s="7">
+      <c r="F146" s="2">
         <v>70</v>
       </c>
       <c r="G146" t="s">
@@ -11943,10 +12002,10 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>690</v>
@@ -11957,7 +12016,7 @@
       <c r="E147" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F147" s="7">
+      <c r="F147" s="2">
         <v>70</v>
       </c>
       <c r="G147" t="s">
@@ -11972,10 +12031,10 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B148" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>690</v>
@@ -11986,7 +12045,7 @@
       <c r="E148" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F148" s="7">
+      <c r="F148" s="2">
         <v>70</v>
       </c>
       <c r="G148" t="s">
@@ -12001,10 +12060,10 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B149" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>690</v>
@@ -12015,7 +12074,7 @@
       <c r="E149" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F149" s="7">
+      <c r="F149" s="2">
         <v>70</v>
       </c>
       <c r="G149" t="s">
@@ -12030,10 +12089,10 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B150" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>690</v>
@@ -12044,7 +12103,7 @@
       <c r="E150" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F150" s="7">
+      <c r="F150" s="2">
         <v>70</v>
       </c>
       <c r="G150" t="s">
@@ -12059,10 +12118,10 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B151" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>690</v>
@@ -12073,7 +12132,7 @@
       <c r="E151" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F151" s="7">
+      <c r="F151" s="2">
         <v>70</v>
       </c>
       <c r="G151" t="s">
@@ -12088,10 +12147,10 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B152" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>690</v>
@@ -12102,7 +12161,7 @@
       <c r="E152" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F152" s="7">
+      <c r="F152" s="2">
         <v>70</v>
       </c>
       <c r="G152" t="s">
@@ -12117,10 +12176,10 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B153" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>690</v>
@@ -12131,7 +12190,7 @@
       <c r="E153" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F153" s="7">
+      <c r="F153" s="2">
         <v>70</v>
       </c>
       <c r="G153" t="s">
@@ -12146,10 +12205,10 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B154" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>690</v>
@@ -12160,7 +12219,7 @@
       <c r="E154" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F154" s="7">
+      <c r="F154" s="2">
         <v>70</v>
       </c>
       <c r="G154" t="s">
@@ -12175,10 +12234,10 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B155" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>690</v>
@@ -12189,7 +12248,7 @@
       <c r="E155" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F155" s="7">
+      <c r="F155" s="2">
         <v>70</v>
       </c>
       <c r="G155" t="s">
@@ -12204,10 +12263,10 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B156" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>690</v>
@@ -12218,7 +12277,7 @@
       <c r="E156" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F156" s="7">
+      <c r="F156" s="2">
         <v>70</v>
       </c>
       <c r="G156" t="s">
@@ -12233,10 +12292,10 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B157" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>690</v>
@@ -12247,7 +12306,7 @@
       <c r="E157" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F157" s="7">
+      <c r="F157" s="2">
         <v>70</v>
       </c>
       <c r="G157" t="s">
@@ -12262,10 +12321,10 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B158" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>690</v>
@@ -12276,7 +12335,7 @@
       <c r="E158" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F158" s="7">
+      <c r="F158" s="2">
         <v>70</v>
       </c>
       <c r="G158" t="s">
@@ -12291,10 +12350,10 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>690</v>
@@ -12305,7 +12364,7 @@
       <c r="E159" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F159" s="7">
+      <c r="F159" s="2">
         <v>70</v>
       </c>
       <c r="G159" t="s">
@@ -12320,10 +12379,10 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B160" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>690</v>
@@ -12334,7 +12393,7 @@
       <c r="E160" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F160" s="7">
+      <c r="F160" s="2">
         <v>70</v>
       </c>
       <c r="G160" t="s">
@@ -12349,10 +12408,10 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B161" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>690</v>
@@ -12363,7 +12422,7 @@
       <c r="E161" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F161" s="7">
+      <c r="F161" s="2">
         <v>70</v>
       </c>
       <c r="G161" t="s">
@@ -12378,10 +12437,10 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B162" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>690</v>
@@ -12392,7 +12451,7 @@
       <c r="E162" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F162" s="7">
+      <c r="F162" s="2">
         <v>70</v>
       </c>
       <c r="G162" t="s">
@@ -12407,10 +12466,10 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="B163" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>690</v>
@@ -12421,7 +12480,7 @@
       <c r="E163" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F163" s="7">
+      <c r="F163" s="2">
         <v>70</v>
       </c>
       <c r="G163" t="s">
@@ -12436,10 +12495,10 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B164" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>690</v>
@@ -12450,7 +12509,7 @@
       <c r="E164" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F164" s="7">
+      <c r="F164" s="2">
         <v>70</v>
       </c>
       <c r="G164" t="s">
@@ -12465,10 +12524,10 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B165" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>690</v>
@@ -12479,7 +12538,7 @@
       <c r="E165" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F165" s="7">
+      <c r="F165" s="2">
         <v>70</v>
       </c>
       <c r="G165" t="s">
@@ -12494,10 +12553,10 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B166" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>690</v>
@@ -12508,7 +12567,7 @@
       <c r="E166" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F166" s="7">
+      <c r="F166" s="2">
         <v>70</v>
       </c>
       <c r="G166" t="s">
@@ -12523,10 +12582,10 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B167" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>690</v>
@@ -12537,7 +12596,7 @@
       <c r="E167" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F167" s="7">
+      <c r="F167" s="2">
         <v>70</v>
       </c>
       <c r="G167" t="s">
@@ -12552,10 +12611,10 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B168" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>690</v>
@@ -12566,7 +12625,7 @@
       <c r="E168" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F168" s="7">
+      <c r="F168" s="2">
         <v>70</v>
       </c>
       <c r="G168" t="s">
@@ -12581,10 +12640,10 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B169" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>690</v>
@@ -12595,7 +12654,7 @@
       <c r="E169" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F169" s="7">
+      <c r="F169" s="2">
         <v>70</v>
       </c>
       <c r="G169" t="s">
@@ -12610,10 +12669,10 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B170" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>690</v>
@@ -12624,7 +12683,7 @@
       <c r="E170" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F170" s="7">
+      <c r="F170" s="2">
         <v>70</v>
       </c>
       <c r="G170" t="s">
@@ -12639,10 +12698,10 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>690</v>
@@ -12653,7 +12712,7 @@
       <c r="E171" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F171" s="7">
+      <c r="F171" s="2">
         <v>70</v>
       </c>
       <c r="G171" t="s">
@@ -12668,10 +12727,10 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B172" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>690</v>
@@ -12682,7 +12741,7 @@
       <c r="E172" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F172" s="7">
+      <c r="F172" s="2">
         <v>70</v>
       </c>
       <c r="G172" t="s">
@@ -12697,10 +12756,10 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>690</v>
@@ -12711,7 +12770,7 @@
       <c r="E173" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F173" s="7">
+      <c r="F173" s="2">
         <v>70</v>
       </c>
       <c r="G173" t="s">
@@ -12726,10 +12785,10 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B174" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>690</v>
@@ -12740,7 +12799,7 @@
       <c r="E174" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F174" s="7">
+      <c r="F174" s="2">
         <v>70</v>
       </c>
       <c r="G174" t="s">
@@ -12755,10 +12814,10 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>690</v>
@@ -12769,7 +12828,7 @@
       <c r="E175" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F175" s="7">
+      <c r="F175" s="2">
         <v>70</v>
       </c>
       <c r="G175" t="s">
@@ -12784,10 +12843,10 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B176" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>690</v>
@@ -12798,7 +12857,7 @@
       <c r="E176" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F176" s="7">
+      <c r="F176" s="2">
         <v>70</v>
       </c>
       <c r="G176" t="s">
@@ -12813,10 +12872,10 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>690</v>
@@ -12827,7 +12886,7 @@
       <c r="E177" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F177" s="7">
+      <c r="F177" s="2">
         <v>70</v>
       </c>
       <c r="G177" t="s">
@@ -12842,10 +12901,10 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B178" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>690</v>
@@ -12856,7 +12915,7 @@
       <c r="E178" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F178" s="7">
+      <c r="F178" s="2">
         <v>70</v>
       </c>
       <c r="G178" t="s">
@@ -12871,10 +12930,10 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>690</v>
@@ -12885,7 +12944,7 @@
       <c r="E179" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F179" s="7">
+      <c r="F179" s="2">
         <v>70</v>
       </c>
       <c r="G179" t="s">
@@ -12900,10 +12959,10 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B180" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>690</v>
@@ -12914,7 +12973,7 @@
       <c r="E180" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F180" s="7">
+      <c r="F180" s="2">
         <v>70</v>
       </c>
       <c r="G180" t="s">
@@ -12929,10 +12988,10 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B181" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>690</v>
@@ -12943,7 +13002,7 @@
       <c r="E181" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F181" s="7">
+      <c r="F181" s="2">
         <v>70</v>
       </c>
       <c r="G181" t="s">
@@ -12958,10 +13017,10 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B182" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>690</v>
@@ -12972,7 +13031,7 @@
       <c r="E182" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F182" s="7">
+      <c r="F182" s="2">
         <v>70</v>
       </c>
       <c r="G182" t="s">
@@ -12987,10 +13046,10 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B183" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>690</v>
@@ -13001,7 +13060,7 @@
       <c r="E183" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F183" s="7">
+      <c r="F183" s="2">
         <v>70</v>
       </c>
       <c r="G183" t="s">
@@ -13016,10 +13075,10 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B184" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>690</v>
@@ -13030,7 +13089,7 @@
       <c r="E184" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F184" s="7">
+      <c r="F184" s="2">
         <v>70</v>
       </c>
       <c r="G184" t="s">
@@ -13045,10 +13104,10 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B185" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>690</v>
@@ -13059,7 +13118,7 @@
       <c r="E185" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F185" s="7">
+      <c r="F185" s="2">
         <v>70</v>
       </c>
       <c r="G185" t="s">
@@ -13074,10 +13133,10 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B186" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>690</v>
@@ -13088,7 +13147,7 @@
       <c r="E186" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F186" s="7">
+      <c r="F186" s="2">
         <v>70</v>
       </c>
       <c r="G186" t="s">
@@ -13103,10 +13162,10 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B187" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>690</v>
@@ -13117,7 +13176,7 @@
       <c r="E187" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F187" s="7">
+      <c r="F187" s="2">
         <v>70</v>
       </c>
       <c r="G187" t="s">
@@ -13132,10 +13191,10 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B188" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>690</v>
@@ -13146,7 +13205,7 @@
       <c r="E188" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F188" s="7">
+      <c r="F188" s="2">
         <v>70</v>
       </c>
       <c r="G188" t="s">
@@ -13161,10 +13220,10 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B189" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>690</v>
@@ -13175,7 +13234,7 @@
       <c r="E189" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F189" s="7">
+      <c r="F189" s="2">
         <v>70</v>
       </c>
       <c r="G189" t="s">
@@ -13190,10 +13249,10 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B190" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>690</v>
@@ -13204,7 +13263,7 @@
       <c r="E190" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F190" s="7">
+      <c r="F190" s="2">
         <v>70</v>
       </c>
       <c r="G190" t="s">
@@ -13219,10 +13278,10 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B191" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>690</v>
@@ -13233,7 +13292,7 @@
       <c r="E191" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F191" s="7">
+      <c r="F191" s="2">
         <v>70</v>
       </c>
       <c r="G191" t="s">
@@ -13248,10 +13307,10 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B192" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>690</v>
@@ -13262,7 +13321,7 @@
       <c r="E192" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F192" s="7">
+      <c r="F192" s="2">
         <v>70</v>
       </c>
       <c r="G192" t="s">
@@ -13277,10 +13336,10 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B193" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>690</v>
@@ -13291,7 +13350,7 @@
       <c r="E193" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F193" s="7">
+      <c r="F193" s="2">
         <v>70</v>
       </c>
       <c r="G193" t="s">
@@ -13306,10 +13365,10 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B194" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>690</v>
@@ -13320,7 +13379,7 @@
       <c r="E194" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F194" s="7">
+      <c r="F194" s="2">
         <v>70</v>
       </c>
       <c r="G194" t="s">
@@ -13335,10 +13394,10 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B195" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>690</v>
@@ -13349,7 +13408,7 @@
       <c r="E195" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F195" s="7">
+      <c r="F195" s="2">
         <v>70</v>
       </c>
       <c r="G195" t="s">
@@ -13364,10 +13423,10 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B196" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>690</v>
@@ -13378,7 +13437,7 @@
       <c r="E196" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F196" s="7">
+      <c r="F196" s="2">
         <v>70</v>
       </c>
       <c r="G196" t="s">
@@ -13393,10 +13452,10 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B197" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>690</v>
@@ -13407,7 +13466,7 @@
       <c r="E197" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F197" s="7">
+      <c r="F197" s="2">
         <v>70</v>
       </c>
       <c r="G197" t="s">
@@ -13422,10 +13481,10 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B198" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>690</v>
@@ -13436,7 +13495,7 @@
       <c r="E198" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F198" s="7">
+      <c r="F198" s="2">
         <v>70</v>
       </c>
       <c r="G198" t="s">
@@ -13451,10 +13510,10 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B199" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>690</v>
@@ -13465,7 +13524,7 @@
       <c r="E199" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F199" s="7">
+      <c r="F199" s="2">
         <v>70</v>
       </c>
       <c r="G199" t="s">
@@ -13480,10 +13539,10 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B200" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>690</v>
@@ -13494,7 +13553,7 @@
       <c r="E200" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F200" s="7">
+      <c r="F200" s="2">
         <v>70</v>
       </c>
       <c r="G200" t="s">
@@ -13509,10 +13568,10 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>690</v>
@@ -13523,7 +13582,7 @@
       <c r="E201" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F201" s="7">
+      <c r="F201" s="2">
         <v>70</v>
       </c>
       <c r="G201" t="s">
@@ -13538,10 +13597,10 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B202" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>690</v>
@@ -13552,7 +13611,7 @@
       <c r="E202" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F202" s="7">
+      <c r="F202" s="2">
         <v>70</v>
       </c>
       <c r="G202" t="s">
@@ -13567,10 +13626,10 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B203" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>690</v>
@@ -13581,7 +13640,7 @@
       <c r="E203" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F203" s="7">
+      <c r="F203" s="2">
         <v>70</v>
       </c>
       <c r="G203" t="s">
@@ -13596,10 +13655,10 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B204" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>690</v>
@@ -13610,7 +13669,7 @@
       <c r="E204" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F204" s="7">
+      <c r="F204" s="2">
         <v>70</v>
       </c>
       <c r="G204" t="s">
@@ -13625,10 +13684,10 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B205" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>690</v>
@@ -13639,7 +13698,7 @@
       <c r="E205" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F205" s="7">
+      <c r="F205" s="2">
         <v>70</v>
       </c>
       <c r="G205" t="s">
@@ -13654,10 +13713,10 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B206" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>690</v>
@@ -13668,7 +13727,7 @@
       <c r="E206" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F206" s="7">
+      <c r="F206" s="2">
         <v>70</v>
       </c>
       <c r="G206" t="s">
@@ -13683,10 +13742,10 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B207" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>690</v>
@@ -13697,7 +13756,7 @@
       <c r="E207" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F207" s="7">
+      <c r="F207" s="2">
         <v>70</v>
       </c>
       <c r="G207" t="s">
@@ -13712,10 +13771,10 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B208" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>690</v>
@@ -13726,7 +13785,7 @@
       <c r="E208" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F208" s="7">
+      <c r="F208" s="2">
         <v>70</v>
       </c>
       <c r="G208" t="s">
@@ -13741,10 +13800,10 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B209" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>690</v>
@@ -13755,7 +13814,7 @@
       <c r="E209" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F209" s="7">
+      <c r="F209" s="2">
         <v>70</v>
       </c>
       <c r="G209" t="s">
@@ -13770,10 +13829,10 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>690</v>
@@ -13784,7 +13843,7 @@
       <c r="E210" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F210" s="7">
+      <c r="F210" s="2">
         <v>70</v>
       </c>
       <c r="G210" t="s">
@@ -13799,10 +13858,10 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B211" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>690</v>
@@ -13813,7 +13872,7 @@
       <c r="E211" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F211" s="7">
+      <c r="F211" s="2">
         <v>70</v>
       </c>
       <c r="G211" t="s">
@@ -13828,10 +13887,10 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B212" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>690</v>
@@ -13842,7 +13901,7 @@
       <c r="E212" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F212" s="7">
+      <c r="F212" s="2">
         <v>70</v>
       </c>
       <c r="G212" t="s">
@@ -13857,10 +13916,10 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="B213" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>690</v>
@@ -13871,7 +13930,7 @@
       <c r="E213" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F213" s="7">
+      <c r="F213" s="2">
         <v>70</v>
       </c>
       <c r="G213" t="s">
@@ -13886,10 +13945,10 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B214" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>690</v>
@@ -13900,7 +13959,7 @@
       <c r="E214" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F214" s="7">
+      <c r="F214" s="2">
         <v>70</v>
       </c>
       <c r="G214" t="s">
@@ -13915,10 +13974,10 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B215" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>690</v>
@@ -13929,7 +13988,7 @@
       <c r="E215" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F215" s="7">
+      <c r="F215" s="2">
         <v>70</v>
       </c>
       <c r="G215" t="s">
@@ -13944,10 +14003,10 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B216" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>690</v>
@@ -13958,7 +14017,7 @@
       <c r="E216" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F216" s="7">
+      <c r="F216" s="2">
         <v>70</v>
       </c>
       <c r="G216" t="s">
@@ -13973,10 +14032,10 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B217" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>690</v>
@@ -13987,7 +14046,7 @@
       <c r="E217" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F217" s="7">
+      <c r="F217" s="2">
         <v>70</v>
       </c>
       <c r="G217" t="s">
@@ -14002,10 +14061,10 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B218" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>690</v>
@@ -14016,7 +14075,7 @@
       <c r="E218" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F218" s="7">
+      <c r="F218" s="2">
         <v>70</v>
       </c>
       <c r="G218" t="s">
@@ -14031,10 +14090,10 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B219" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>690</v>
@@ -14045,7 +14104,7 @@
       <c r="E219" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F219" s="7">
+      <c r="F219" s="2">
         <v>70</v>
       </c>
       <c r="G219" t="s">
@@ -14060,10 +14119,10 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B220" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>690</v>
@@ -14074,7 +14133,7 @@
       <c r="E220" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F220" s="7">
+      <c r="F220" s="2">
         <v>70</v>
       </c>
       <c r="G220" t="s">
@@ -14089,10 +14148,10 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B221" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>690</v>
@@ -14103,7 +14162,7 @@
       <c r="E221" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F221" s="7">
+      <c r="F221" s="2">
         <v>70</v>
       </c>
       <c r="G221" t="s">
@@ -14118,10 +14177,10 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B222" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>690</v>
@@ -14132,7 +14191,7 @@
       <c r="E222" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F222" s="7">
+      <c r="F222" s="2">
         <v>70</v>
       </c>
       <c r="G222" t="s">
@@ -14147,10 +14206,10 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B223" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>690</v>
@@ -14161,7 +14220,7 @@
       <c r="E223" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F223" s="7">
+      <c r="F223" s="2">
         <v>70</v>
       </c>
       <c r="G223" t="s">
@@ -14176,10 +14235,10 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B224" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>690</v>
@@ -14190,7 +14249,7 @@
       <c r="E224" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F224" s="7">
+      <c r="F224" s="2">
         <v>70</v>
       </c>
       <c r="G224" t="s">
@@ -14205,10 +14264,10 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="B225" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>690</v>
@@ -14219,7 +14278,7 @@
       <c r="E225" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F225" s="7">
+      <c r="F225" s="2">
         <v>70</v>
       </c>
       <c r="G225" t="s">
@@ -14234,10 +14293,10 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B226" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>690</v>
@@ -14248,7 +14307,7 @@
       <c r="E226" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F226" s="7">
+      <c r="F226" s="2">
         <v>70</v>
       </c>
       <c r="G226" t="s">
@@ -14263,10 +14322,10 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B227" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>690</v>
@@ -14277,7 +14336,7 @@
       <c r="E227" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F227" s="7">
+      <c r="F227" s="2">
         <v>70</v>
       </c>
       <c r="G227" t="s">
@@ -14292,10 +14351,10 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B228" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>690</v>
@@ -14306,7 +14365,7 @@
       <c r="E228" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F228" s="7">
+      <c r="F228" s="2">
         <v>70</v>
       </c>
       <c r="G228" t="s">
@@ -14321,10 +14380,10 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B229" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>690</v>
@@ -14335,7 +14394,7 @@
       <c r="E229" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="F229" s="7">
+      <c r="F229" s="2">
         <v>70</v>
       </c>
       <c r="G229" t="s">
@@ -14345,6 +14404,122 @@
         <v>693</v>
       </c>
       <c r="I229" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>464</v>
+      </c>
+      <c r="B230" t="s">
+        <v>465</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F230" s="2">
+        <v>70</v>
+      </c>
+      <c r="G230" t="s">
+        <v>472</v>
+      </c>
+      <c r="H230" t="s">
+        <v>693</v>
+      </c>
+      <c r="I230" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>466</v>
+      </c>
+      <c r="B231" t="s">
+        <v>467</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F231" s="2">
+        <v>70</v>
+      </c>
+      <c r="G231" t="s">
+        <v>472</v>
+      </c>
+      <c r="H231" t="s">
+        <v>693</v>
+      </c>
+      <c r="I231" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>468</v>
+      </c>
+      <c r="B232" t="s">
+        <v>469</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F232" s="2">
+        <v>70</v>
+      </c>
+      <c r="G232" t="s">
+        <v>472</v>
+      </c>
+      <c r="H232" t="s">
+        <v>693</v>
+      </c>
+      <c r="I232" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>470</v>
+      </c>
+      <c r="B233" t="s">
+        <v>471</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F233" s="2">
+        <v>70</v>
+      </c>
+      <c r="G233" t="s">
+        <v>472</v>
+      </c>
+      <c r="H233" t="s">
+        <v>693</v>
+      </c>
+      <c r="I233" t="s">
         <v>694</v>
       </c>
     </row>
@@ -14358,6 +14533,168 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F606AB97-7AC5-49C6-9A12-A852503C2A14}">
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.42578125" customWidth="1"/>
+    <col min="2" max="2" width="62.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>936</v>
+      </c>
+      <c r="B4" t="s">
+        <v>937</v>
+      </c>
+      <c r="C4" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>804</v>
+      </c>
+      <c r="B5" t="s">
+        <v>805</v>
+      </c>
+      <c r="C5" t="s">
+        <v>943</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>943</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBCCFDC-4EB7-4695-AF08-ED1833819D06}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
